--- a/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 01.12.2025 a 08.12.2025.xlsx
+++ b/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 01.12.2025 a 08.12.2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/shirlei_witkowski_allianz_com_br/Documents/E-MAILS Santander Recusa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{913750D9-B8C9-4CAA-8194-492379584784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{85757B70-77AD-4AC7-B8D6-F3264521EA3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01.12" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="197">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -385,13 +385,324 @@
   </si>
   <si>
     <t xml:space="preserve">MASTER PREMIUM SOLUCOES FINANCEIRAS LTDA ME  </t>
+  </si>
+  <si>
+    <t>GUSTAVO BOGUSZEWSKI CPF- 03307627961</t>
+  </si>
+  <si>
+    <t>Chassi irregular</t>
+  </si>
+  <si>
+    <t>ALESSANDRA DOS SANTOS VICENTE CPF 28164087874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DORIEL DA SILVA FERREIRA BAR LTDA ME         </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, a apólice foi renovada na
+congênere de origem. Portanto, peço a gentileza de encaminhar a d
+ocumentação abaixo para análise:&lt;br&gt; Cópia da apólice congênere c
+om vigência de 2025 a 2026.&lt;br&gt; Endosso de cancelamento emitido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIT STOP COMERCIO DE BEBIDAS LTDA ME         </t>
+  </si>
+  <si>
+    <t>Informamos que a pr
+oposta em questão se encontra em duplicidade com a proposta 135475
+190 , para prosseguirmos com a emissão se faz necessário realizar
+o cancelamento da mesma. &lt;br&gt;&lt;br&gt;/////////////////////////////////
+/////////////////&lt;br&gt;&lt;br&gt;PENDÊNCIA 1736  DIVERGÊNCIAS CBE (Diverg
+ência de bônus/Mudança de Cobertura)&lt;br&gt;&lt;br&gt;Conforme CBE pela regr
+a de mudança de cobertura, ocorre a redução de 1 classe de bônus,
+assim sendo o correto bônus 0.&lt;br&gt;Com a correção ficou 10x R$ 419,
+64. Podemos emitir desta forma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOISES ALVES DOS SANTOS                      </t>
+  </si>
+  <si>
+    <t>Id
+entificamos que houve quebra de vigência de 125 dias (apólice canc
+elada em 25/07/25, conforme regra reduz 4 classes de bônus, assim
+sendoo correto bônus 0.&lt;br&gt;Com a correção ficou 10x R$ 1.084,11.
+Podemos emitir desta forma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIZ FERNANDO MORENO MARQUES                 </t>
+  </si>
+  <si>
+    <t>FRUSTRADO *PRAZO EXP * repique: Documento da moto, Painel com a motocicleta desligada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RICARDO HENRIQUE HELENO                      </t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 01.12.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGNALDO TIMOTIO MOREIRA DE JESUS             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRUSTRADO *PRAZO EXP * SEGURADO N CORRIGIU OS PASSOS SOLICITADOS repique:Porta malas aberto / Cor do veículo diferente do informado no CRLV </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEZERRA ADMINISTRACAO E SERVICOS LTDA        </t>
+  </si>
+  <si>
+    <t>FRUSTRADO *PRAZO EXP * SEGURADO N CORRIGIU OS PASSOS SOLICITADOS repique: Frente e lateral do passageiro, Chassi</t>
+  </si>
+  <si>
+    <t>RIBEIRO LOCACAO DE MAQUINAS E TERRAPLENAGEM L</t>
+  </si>
+  <si>
+    <t>FRUSTRADO *PRAZO EXP * SEGURADO N CORRIGIU OS PASSOS SOLICITADOS repique: Chassi // CHASSI ILEGÍVEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VINICIUS DE MARCO E PAULA                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GABRIELLY DOLORES RIOS DA CUNHA              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAGUARBERTO LOPES DE MEDEIROS                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAMIAO MOURATO BEZERRA                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">55 031 804 MARIANA CAMARGO AGUIAR ME         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEORGINA EULALIA BUENO DO PRADO              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUCILENE DE SOUZA DUARTE                     </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não há
+possibilidade efetuar a transferência de bônus para o(a)
+senhor(a) JUCILENE DE SOUZA DUARTE, pois este não consta como
+condutor na apólice anterior.
+Neste caso estamos nesta data efetuando a recusa desta proposta.
+Orientamos transmitir um novo processo como Seguro Novo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE LUIZ CORREA DOS SANTOS FILHO            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">WILLIAN DIAS FERREIRA                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVANDRO GONCALVES                            </t>
+  </si>
+  <si>
+    <t>RECUSA: SEGURADO NAO APRESENTOU O CRLV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G F DO VALE EPP                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MILTON MARILDO MILARE                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANUBIA NOVAIS DE CARVALHO                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GIRLENE ALVES BONATO MORINI                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAIME SASAKI                                 </t>
+  </si>
+  <si>
+    <t>Co
+nforme regra, apólice não completou 365 dias vigente , portanto, d
+eve-se manter a classe de bônus, assim sendo o bônus correto 1.&lt;br
+&gt;Com a correção ficou 10x R$ 439,98. Podemos emitir desta forma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FATIMA IARA GOMES                            </t>
+  </si>
+  <si>
+    <t>Favor enviar cópia completa da apólice referente 2024/2025 (Não
+será aceito a CI, uma vez em que a CBE não retorna os dados)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FERNANDO DONISETI PULTZ                      </t>
+  </si>
+  <si>
+    <t>Informamos que a p
+roposta em questão se encontra em duplicidade com a proposta 13481
+1233, para prosseguirmos com a emissão se faz necessário realizar
+o cancelamento dela.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUGUSTO CESAR ODORIZZI                       </t>
+  </si>
+  <si>
+    <t>Identificamos uma divergência entre o modelo do veículo informado
+na transmissão da proposta. Para garantir a correção e a emissão d
+o seguro com os dados precisos, solicitamos que nos encaminhe uma
+cópia do CRLV (Certificado de Registro e Licenciamento do Veículo)
+ou nota fiscal para confirmar o modelo correto do veículo."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUELLEN CRISTINA MILLAS PINTO                </t>
+  </si>
+  <si>
+    <t>FRUSTRADO *PRAZO EXP * SEGURADO N FEZ O ENVIO DE TODAS AS FOTOS // FOTO 45 // CHASSI // PORTA-MALAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELTONJON CORREA DA SILVA                     </t>
+  </si>
+  <si>
+    <t>FRUSTRADO *PRAZO EXP * SEGURADO N CORRIGIU OS PASSOS SOLICITADOS repique: D, Frente passageiro, Frente motorista, Traseira motorista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JURACI DA SILVA SANTOS                       </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: DOCUMENTO DO VEICULO ( NÃO ENVIADO) CHASSI (FOTO DO LOCAL INCORRETO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEBORA DENARDI DE PAULA                      </t>
+  </si>
+  <si>
+    <t>FRUSTRADO *PRAZO EXP * SEGURADO N CORRIGIU OS PASSOS SOLICITADOS repique: Documento do veículo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BENASILDA FREITAS VILELA                     </t>
+  </si>
+  <si>
+    <t>FRUSTRADO *PRAZO EXP * SEGURADO N CORRIGIU OS PASSOS SOLICITADOS repique: Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADRIANA RODOLFA DIAS PEREIRA RESTAURANTE ME  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">APARECIDA LIVIO ZANE                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">WILLIAM VICENTE BALENSIEFER                  </t>
+  </si>
+  <si>
+    <t>***FRUSTRADO**CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO: Chassi local incorreto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA DAS GRACAS TENORIO VITAL NOE           </t>
+  </si>
+  <si>
+    <t>FRUSTRADO *PRAZO EXP * SEGURADO N CORRIGIU OS PASSOS SOLICITADOS repique: Documento do veículo, Frente e lateral do passageiro, Painel com carro desligado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TULZA CARDOSO DE MORAES                      </t>
+  </si>
+  <si>
+    <t>FRUSTRADO *PRAZO EXP * SEGURADO N CORRIGIU OS PASSOS SOLICITADOS repique: Painel com carro desligado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA VANUZIA BEZERRA LTDA                   </t>
+  </si>
+  <si>
+    <t>FRUSTRADO *PRAZO EXP * SEGURADO N CORRIGIU OS PASSOS SOLICITADOS repique: Documento do veículo, Painel com carro desligado, Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALICE ABREU GONCALVES                        </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: Traseira e lateral do motorista, Traseira e lateral do passageiro)Fotos não enquadradas corretamente)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CELSO ROBERTO ROSA DA SILVA                  </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: Frente e lateral do passageiro e do motorista, Traseira e lateral do motorista, (Foto não enquadrada corretamente) Chassi (ocal incorreto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GILMAR SOARES DE SOUZA                       </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, a apólice foi renovada na
+congênere de origem. Portanto, peço a gentileza de encaminhar a d
+ocumentação abaixo para análise:&lt;br&gt; Cópia da apólice congênere c
+om vigência de 2025 a 2026;&lt;br&gt; Endosso de cancelamento emitido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA IZABEL DE OLIVEIRA LYRA                </t>
+  </si>
+  <si>
+    <t>Proposta em duplicidade&lt;br&gt;&lt;br&gt;Informamos que a p
+roposta em questão se encontra em duplicidade com a proposta 13561
+6267, para prosseguirmos com a emissão se faz necessário realizar
+o cancelamento de uma delas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADAIR ANTONIETTI                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AFONSO CELSO FULCHI VIANNA JUNIOR            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KARLOS ALBERTO CONCEICAO SILVA               </t>
+  </si>
+  <si>
+    <t>Co
+nforme CBE houve sinistro na apólice anterior, portanto a renovaçã
+o correta é externa com sinistro, conforme regra diminui uma class
+e de bônus, assim sendo o correto bônus 0. &lt;br&gt;Com a correção fico
+u 10x R$ 989,31. Podemos emitir desta forma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITAMAR JOSE DOS SANTOS                       </t>
+  </si>
+  <si>
+    <t>C
+onforme CBE houve sinistro na apólice anterior, portanto a renovaç
+ão correta é externa COM sinistro, conforme regra diminui uma clas
+se debônus, assim sendo o correto bônus  9 . &lt;br&gt;Com a correção
+ficou 10x R$ 238,80. Podemos emitir desta forma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUBENILSON SILVA MENEZES                     </t>
+  </si>
+  <si>
+    <t>Conforme CBE pela regra de mudança de cobertura
+, ocorre a redução de 1 classe de bônus, assim sendo o correto bôn
+us 1.Com a correção ficou 10x R$ 160,59. Podemos emitir desta for
+ma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIEL GUIMARAES GIOVANI                     </t>
+  </si>
+  <si>
+    <t>A apólice enviada (CI 65724024693999) foi cancelada na congênere e
+m 09/12/24, caso não possua apólice com vigência atual, será neces
+sário realizar nova transmissão como seguro novo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIZ FRANCISCO DA SILVA                      </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, a apólice foi renovada na
+congênere de origem. Portanto, peço a gentileza de encaminhar a d
+ocumentação abaixo para análise:&lt;br&gt; Cópia da apólice congênere c
+om vigência de 2025 a 2026.&lt;br&gt; Endosso de cancelamento emitido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCISCO GERLAN EVANGELISTA OLIVEIRA        </t>
+  </si>
+  <si>
+    <t>Conforme CBE pela regra de mudança de cobertura
+, de INCÊNDIO E BOUBO para COMPREENSIVA, ocorre a redução de 1 cla
+sse debônus, assim sendo o correto bônus 0.&lt;br&gt;Com a correção fico
+u 10x R$ 423,80. Podemos emitir desta forma?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -427,6 +738,18 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -803,37 +1126,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -860,7 +1153,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -870,12 +1162,41 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1329,13 +1650,13 @@
       <c r="C4" s="25">
         <v>45992</v>
       </c>
-      <c r="D4" s="73" t="s">
+      <c r="D4" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="65">
+      <c r="E4" s="55">
         <v>3450166159</v>
       </c>
-      <c r="F4" s="66" t="s">
+      <c r="F4" s="56" t="s">
         <v>16</v>
       </c>
       <c r="G4" s="42" t="s">
@@ -1356,16 +1677,16 @@
       <c r="C5" s="25">
         <v>45992</v>
       </c>
-      <c r="D5" s="75">
+      <c r="D5" s="22">
         <v>135474140</v>
       </c>
       <c r="E5" s="17">
         <v>3450153564</v>
       </c>
-      <c r="F5" s="71" t="s">
+      <c r="F5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="72" t="s">
+      <c r="G5" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H5" s="45" t="s">
@@ -1385,16 +1706,16 @@
       <c r="C6" s="25">
         <v>45992</v>
       </c>
-      <c r="D6" s="75">
+      <c r="D6" s="22">
         <v>135474812</v>
       </c>
       <c r="E6" s="17">
         <v>3450153696</v>
       </c>
-      <c r="F6" s="71" t="s">
+      <c r="F6" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="72" t="s">
+      <c r="G6" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H6" s="45" t="s">
@@ -1414,16 +1735,16 @@
       <c r="C7" s="25">
         <v>45992</v>
       </c>
-      <c r="D7" s="75">
+      <c r="D7" s="22">
         <v>135468066</v>
       </c>
       <c r="E7" s="17">
         <v>3450153014</v>
       </c>
-      <c r="F7" s="71" t="s">
+      <c r="F7" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="72" t="s">
+      <c r="G7" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H7" s="45" t="s">
@@ -1443,16 +1764,16 @@
       <c r="C8" s="25">
         <v>45992</v>
       </c>
-      <c r="D8" s="75">
+      <c r="D8" s="22">
         <v>135475160</v>
       </c>
       <c r="E8" s="17">
         <v>3450153751</v>
       </c>
-      <c r="F8" s="71" t="s">
+      <c r="F8" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="72" t="s">
+      <c r="G8" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H8" s="45" t="s">
@@ -1472,16 +1793,16 @@
       <c r="C9" s="25">
         <v>45992</v>
       </c>
-      <c r="D9" s="75">
+      <c r="D9" s="22">
         <v>135475293</v>
       </c>
       <c r="E9" s="17">
         <v>3450153773</v>
       </c>
-      <c r="F9" s="71" t="s">
+      <c r="F9" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="72" t="s">
+      <c r="G9" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H9" s="45" t="s">
@@ -1501,16 +1822,16 @@
       <c r="C10" s="25">
         <v>45992</v>
       </c>
-      <c r="D10" s="75">
+      <c r="D10" s="22">
         <v>135479583</v>
       </c>
       <c r="E10" s="17">
         <v>3450154048</v>
       </c>
-      <c r="F10" s="71" t="s">
+      <c r="F10" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="72" t="s">
+      <c r="G10" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H10" s="45" t="s">
@@ -1530,16 +1851,16 @@
       <c r="C11" s="25">
         <v>45992</v>
       </c>
-      <c r="D11" s="75">
+      <c r="D11" s="22">
         <v>135498971</v>
       </c>
       <c r="E11" s="17">
         <v>3450155600</v>
       </c>
-      <c r="F11" s="71" t="s">
+      <c r="F11" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="72" t="s">
+      <c r="G11" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H11" s="45" t="s">
@@ -1559,16 +1880,16 @@
       <c r="C12" s="25">
         <v>45992</v>
       </c>
-      <c r="D12" s="75">
+      <c r="D12" s="22">
         <v>135493667</v>
       </c>
       <c r="E12" s="17">
         <v>3450155016</v>
       </c>
-      <c r="F12" s="71" t="s">
+      <c r="F12" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="G12" s="72" t="s">
+      <c r="G12" s="61" t="s">
         <v>26</v>
       </c>
       <c r="H12" s="45" t="s">
@@ -1588,16 +1909,16 @@
       <c r="C13" s="25">
         <v>45992</v>
       </c>
-      <c r="D13" s="75">
+      <c r="D13" s="22">
         <v>135514119</v>
       </c>
       <c r="E13" s="17">
         <v>3450156875</v>
       </c>
-      <c r="F13" s="71" t="s">
+      <c r="F13" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="G13" s="72" t="s">
+      <c r="G13" s="61" t="s">
         <v>26</v>
       </c>
       <c r="H13" s="45" t="s">
@@ -1617,16 +1938,16 @@
       <c r="C14" s="25">
         <v>45992</v>
       </c>
-      <c r="D14" s="75">
+      <c r="D14" s="22">
         <v>135512202</v>
       </c>
       <c r="E14" s="17">
         <v>3450156534</v>
       </c>
-      <c r="F14" s="71" t="s">
+      <c r="F14" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="G14" s="72" t="s">
+      <c r="G14" s="61" t="s">
         <v>31</v>
       </c>
       <c r="H14" s="45" t="s">
@@ -1646,19 +1967,19 @@
       <c r="C15" s="25">
         <v>45992</v>
       </c>
-      <c r="D15" s="75">
+      <c r="D15" s="22">
         <v>135522219</v>
       </c>
       <c r="E15" s="17">
         <v>3450157656</v>
       </c>
-      <c r="F15" s="71" t="s">
+      <c r="F15" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="G15" s="72" t="s">
+      <c r="G15" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="H15" s="76" t="s">
+      <c r="H15" s="45" t="s">
         <v>35</v>
       </c>
       <c r="I15" s="44">
@@ -1675,16 +1996,16 @@
       <c r="C16" s="25">
         <v>45992</v>
       </c>
-      <c r="D16" s="75">
+      <c r="D16" s="22">
         <v>135523239</v>
       </c>
       <c r="E16" s="17">
         <v>3450157832</v>
       </c>
-      <c r="F16" s="71" t="s">
+      <c r="F16" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="G16" s="72" t="s">
+      <c r="G16" s="61" t="s">
         <v>31</v>
       </c>
       <c r="H16" s="45" t="s">
@@ -1704,16 +2025,16 @@
       <c r="C17" s="25">
         <v>45992</v>
       </c>
-      <c r="D17" s="75">
+      <c r="D17" s="22">
         <v>135522967</v>
       </c>
       <c r="E17" s="17">
         <v>3450157777</v>
       </c>
-      <c r="F17" s="71" t="s">
+      <c r="F17" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="G17" s="72" t="s">
+      <c r="G17" s="61" t="s">
         <v>26</v>
       </c>
       <c r="H17" s="45" t="s">
@@ -1733,16 +2054,16 @@
       <c r="C18" s="25">
         <v>45992</v>
       </c>
-      <c r="D18" s="75">
+      <c r="D18" s="22">
         <v>135492497</v>
       </c>
       <c r="E18" s="17">
         <v>3450154906</v>
       </c>
-      <c r="F18" s="71" t="s">
+      <c r="F18" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="G18" s="72" t="s">
+      <c r="G18" s="61" t="s">
         <v>26</v>
       </c>
       <c r="H18" s="45" t="s">
@@ -1762,16 +2083,16 @@
       <c r="C19" s="25">
         <v>45992</v>
       </c>
-      <c r="D19" s="75">
+      <c r="D19" s="22">
         <v>135478449</v>
       </c>
       <c r="E19" s="17">
         <v>3450154026</v>
       </c>
-      <c r="F19" s="71" t="s">
+      <c r="F19" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="G19" s="72" t="s">
+      <c r="G19" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H19" s="45" t="s">
@@ -1791,16 +2112,16 @@
       <c r="C20" s="25">
         <v>45992</v>
       </c>
-      <c r="D20" s="75">
+      <c r="D20" s="22">
         <v>135529810</v>
       </c>
       <c r="E20" s="17">
         <v>3450158206</v>
       </c>
-      <c r="F20" s="71" t="s">
+      <c r="F20" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="G20" s="72" t="s">
+      <c r="G20" s="61" t="s">
         <v>26</v>
       </c>
       <c r="H20" s="45" t="s">
@@ -1820,16 +2141,16 @@
       <c r="C21" s="25">
         <v>45992</v>
       </c>
-      <c r="D21" s="75">
+      <c r="D21" s="22">
         <v>135534132</v>
       </c>
       <c r="E21" s="17">
         <v>3450151958</v>
       </c>
-      <c r="F21" s="71" t="s">
+      <c r="F21" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="G21" s="72" t="s">
+      <c r="G21" s="61" t="s">
         <v>26</v>
       </c>
       <c r="H21" s="45" t="s">
@@ -1849,16 +2170,16 @@
       <c r="C22" s="25">
         <v>45992</v>
       </c>
-      <c r="D22" s="75">
+      <c r="D22" s="22">
         <v>135544398</v>
       </c>
       <c r="E22" s="17">
         <v>3450159251</v>
       </c>
-      <c r="F22" s="71" t="s">
+      <c r="F22" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="G22" s="72" t="s">
+      <c r="G22" s="61" t="s">
         <v>26</v>
       </c>
       <c r="H22" s="45" t="s">
@@ -1878,16 +2199,16 @@
       <c r="C23" s="25">
         <v>45992</v>
       </c>
-      <c r="D23" s="75">
+      <c r="D23" s="22">
         <v>135546544</v>
       </c>
       <c r="E23" s="17">
         <v>3450159592</v>
       </c>
-      <c r="F23" s="71" t="s">
+      <c r="F23" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="G23" s="72" t="s">
+      <c r="G23" s="61" t="s">
         <v>26</v>
       </c>
       <c r="H23" s="45" t="s">
@@ -1907,16 +2228,16 @@
       <c r="C24" s="25">
         <v>45992</v>
       </c>
-      <c r="D24" s="75">
+      <c r="D24" s="22">
         <v>135533868</v>
       </c>
       <c r="E24" s="17">
         <v>3450151991</v>
       </c>
-      <c r="F24" s="71" t="s">
+      <c r="F24" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="G24" s="72" t="s">
+      <c r="G24" s="61" t="s">
         <v>26</v>
       </c>
       <c r="H24" s="45" t="s">
@@ -1936,16 +2257,16 @@
       <c r="C25" s="25">
         <v>45992</v>
       </c>
-      <c r="D25" s="75">
+      <c r="D25" s="22">
         <v>135535321</v>
       </c>
       <c r="E25" s="17">
         <v>3450158723</v>
       </c>
-      <c r="F25" s="71" t="s">
+      <c r="F25" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="G25" s="72" t="s">
+      <c r="G25" s="61" t="s">
         <v>31</v>
       </c>
       <c r="H25" s="45" t="s">
@@ -1965,16 +2286,16 @@
       <c r="C26" s="25">
         <v>45992</v>
       </c>
-      <c r="D26" s="75">
+      <c r="D26" s="22">
         <v>135533044</v>
       </c>
       <c r="E26" s="17">
         <v>3450152167</v>
       </c>
-      <c r="F26" s="71" t="s">
+      <c r="F26" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="G26" s="72" t="s">
+      <c r="G26" s="61" t="s">
         <v>26</v>
       </c>
       <c r="H26" s="45" t="s">
@@ -1994,16 +2315,16 @@
       <c r="C27" s="25">
         <v>45992</v>
       </c>
-      <c r="D27" s="75">
+      <c r="D27" s="22">
         <v>135546431</v>
       </c>
       <c r="E27" s="17">
         <v>3450159570</v>
       </c>
-      <c r="F27" s="71" t="s">
+      <c r="F27" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="G27" s="72" t="s">
+      <c r="G27" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H27" s="45" t="s">
@@ -2023,16 +2344,16 @@
       <c r="C28" s="25">
         <v>45992</v>
       </c>
-      <c r="D28" s="75">
+      <c r="D28" s="22">
         <v>135545842</v>
       </c>
       <c r="E28" s="17">
         <v>3450159493</v>
       </c>
-      <c r="F28" s="71" t="s">
+      <c r="F28" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="G28" s="72" t="s">
+      <c r="G28" s="61" t="s">
         <v>26</v>
       </c>
       <c r="H28" s="45" t="s">
@@ -2052,16 +2373,16 @@
       <c r="C29" s="25">
         <v>45992</v>
       </c>
-      <c r="D29" s="75">
+      <c r="D29" s="22">
         <v>135529148</v>
       </c>
       <c r="E29" s="17">
         <v>3450158173</v>
       </c>
-      <c r="F29" s="71" t="s">
+      <c r="F29" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G29" s="72" t="s">
+      <c r="G29" s="61" t="s">
         <v>26</v>
       </c>
       <c r="H29" s="45" t="s">
@@ -2081,16 +2402,16 @@
       <c r="C30" s="25">
         <v>45992</v>
       </c>
-      <c r="D30" s="75">
+      <c r="D30" s="22">
         <v>135536166</v>
       </c>
       <c r="E30" s="17">
         <v>3450155951</v>
       </c>
-      <c r="F30" s="71" t="s">
+      <c r="F30" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="G30" s="72" t="s">
+      <c r="G30" s="61" t="s">
         <v>26</v>
       </c>
       <c r="H30" s="45" t="s">
@@ -2110,16 +2431,16 @@
       <c r="C31" s="25">
         <v>45992</v>
       </c>
-      <c r="D31" s="75">
+      <c r="D31" s="22">
         <v>135557269</v>
       </c>
       <c r="E31" s="17">
         <v>3450160593</v>
       </c>
-      <c r="F31" s="71" t="s">
+      <c r="F31" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="G31" s="72" t="s">
+      <c r="G31" s="61" t="s">
         <v>26</v>
       </c>
       <c r="H31" s="45" t="s">
@@ -2139,19 +2460,19 @@
       <c r="C32" s="25">
         <v>45992</v>
       </c>
-      <c r="D32" s="75">
+      <c r="D32" s="22">
         <v>135494206</v>
       </c>
       <c r="E32" s="17">
         <v>3450155060</v>
       </c>
-      <c r="F32" s="71" t="s">
+      <c r="F32" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="G32" s="72" t="s">
+      <c r="G32" s="61" t="s">
         <v>63</v>
       </c>
-      <c r="H32" s="76" t="s">
+      <c r="H32" s="45" t="s">
         <v>64</v>
       </c>
       <c r="I32" s="44">
@@ -2168,16 +2489,16 @@
       <c r="C33" s="25">
         <v>45992</v>
       </c>
-      <c r="D33" s="75">
+      <c r="D33" s="22">
         <v>135460854</v>
       </c>
       <c r="E33" s="17">
         <v>3450152112</v>
       </c>
-      <c r="F33" s="71" t="s">
+      <c r="F33" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="G33" s="72" t="s">
+      <c r="G33" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H33" s="45" t="s">
@@ -2197,16 +2518,16 @@
       <c r="C34" s="25">
         <v>45992</v>
       </c>
-      <c r="D34" s="75">
+      <c r="D34" s="22">
         <v>135485806</v>
       </c>
       <c r="E34" s="17">
         <v>3450154246</v>
       </c>
-      <c r="F34" s="71" t="s">
+      <c r="F34" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="G34" s="72" t="s">
+      <c r="G34" s="61" t="s">
         <v>26</v>
       </c>
       <c r="H34" s="45" t="s">
@@ -2226,16 +2547,16 @@
       <c r="C35" s="25">
         <v>45992</v>
       </c>
-      <c r="D35" s="75">
+      <c r="D35" s="22">
         <v>135560592</v>
       </c>
       <c r="E35" s="17">
         <v>3450161165</v>
       </c>
-      <c r="F35" s="71" t="s">
+      <c r="F35" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="G35" s="72" t="s">
+      <c r="G35" s="61" t="s">
         <v>31</v>
       </c>
       <c r="H35" s="45" t="s">
@@ -2255,16 +2576,16 @@
       <c r="C36" s="25">
         <v>45992</v>
       </c>
-      <c r="D36" s="75">
+      <c r="D36" s="22">
         <v>135579805</v>
       </c>
       <c r="E36" s="17">
         <v>3450162970</v>
       </c>
-      <c r="F36" s="71" t="s">
+      <c r="F36" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="G36" s="72" t="s">
+      <c r="G36" s="61" t="s">
         <v>31</v>
       </c>
       <c r="H36" s="45" t="s">
@@ -2284,16 +2605,16 @@
       <c r="C37" s="25">
         <v>45992</v>
       </c>
-      <c r="D37" s="75">
+      <c r="D37" s="22">
         <v>135581568</v>
       </c>
       <c r="E37" s="17">
         <v>3450161880</v>
       </c>
-      <c r="F37" s="71" t="s">
+      <c r="F37" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="G37" s="72" t="s">
+      <c r="G37" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H37" s="45" t="s">
@@ -2313,16 +2634,16 @@
       <c r="C38" s="25">
         <v>45992</v>
       </c>
-      <c r="D38" s="75">
+      <c r="D38" s="22">
         <v>135574821</v>
       </c>
       <c r="E38" s="17">
         <v>3450162342</v>
       </c>
-      <c r="F38" s="71" t="s">
+      <c r="F38" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="G38" s="72" t="s">
+      <c r="G38" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H38" s="45" t="s">
@@ -2342,16 +2663,16 @@
       <c r="C39" s="25">
         <v>45992</v>
       </c>
-      <c r="D39" s="75">
+      <c r="D39" s="22">
         <v>135555960</v>
       </c>
       <c r="E39" s="17">
         <v>3450156050</v>
       </c>
-      <c r="F39" s="71" t="s">
+      <c r="F39" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="G39" s="72" t="s">
+      <c r="G39" s="61" t="s">
         <v>31</v>
       </c>
       <c r="H39" s="45" t="s">
@@ -2371,16 +2692,16 @@
       <c r="C40" s="25">
         <v>45992</v>
       </c>
-      <c r="D40" s="75">
+      <c r="D40" s="22">
         <v>135547329</v>
       </c>
       <c r="E40" s="17">
         <v>3450159834</v>
       </c>
-      <c r="F40" s="71" t="s">
+      <c r="F40" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="G40" s="72" t="s">
+      <c r="G40" s="61" t="s">
         <v>26</v>
       </c>
       <c r="H40" s="45" t="s">
@@ -2400,22 +2721,22 @@
       <c r="C41" s="25">
         <v>45992</v>
       </c>
-      <c r="D41" s="75">
+      <c r="D41" s="22">
         <v>135595402</v>
       </c>
       <c r="E41" s="17">
         <v>3450164652</v>
       </c>
-      <c r="F41" s="71" t="s">
+      <c r="F41" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="G41" s="72" t="s">
+      <c r="G41" s="61" t="s">
         <v>75</v>
       </c>
       <c r="H41" s="45" t="s">
         <v>76</v>
       </c>
-      <c r="I41" s="77">
+      <c r="I41" s="64">
         <v>45992</v>
       </c>
     </row>
@@ -2429,16 +2750,16 @@
       <c r="C42" s="25">
         <v>45992</v>
       </c>
-      <c r="D42" s="75">
+      <c r="D42" s="22">
         <v>135491263</v>
       </c>
       <c r="E42" s="17">
         <v>3450154686</v>
       </c>
-      <c r="F42" s="71" t="s">
+      <c r="F42" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="G42" s="72" t="s">
+      <c r="G42" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H42" s="45" t="s">
@@ -2458,16 +2779,16 @@
       <c r="C43" s="25">
         <v>45992</v>
       </c>
-      <c r="D43" s="75">
+      <c r="D43" s="22">
         <v>135516843</v>
       </c>
       <c r="E43" s="17">
         <v>3450157106</v>
       </c>
-      <c r="F43" s="71" t="s">
+      <c r="F43" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="G43" s="72" t="s">
+      <c r="G43" s="61" t="s">
         <v>26</v>
       </c>
       <c r="H43" s="46" t="s">
@@ -2487,16 +2808,16 @@
       <c r="C44" s="25">
         <v>45992</v>
       </c>
-      <c r="D44" s="75">
+      <c r="D44" s="22">
         <v>135472699</v>
       </c>
       <c r="E44" s="17">
         <v>3450153465</v>
       </c>
-      <c r="F44" s="71" t="s">
+      <c r="F44" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="G44" s="72" t="s">
+      <c r="G44" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H44" s="46" t="s">
@@ -2516,16 +2837,16 @@
       <c r="C45" s="25">
         <v>45992</v>
       </c>
-      <c r="D45" s="75">
+      <c r="D45" s="22">
         <v>135461886</v>
       </c>
       <c r="E45" s="17">
         <v>3450152211</v>
       </c>
-      <c r="F45" s="71" t="s">
+      <c r="F45" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="G45" s="72" t="s">
+      <c r="G45" s="61" t="s">
         <v>26</v>
       </c>
       <c r="H45" s="45" t="s">
@@ -2545,16 +2866,16 @@
       <c r="C46" s="25">
         <v>45992</v>
       </c>
-      <c r="D46" s="75">
+      <c r="D46" s="22">
         <v>135632322</v>
       </c>
       <c r="E46" s="17">
         <v>3450167842</v>
       </c>
-      <c r="F46" s="71" t="s">
+      <c r="F46" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="G46" s="72" t="s">
+      <c r="G46" s="61" t="s">
         <v>31</v>
       </c>
       <c r="H46" s="45" t="s">
@@ -2574,16 +2895,16 @@
       <c r="C47" s="25">
         <v>45992</v>
       </c>
-      <c r="D47" s="75">
+      <c r="D47" s="22">
         <v>135458498</v>
       </c>
       <c r="E47" s="17">
         <v>3450151914</v>
       </c>
-      <c r="F47" s="71" t="s">
+      <c r="F47" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="G47" s="72" t="s">
+      <c r="G47" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H47" s="45" t="s">
@@ -2603,16 +2924,16 @@
       <c r="C48" s="25">
         <v>45992</v>
       </c>
-      <c r="D48" s="75">
+      <c r="D48" s="22">
         <v>135491743</v>
       </c>
       <c r="E48" s="17">
         <v>3450153278</v>
       </c>
-      <c r="F48" s="71" t="s">
+      <c r="F48" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="G48" s="72" t="s">
+      <c r="G48" s="61" t="s">
         <v>26</v>
       </c>
       <c r="H48" s="45" t="s">
@@ -2632,16 +2953,16 @@
       <c r="C49" s="25">
         <v>45992</v>
       </c>
-      <c r="D49" s="75">
+      <c r="D49" s="22">
         <v>135464003</v>
       </c>
       <c r="E49" s="17">
         <v>3450152398</v>
       </c>
-      <c r="F49" s="71" t="s">
+      <c r="F49" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="G49" s="72" t="s">
+      <c r="G49" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H49" s="45" t="s">
@@ -2661,16 +2982,16 @@
       <c r="C50" s="25">
         <v>45992</v>
       </c>
-      <c r="D50" s="75">
+      <c r="D50" s="22">
         <v>135464315</v>
       </c>
       <c r="E50" s="17">
         <v>3450150693</v>
       </c>
-      <c r="F50" s="71" t="s">
+      <c r="F50" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="G50" s="72" t="s">
+      <c r="G50" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H50" s="45" t="s">
@@ -2690,16 +3011,16 @@
       <c r="C51" s="25">
         <v>45992</v>
       </c>
-      <c r="D51" s="75">
+      <c r="D51" s="22">
         <v>135465557</v>
       </c>
       <c r="E51" s="17">
         <v>3450147371</v>
       </c>
-      <c r="F51" s="71" t="s">
+      <c r="F51" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="G51" s="72" t="s">
+      <c r="G51" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H51" s="45" t="s">
@@ -2719,16 +3040,16 @@
       <c r="C52" s="25">
         <v>45992</v>
       </c>
-      <c r="D52" s="75">
+      <c r="D52" s="22">
         <v>135467783</v>
       </c>
       <c r="E52" s="17">
         <v>3450152937</v>
       </c>
-      <c r="F52" s="71" t="s">
+      <c r="F52" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="G52" s="72" t="s">
+      <c r="G52" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H52" s="45" t="s">
@@ -2748,16 +3069,16 @@
       <c r="C53" s="25">
         <v>45992</v>
       </c>
-      <c r="D53" s="75">
+      <c r="D53" s="22">
         <v>135468824</v>
       </c>
       <c r="E53" s="17">
         <v>3450153124</v>
       </c>
-      <c r="F53" s="71" t="s">
+      <c r="F53" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="G53" s="72" t="s">
+      <c r="G53" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H53" s="45" t="s">
@@ -2777,16 +3098,16 @@
       <c r="C54" s="25">
         <v>45992</v>
       </c>
-      <c r="D54" s="75">
+      <c r="D54" s="22">
         <v>135469361</v>
       </c>
       <c r="E54" s="17">
         <v>3450153179</v>
       </c>
-      <c r="F54" s="71" t="s">
+      <c r="F54" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="G54" s="72" t="s">
+      <c r="G54" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H54" s="45" t="s">
@@ -2806,16 +3127,16 @@
       <c r="C55" s="25">
         <v>45992</v>
       </c>
-      <c r="D55" s="75">
+      <c r="D55" s="22">
         <v>135474843</v>
       </c>
       <c r="E55" s="17">
         <v>3450153707</v>
       </c>
-      <c r="F55" s="71" t="s">
+      <c r="F55" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="G55" s="72" t="s">
+      <c r="G55" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H55" s="45" t="s">
@@ -2835,16 +3156,16 @@
       <c r="C56" s="25">
         <v>45992</v>
       </c>
-      <c r="D56" s="75">
+      <c r="D56" s="22">
         <v>135475874</v>
       </c>
       <c r="E56" s="17">
         <v>3450153817</v>
       </c>
-      <c r="F56" s="71" t="s">
+      <c r="F56" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="G56" s="72" t="s">
+      <c r="G56" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H56" s="45" t="s">
@@ -2864,16 +3185,16 @@
       <c r="C57" s="25">
         <v>45992</v>
       </c>
-      <c r="D57" s="75">
+      <c r="D57" s="22">
         <v>135476431</v>
       </c>
       <c r="E57" s="17">
         <v>3450153894</v>
       </c>
-      <c r="F57" s="71" t="s">
+      <c r="F57" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="G57" s="72" t="s">
+      <c r="G57" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H57" s="45" t="s">
@@ -2893,16 +3214,16 @@
       <c r="C58" s="25">
         <v>45992</v>
       </c>
-      <c r="D58" s="75">
+      <c r="D58" s="22">
         <v>135477461</v>
       </c>
       <c r="E58" s="17">
         <v>3450153971</v>
       </c>
-      <c r="F58" s="71" t="s">
+      <c r="F58" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="G58" s="72" t="s">
+      <c r="G58" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H58" s="45" t="s">
@@ -2922,16 +3243,16 @@
       <c r="C59" s="25">
         <v>45992</v>
       </c>
-      <c r="D59" s="75">
+      <c r="D59" s="22">
         <v>135485394</v>
       </c>
       <c r="E59" s="17">
         <v>3450154213</v>
       </c>
-      <c r="F59" s="71" t="s">
+      <c r="F59" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="G59" s="72" t="s">
+      <c r="G59" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H59" s="45" t="s">
@@ -2951,16 +3272,16 @@
       <c r="C60" s="25">
         <v>45992</v>
       </c>
-      <c r="D60" s="75">
+      <c r="D60" s="22">
         <v>135488494</v>
       </c>
       <c r="E60" s="17">
         <v>3450151364</v>
       </c>
-      <c r="F60" s="71" t="s">
+      <c r="F60" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="G60" s="72" t="s">
+      <c r="G60" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H60" s="45" t="s">
@@ -2980,16 +3301,16 @@
       <c r="C61" s="25">
         <v>45992</v>
       </c>
-      <c r="D61" s="75">
+      <c r="D61" s="22">
         <v>135490205</v>
       </c>
       <c r="E61" s="17">
         <v>3450154609</v>
       </c>
-      <c r="F61" s="71" t="s">
+      <c r="F61" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="G61" s="72" t="s">
+      <c r="G61" s="61" t="s">
         <v>26</v>
       </c>
       <c r="H61" s="45" t="s">
@@ -3009,16 +3330,16 @@
       <c r="C62" s="25">
         <v>45992</v>
       </c>
-      <c r="D62" s="75">
+      <c r="D62" s="22">
         <v>135491118</v>
       </c>
       <c r="E62" s="17">
         <v>3450153575</v>
       </c>
-      <c r="F62" s="71" t="s">
+      <c r="F62" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="G62" s="72" t="s">
+      <c r="G62" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H62" s="45" t="s">
@@ -3038,16 +3359,16 @@
       <c r="C63" s="25">
         <v>45992</v>
       </c>
-      <c r="D63" s="75">
+      <c r="D63" s="22">
         <v>135491355</v>
       </c>
       <c r="E63" s="17">
         <v>3450154720</v>
       </c>
-      <c r="F63" s="71" t="s">
+      <c r="F63" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="G63" s="72" t="s">
+      <c r="G63" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H63" s="45" t="s">
@@ -3067,16 +3388,16 @@
       <c r="C64" s="25">
         <v>45992</v>
       </c>
-      <c r="D64" s="75">
+      <c r="D64" s="22">
         <v>135491432</v>
       </c>
       <c r="E64" s="17">
         <v>3450154752</v>
       </c>
-      <c r="F64" s="71" t="s">
+      <c r="F64" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="G64" s="72" t="s">
+      <c r="G64" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H64" s="45" t="s">
@@ -3096,16 +3417,16 @@
       <c r="C65" s="25">
         <v>45992</v>
       </c>
-      <c r="D65" s="75">
+      <c r="D65" s="22">
         <v>135491465</v>
       </c>
       <c r="E65" s="17">
         <v>3450153399</v>
       </c>
-      <c r="F65" s="71" t="s">
+      <c r="F65" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="G65" s="72" t="s">
+      <c r="G65" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H65" s="45" t="s">
@@ -3125,16 +3446,16 @@
       <c r="C66" s="25">
         <v>45992</v>
       </c>
-      <c r="D66" s="75">
+      <c r="D66" s="22">
         <v>135491559</v>
       </c>
       <c r="E66" s="17">
         <v>3450153388</v>
       </c>
-      <c r="F66" s="71" t="s">
+      <c r="F66" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="G66" s="72" t="s">
+      <c r="G66" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H66" s="12" t="s">
@@ -3154,16 +3475,16 @@
       <c r="C67" s="25">
         <v>45992</v>
       </c>
-      <c r="D67" s="75">
+      <c r="D67" s="22">
         <v>135491650</v>
       </c>
       <c r="E67" s="17">
         <v>3450153311</v>
       </c>
-      <c r="F67" s="71" t="s">
+      <c r="F67" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="G67" s="72" t="s">
+      <c r="G67" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H67" s="12" t="s">
@@ -3183,16 +3504,16 @@
       <c r="C68" s="25">
         <v>45992</v>
       </c>
-      <c r="D68" s="75">
+      <c r="D68" s="22">
         <v>135493212</v>
       </c>
       <c r="E68" s="17">
         <v>3450154972</v>
       </c>
-      <c r="F68" s="71" t="s">
+      <c r="F68" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="G68" s="72" t="s">
+      <c r="G68" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H68" s="12" t="s">
@@ -3212,16 +3533,16 @@
       <c r="C69" s="25">
         <v>45992</v>
       </c>
-      <c r="D69" s="75">
+      <c r="D69" s="22">
         <v>135495564</v>
       </c>
       <c r="E69" s="17">
         <v>3450155137</v>
       </c>
-      <c r="F69" s="71" t="s">
+      <c r="F69" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="G69" s="72" t="s">
+      <c r="G69" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H69" s="12" t="s">
@@ -3241,16 +3562,16 @@
       <c r="C70" s="25">
         <v>45992</v>
       </c>
-      <c r="D70" s="75">
+      <c r="D70" s="22">
         <v>135497503</v>
       </c>
       <c r="E70" s="17">
         <v>3450155445</v>
       </c>
-      <c r="F70" s="71" t="s">
+      <c r="F70" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="G70" s="72" t="s">
+      <c r="G70" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H70" s="12" t="s">
@@ -3270,16 +3591,16 @@
       <c r="C71" s="25">
         <v>45992</v>
       </c>
-      <c r="D71" s="75">
+      <c r="D71" s="22">
         <v>135500468</v>
       </c>
       <c r="E71" s="17">
         <v>3450155797</v>
       </c>
-      <c r="F71" s="71" t="s">
+      <c r="F71" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="G71" s="72" t="s">
+      <c r="G71" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H71" s="12" t="s">
@@ -3299,16 +3620,16 @@
       <c r="C72" s="25">
         <v>45992</v>
       </c>
-      <c r="D72" s="75">
+      <c r="D72" s="22">
         <v>135501247</v>
       </c>
       <c r="E72" s="17">
         <v>3450155863</v>
       </c>
-      <c r="F72" s="71" t="s">
+      <c r="F72" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="G72" s="72" t="s">
+      <c r="G72" s="61" t="s">
         <v>18</v>
       </c>
       <c r="H72" s="12" t="s">
@@ -3328,16 +3649,16 @@
       <c r="C73" s="25">
         <v>45992</v>
       </c>
-      <c r="D73" s="75">
+      <c r="D73" s="22">
         <v>135501543</v>
       </c>
       <c r="E73" s="17">
         <v>3450155907</v>
       </c>
-      <c r="F73" s="71" t="s">
+      <c r="F73" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="G73" s="72" t="s">
+      <c r="G73" s="61" t="s">
         <v>26</v>
       </c>
       <c r="H73" s="12" t="s">
@@ -3351,8 +3672,8 @@
       <c r="A74" s="6"/>
       <c r="B74" s="7"/>
       <c r="C74" s="25"/>
-      <c r="D74" s="74"/>
-      <c r="E74" s="57"/>
+      <c r="D74" s="63"/>
+      <c r="E74" s="50"/>
       <c r="F74" s="31"/>
       <c r="G74" s="42"/>
       <c r="H74" s="12"/>
@@ -3433,7 +3754,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFA17127-7620-4DD9-9061-6C654E2EC5C2}">
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -3441,469 +3762,1581 @@
     <col min="3" max="3" width="21.5703125" customWidth="1"/>
     <col min="4" max="4" width="27.7109375" style="16" customWidth="1"/>
     <col min="5" max="5" width="18.5703125" customWidth="1"/>
-    <col min="6" max="6" width="31.5703125" customWidth="1"/>
+    <col min="6" max="6" width="43.42578125" customWidth="1"/>
     <col min="7" max="7" width="19.7109375" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="8" max="8" width="27.28515625" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" style="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="52" t="s">
+      <c r="C1" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="53" t="s">
+      <c r="D1" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="53" t="s">
+      <c r="E1" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="51" t="s">
+      <c r="F1" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="51" t="s">
+      <c r="G1" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="54" t="s">
+      <c r="H1" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="51" t="s">
+      <c r="I1" s="66" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="59"/>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="44"/>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="44"/>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="44"/>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="44"/>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="56"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="44"/>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="56"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="44"/>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="56"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="44"/>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="56"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="44"/>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="56"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="44"/>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="56"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="44"/>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="56"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="44"/>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="56"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="44"/>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="56"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="44"/>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="56"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="44"/>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="56"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="44"/>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="56"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="44"/>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="56"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="44"/>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="56"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="44"/>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="56"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="44"/>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="56"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="44"/>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="56"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="44"/>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="56"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="42"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="44"/>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="56"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="42"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="44"/>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="56"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="44"/>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="56"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="44"/>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="56"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="42"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="44"/>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="56"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="42"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="44"/>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="A30" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B30" s="7"/>
-      <c r="C30" s="56"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="42"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="44"/>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B31" s="7"/>
-      <c r="C31" s="56"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="42"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="44"/>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="56"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="42"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="44"/>
-    </row>
-    <row r="33" spans="1:9">
-      <c r="A33" s="6"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="50"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="24"/>
+    <row r="2" spans="1:9" ht="15.75">
+      <c r="A2" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="71">
+        <v>46011</v>
+      </c>
+      <c r="C2" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D2" s="72" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="69">
+        <v>3450167468</v>
+      </c>
+      <c r="F2" s="73" t="s">
+        <v>112</v>
+      </c>
+      <c r="G2" s="70" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="73" t="s">
+        <v>113</v>
+      </c>
+      <c r="I2" s="71"/>
+    </row>
+    <row r="3" spans="1:9" ht="15.75">
+      <c r="A3" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="71">
+        <v>45986</v>
+      </c>
+      <c r="C3" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D3" s="72" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="69">
+        <v>3450158602</v>
+      </c>
+      <c r="F3" s="73" t="s">
+        <v>114</v>
+      </c>
+      <c r="G3" s="70" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="73" t="s">
+        <v>113</v>
+      </c>
+      <c r="I3" s="71"/>
+    </row>
+    <row r="4" spans="1:9" ht="15.75">
+      <c r="A4" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="71">
+        <v>45989</v>
+      </c>
+      <c r="C4" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D4" s="72">
+        <v>135472314</v>
+      </c>
+      <c r="E4" s="69">
+        <v>3450153410</v>
+      </c>
+      <c r="F4" s="73" t="s">
+        <v>115</v>
+      </c>
+      <c r="G4" s="70" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="74" t="s">
+        <v>116</v>
+      </c>
+      <c r="I4" s="71">
+        <v>45988</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15.75">
+      <c r="A5" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="71">
+        <v>45996</v>
+      </c>
+      <c r="C5" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D5" s="72">
+        <v>135476128</v>
+      </c>
+      <c r="E5" s="69">
+        <v>3450153861</v>
+      </c>
+      <c r="F5" s="73" t="s">
+        <v>117</v>
+      </c>
+      <c r="G5" s="70" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="74" t="s">
+        <v>118</v>
+      </c>
+      <c r="I5" s="71">
+        <v>45987</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15.75">
+      <c r="A6" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="71">
+        <v>45988</v>
+      </c>
+      <c r="C6" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D6" s="72">
+        <v>135474963</v>
+      </c>
+      <c r="E6" s="69">
+        <v>3450153729</v>
+      </c>
+      <c r="F6" s="73" t="s">
+        <v>119</v>
+      </c>
+      <c r="G6" s="70" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="74" t="s">
+        <v>120</v>
+      </c>
+      <c r="I6" s="71">
+        <v>45987</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15.75">
+      <c r="A7" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="71">
+        <v>45985</v>
+      </c>
+      <c r="C7" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D7" s="72">
+        <v>135522118</v>
+      </c>
+      <c r="E7" s="69">
+        <v>3450157634</v>
+      </c>
+      <c r="F7" s="73" t="s">
+        <v>121</v>
+      </c>
+      <c r="G7" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" s="74" t="s">
+        <v>122</v>
+      </c>
+      <c r="I7" s="71">
+        <v>45985</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15.75">
+      <c r="A8" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="71">
+        <v>45986</v>
+      </c>
+      <c r="C8" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D8" s="72">
+        <v>135533831</v>
+      </c>
+      <c r="E8" s="69">
+        <v>3450158536</v>
+      </c>
+      <c r="F8" s="73" t="s">
+        <v>123</v>
+      </c>
+      <c r="G8" s="70" t="s">
+        <v>75</v>
+      </c>
+      <c r="H8" s="74" t="s">
+        <v>124</v>
+      </c>
+      <c r="I8" s="71">
+        <v>45992</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15.75">
+      <c r="A9" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="71">
+        <v>45982</v>
+      </c>
+      <c r="C9" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D9" s="72">
+        <v>135538973</v>
+      </c>
+      <c r="E9" s="69">
+        <v>3450155423</v>
+      </c>
+      <c r="F9" s="73" t="s">
+        <v>125</v>
+      </c>
+      <c r="G9" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="74" t="s">
+        <v>126</v>
+      </c>
+      <c r="I9" s="71">
+        <v>45988</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15.75">
+      <c r="A10" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="71">
+        <v>45985</v>
+      </c>
+      <c r="C10" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D10" s="72">
+        <v>135517415</v>
+      </c>
+      <c r="E10" s="69">
+        <v>3450157140</v>
+      </c>
+      <c r="F10" s="73" t="s">
+        <v>127</v>
+      </c>
+      <c r="G10" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="74" t="s">
+        <v>128</v>
+      </c>
+      <c r="I10" s="71">
+        <v>45985</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="15.75">
+      <c r="A11" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="71">
+        <v>45986</v>
+      </c>
+      <c r="C11" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D11" s="72">
+        <v>135547880</v>
+      </c>
+      <c r="E11" s="69">
+        <v>3450159955</v>
+      </c>
+      <c r="F11" s="73" t="s">
+        <v>129</v>
+      </c>
+      <c r="G11" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" s="74" t="s">
+        <v>130</v>
+      </c>
+      <c r="I11" s="71">
+        <v>45986</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15.75">
+      <c r="A12" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="71">
+        <v>45985</v>
+      </c>
+      <c r="C12" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D12" s="72">
+        <v>135559942</v>
+      </c>
+      <c r="E12" s="69">
+        <v>3450157073</v>
+      </c>
+      <c r="F12" s="73" t="s">
+        <v>131</v>
+      </c>
+      <c r="G12" s="70" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" s="74" t="s">
+        <v>19</v>
+      </c>
+      <c r="I12" s="71">
+        <v>45985</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="15.75">
+      <c r="A13" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="71">
+        <v>45987</v>
+      </c>
+      <c r="C13" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D13" s="72">
+        <v>135567017</v>
+      </c>
+      <c r="E13" s="69">
+        <v>3450161924</v>
+      </c>
+      <c r="F13" s="73" t="s">
+        <v>132</v>
+      </c>
+      <c r="G13" s="70" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="74" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="71">
+        <v>46017</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15.75">
+      <c r="A14" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="71">
+        <v>45988</v>
+      </c>
+      <c r="C14" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D14" s="72">
+        <v>135573429</v>
+      </c>
+      <c r="E14" s="69">
+        <v>3450162232</v>
+      </c>
+      <c r="F14" s="73" t="s">
+        <v>133</v>
+      </c>
+      <c r="G14" s="70" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="74" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="71">
+        <v>45988</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15.75">
+      <c r="A15" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="71">
+        <v>45987</v>
+      </c>
+      <c r="C15" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D15" s="72">
+        <v>135555249</v>
+      </c>
+      <c r="E15" s="69">
+        <v>3450160329</v>
+      </c>
+      <c r="F15" s="73" t="s">
+        <v>134</v>
+      </c>
+      <c r="G15" s="70" t="s">
+        <v>75</v>
+      </c>
+      <c r="H15" s="74" t="s">
+        <v>124</v>
+      </c>
+      <c r="I15" s="71">
+        <v>45992</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="15.75">
+      <c r="A16" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="71">
+        <v>45987</v>
+      </c>
+      <c r="C16" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D16" s="72">
+        <v>135559287</v>
+      </c>
+      <c r="E16" s="69">
+        <v>3450160967</v>
+      </c>
+      <c r="F16" s="73" t="s">
+        <v>135</v>
+      </c>
+      <c r="G16" s="70" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="74" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="71">
+        <v>45987</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="15.75">
+      <c r="A17" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="71">
+        <v>45985</v>
+      </c>
+      <c r="C17" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D17" s="72">
+        <v>135579972</v>
+      </c>
+      <c r="E17" s="69">
+        <v>3450158162</v>
+      </c>
+      <c r="F17" s="73" t="s">
+        <v>136</v>
+      </c>
+      <c r="G17" s="70" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" s="74" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="71">
+        <v>45985</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15.75">
+      <c r="A18" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="71">
+        <v>45987</v>
+      </c>
+      <c r="C18" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D18" s="72">
+        <v>135583928</v>
+      </c>
+      <c r="E18" s="69">
+        <v>3450161451</v>
+      </c>
+      <c r="F18" s="73" t="s">
+        <v>137</v>
+      </c>
+      <c r="G18" s="70" t="s">
+        <v>34</v>
+      </c>
+      <c r="H18" s="74" t="s">
+        <v>138</v>
+      </c>
+      <c r="I18" s="71">
+        <v>45993</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15.75">
+      <c r="A19" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="71">
+        <v>45988</v>
+      </c>
+      <c r="C19" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D19" s="72">
+        <v>135578989</v>
+      </c>
+      <c r="E19" s="69">
+        <v>3450162826</v>
+      </c>
+      <c r="F19" s="73" t="s">
+        <v>139</v>
+      </c>
+      <c r="G19" s="70" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19" s="74" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="71">
+        <v>45988</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15.75">
+      <c r="A20" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="71">
+        <v>45988</v>
+      </c>
+      <c r="C20" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D20" s="72">
+        <v>135606960</v>
+      </c>
+      <c r="E20" s="69">
+        <v>3450162727</v>
+      </c>
+      <c r="F20" s="73" t="s">
+        <v>140</v>
+      </c>
+      <c r="G20" s="70" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" s="74" t="s">
+        <v>19</v>
+      </c>
+      <c r="I20" s="71">
+        <v>45988</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="15.75">
+      <c r="A21" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="71">
+        <v>45986</v>
+      </c>
+      <c r="C21" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D21" s="72">
+        <v>135574132</v>
+      </c>
+      <c r="E21" s="69">
+        <v>3450159438</v>
+      </c>
+      <c r="F21" s="73" t="s">
+        <v>141</v>
+      </c>
+      <c r="G21" s="70" t="s">
+        <v>31</v>
+      </c>
+      <c r="H21" s="74" t="s">
+        <v>142</v>
+      </c>
+      <c r="I21" s="71">
+        <v>45986</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="15.75">
+      <c r="A22" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="71">
+        <v>45987</v>
+      </c>
+      <c r="C22" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D22" s="72">
+        <v>135552819</v>
+      </c>
+      <c r="E22" s="69">
+        <v>3450160098</v>
+      </c>
+      <c r="F22" s="73" t="s">
+        <v>143</v>
+      </c>
+      <c r="G22" s="70" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22" s="74" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="71">
+        <v>45987</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="15.75">
+      <c r="A23" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="71">
+        <v>46011</v>
+      </c>
+      <c r="C23" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D23" s="72">
+        <v>135622491</v>
+      </c>
+      <c r="E23" s="69">
+        <v>3450166434</v>
+      </c>
+      <c r="F23" s="73" t="s">
+        <v>144</v>
+      </c>
+      <c r="G23" s="70" t="s">
+        <v>31</v>
+      </c>
+      <c r="H23" s="74" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="71">
+        <v>46011</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="15.75">
+      <c r="A24" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="71">
+        <v>45992</v>
+      </c>
+      <c r="C24" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D24" s="72">
+        <v>135633604</v>
+      </c>
+      <c r="E24" s="69">
+        <v>3450168062</v>
+      </c>
+      <c r="F24" s="73" t="s">
+        <v>145</v>
+      </c>
+      <c r="G24" s="70" t="s">
+        <v>31</v>
+      </c>
+      <c r="H24" s="74" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" s="71">
+        <v>45992</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="15.75">
+      <c r="A25" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="71">
+        <v>45992</v>
+      </c>
+      <c r="C25" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D25" s="72">
+        <v>135636611</v>
+      </c>
+      <c r="E25" s="69">
+        <v>3450168293</v>
+      </c>
+      <c r="F25" s="73" t="s">
+        <v>146</v>
+      </c>
+      <c r="G25" s="70" t="s">
+        <v>31</v>
+      </c>
+      <c r="H25" s="74" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" s="71">
+        <v>45992</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="15.75">
+      <c r="A26" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="71">
+        <v>45992</v>
+      </c>
+      <c r="C26" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D26" s="72">
+        <v>135424805</v>
+      </c>
+      <c r="E26" s="69">
+        <v>3450148966</v>
+      </c>
+      <c r="F26" s="73" t="s">
+        <v>147</v>
+      </c>
+      <c r="G26" s="70" t="s">
+        <v>34</v>
+      </c>
+      <c r="H26" s="74" t="s">
+        <v>148</v>
+      </c>
+      <c r="I26" s="71">
+        <v>45985</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="15.75">
+      <c r="A27" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="71">
+        <v>46009</v>
+      </c>
+      <c r="C27" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D27" s="72">
+        <v>135461082</v>
+      </c>
+      <c r="E27" s="69">
+        <v>3450152134</v>
+      </c>
+      <c r="F27" s="73" t="s">
+        <v>149</v>
+      </c>
+      <c r="G27" s="70" t="s">
+        <v>34</v>
+      </c>
+      <c r="H27" s="74" t="s">
+        <v>150</v>
+      </c>
+      <c r="I27" s="71">
+        <v>45988</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="15.75">
+      <c r="A28" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="71">
+        <v>45980</v>
+      </c>
+      <c r="C28" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D28" s="72">
+        <v>135467713</v>
+      </c>
+      <c r="E28" s="69">
+        <v>3450152981</v>
+      </c>
+      <c r="F28" s="73" t="s">
+        <v>151</v>
+      </c>
+      <c r="G28" s="70" t="s">
+        <v>63</v>
+      </c>
+      <c r="H28" s="74" t="s">
+        <v>152</v>
+      </c>
+      <c r="I28" s="71">
+        <v>45988</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="15.75">
+      <c r="A29" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="71">
+        <v>45980</v>
+      </c>
+      <c r="C29" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D29" s="72">
+        <v>135476188</v>
+      </c>
+      <c r="E29" s="69">
+        <v>3450153872</v>
+      </c>
+      <c r="F29" s="73" t="s">
+        <v>153</v>
+      </c>
+      <c r="G29" s="70" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" s="73" t="s">
+        <v>154</v>
+      </c>
+      <c r="I29" s="71">
+        <v>45980</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="15.75">
+      <c r="A30" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="71">
+        <v>45982</v>
+      </c>
+      <c r="C30" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D30" s="72">
+        <v>135551705</v>
+      </c>
+      <c r="E30" s="69">
+        <v>3450155247</v>
+      </c>
+      <c r="F30" s="73" t="s">
+        <v>155</v>
+      </c>
+      <c r="G30" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="H30" s="73" t="s">
+        <v>156</v>
+      </c>
+      <c r="I30" s="71">
+        <v>45982</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="15.75">
+      <c r="A31" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="71">
+        <v>45987</v>
+      </c>
+      <c r="C31" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D31" s="72">
+        <v>135558261</v>
+      </c>
+      <c r="E31" s="69">
+        <v>3450160769</v>
+      </c>
+      <c r="F31" s="73" t="s">
+        <v>157</v>
+      </c>
+      <c r="G31" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="H31" s="74" t="s">
+        <v>158</v>
+      </c>
+      <c r="I31" s="71">
+        <v>45987</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="15.75">
+      <c r="A32" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="71">
+        <v>45987</v>
+      </c>
+      <c r="C32" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D32" s="72">
+        <v>135561802</v>
+      </c>
+      <c r="E32" s="69">
+        <v>3450161385</v>
+      </c>
+      <c r="F32" s="73" t="s">
+        <v>159</v>
+      </c>
+      <c r="G32" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="H32" s="74" t="s">
+        <v>160</v>
+      </c>
+      <c r="I32" s="71">
+        <v>45987</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="15.75">
+      <c r="A33" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="71">
+        <v>45987</v>
+      </c>
+      <c r="C33" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D33" s="72">
+        <v>135565511</v>
+      </c>
+      <c r="E33" s="69">
+        <v>3450161781</v>
+      </c>
+      <c r="F33" s="73" t="s">
+        <v>161</v>
+      </c>
+      <c r="G33" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="H33" s="74" t="s">
+        <v>162</v>
+      </c>
+      <c r="I33" s="71">
+        <v>45987</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="15.75">
+      <c r="A34" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="71">
+        <v>45985</v>
+      </c>
+      <c r="C34" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D34" s="72">
+        <v>135521668</v>
+      </c>
+      <c r="E34" s="69">
+        <v>3450157579</v>
+      </c>
+      <c r="F34" s="73" t="s">
+        <v>163</v>
+      </c>
+      <c r="G34" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="H34" s="74" t="s">
+        <v>164</v>
+      </c>
+      <c r="I34" s="71">
+        <v>45985</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="15.75">
+      <c r="A35" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="71">
+        <v>45987</v>
+      </c>
+      <c r="C35" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D35" s="72">
+        <v>135567034</v>
+      </c>
+      <c r="E35" s="69">
+        <v>3450161935</v>
+      </c>
+      <c r="F35" s="73" t="s">
+        <v>165</v>
+      </c>
+      <c r="G35" s="70" t="s">
+        <v>31</v>
+      </c>
+      <c r="H35" s="74" t="s">
+        <v>32</v>
+      </c>
+      <c r="I35" s="71">
+        <v>45987</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="15.75">
+      <c r="A36" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" s="71">
+        <v>45985</v>
+      </c>
+      <c r="C36" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D36" s="72">
+        <v>135559199</v>
+      </c>
+      <c r="E36" s="69">
+        <v>3450157711</v>
+      </c>
+      <c r="F36" s="73" t="s">
+        <v>166</v>
+      </c>
+      <c r="G36" s="70" t="s">
+        <v>31</v>
+      </c>
+      <c r="H36" s="74" t="s">
+        <v>32</v>
+      </c>
+      <c r="I36" s="71">
+        <v>45985</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="15.75">
+      <c r="A37" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="71">
+        <v>45987</v>
+      </c>
+      <c r="C37" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D37" s="72">
+        <v>135556960</v>
+      </c>
+      <c r="E37" s="69">
+        <v>3450160549</v>
+      </c>
+      <c r="F37" s="73" t="s">
+        <v>167</v>
+      </c>
+      <c r="G37" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="H37" s="74" t="s">
+        <v>168</v>
+      </c>
+      <c r="I37" s="71">
+        <v>45987</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="15.75">
+      <c r="A38" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" s="71">
+        <v>45986</v>
+      </c>
+      <c r="C38" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D38" s="72">
+        <v>135547182</v>
+      </c>
+      <c r="E38" s="69">
+        <v>3450159780</v>
+      </c>
+      <c r="F38" s="73" t="s">
+        <v>169</v>
+      </c>
+      <c r="G38" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="H38" s="74" t="s">
+        <v>170</v>
+      </c>
+      <c r="I38" s="71">
+        <v>45986</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="15.75">
+      <c r="A39" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39" s="71">
+        <v>45986</v>
+      </c>
+      <c r="C39" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D39" s="72">
+        <v>135530271</v>
+      </c>
+      <c r="E39" s="69">
+        <v>3450158239</v>
+      </c>
+      <c r="F39" s="73" t="s">
+        <v>171</v>
+      </c>
+      <c r="G39" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="H39" s="74" t="s">
+        <v>172</v>
+      </c>
+      <c r="I39" s="71">
+        <v>45986</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="15.75">
+      <c r="A40" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" s="71">
+        <v>45985</v>
+      </c>
+      <c r="C40" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D40" s="72">
+        <v>135519157</v>
+      </c>
+      <c r="E40" s="69">
+        <v>3450157315</v>
+      </c>
+      <c r="F40" s="73" t="s">
+        <v>173</v>
+      </c>
+      <c r="G40" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="H40" s="74" t="s">
+        <v>174</v>
+      </c>
+      <c r="I40" s="71">
+        <v>45985</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="15.75">
+      <c r="A41" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" s="71">
+        <v>45987</v>
+      </c>
+      <c r="C41" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D41" s="72">
+        <v>135561675</v>
+      </c>
+      <c r="E41" s="69">
+        <v>3450161341</v>
+      </c>
+      <c r="F41" s="73" t="s">
+        <v>175</v>
+      </c>
+      <c r="G41" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="H41" s="74" t="s">
+        <v>176</v>
+      </c>
+      <c r="I41" s="71">
+        <v>45987</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="15.75">
+      <c r="A42" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" s="71">
+        <v>45985</v>
+      </c>
+      <c r="C42" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D42" s="72">
+        <v>135559785</v>
+      </c>
+      <c r="E42" s="69">
+        <v>3450157360</v>
+      </c>
+      <c r="F42" s="73" t="s">
+        <v>177</v>
+      </c>
+      <c r="G42" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="H42" s="74" t="s">
+        <v>178</v>
+      </c>
+      <c r="I42" s="71">
+        <v>45985</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="15.75">
+      <c r="A43" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B43" s="71">
+        <v>46010</v>
+      </c>
+      <c r="C43" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D43" s="72">
+        <v>135459425</v>
+      </c>
+      <c r="E43" s="69">
+        <v>3450151969</v>
+      </c>
+      <c r="F43" s="73" t="s">
+        <v>179</v>
+      </c>
+      <c r="G43" s="70" t="s">
+        <v>34</v>
+      </c>
+      <c r="H43" s="75" t="s">
+        <v>180</v>
+      </c>
+      <c r="I43" s="71">
+        <v>45980</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="15.75">
+      <c r="A44" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B44" s="71">
+        <v>45982</v>
+      </c>
+      <c r="C44" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D44" s="72">
+        <v>135462249</v>
+      </c>
+      <c r="E44" s="69">
+        <v>3450152277</v>
+      </c>
+      <c r="F44" s="73" t="s">
+        <v>181</v>
+      </c>
+      <c r="G44" s="70" t="s">
+        <v>63</v>
+      </c>
+      <c r="H44" s="75" t="s">
+        <v>182</v>
+      </c>
+      <c r="I44" s="71">
+        <v>45987</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="15.75">
+      <c r="A45" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B45" s="71">
+        <v>45990</v>
+      </c>
+      <c r="C45" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D45" s="72">
+        <v>135464234</v>
+      </c>
+      <c r="E45" s="69">
+        <v>3450152431</v>
+      </c>
+      <c r="F45" s="73" t="s">
+        <v>183</v>
+      </c>
+      <c r="G45" s="70" t="s">
+        <v>34</v>
+      </c>
+      <c r="H45" s="75" t="s">
+        <v>180</v>
+      </c>
+      <c r="I45" s="71">
+        <v>45990</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="15.75">
+      <c r="A46" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46" s="71">
+        <v>45996</v>
+      </c>
+      <c r="C46" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D46" s="72">
+        <v>135465443</v>
+      </c>
+      <c r="E46" s="69">
+        <v>3450152640</v>
+      </c>
+      <c r="F46" s="73" t="s">
+        <v>184</v>
+      </c>
+      <c r="G46" s="70" t="s">
+        <v>34</v>
+      </c>
+      <c r="H46" s="75" t="s">
+        <v>180</v>
+      </c>
+      <c r="I46" s="71">
+        <v>45988</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="15.75">
+      <c r="A47" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B47" s="71">
+        <v>46001</v>
+      </c>
+      <c r="C47" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D47" s="72">
+        <v>135467241</v>
+      </c>
+      <c r="E47" s="69">
+        <v>3450152915</v>
+      </c>
+      <c r="F47" s="73" t="s">
+        <v>185</v>
+      </c>
+      <c r="G47" s="70" t="s">
+        <v>34</v>
+      </c>
+      <c r="H47" s="75" t="s">
+        <v>186</v>
+      </c>
+      <c r="I47" s="71">
+        <v>46001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="15.75">
+      <c r="A48" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B48" s="71">
+        <v>45980</v>
+      </c>
+      <c r="C48" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D48" s="72">
+        <v>135468654</v>
+      </c>
+      <c r="E48" s="69">
+        <v>3450153091</v>
+      </c>
+      <c r="F48" s="73" t="s">
+        <v>187</v>
+      </c>
+      <c r="G48" s="70" t="s">
+        <v>34</v>
+      </c>
+      <c r="H48" s="75" t="s">
+        <v>188</v>
+      </c>
+      <c r="I48" s="71">
+        <v>45988</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="15.75">
+      <c r="A49" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49" s="71">
+        <v>45984</v>
+      </c>
+      <c r="C49" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D49" s="72">
+        <v>135471047</v>
+      </c>
+      <c r="E49" s="69">
+        <v>3450153289</v>
+      </c>
+      <c r="F49" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="G49" s="70" t="s">
+        <v>34</v>
+      </c>
+      <c r="H49" s="75" t="s">
+        <v>190</v>
+      </c>
+      <c r="I49" s="71">
+        <v>45988</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="15.75">
+      <c r="A50" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" s="77">
+        <v>46000</v>
+      </c>
+      <c r="C50" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D50" s="72">
+        <v>135471126</v>
+      </c>
+      <c r="E50" s="69">
+        <v>3450153290</v>
+      </c>
+      <c r="F50" s="73" t="s">
+        <v>191</v>
+      </c>
+      <c r="G50" s="76" t="s">
+        <v>34</v>
+      </c>
+      <c r="H50" s="75" t="s">
+        <v>192</v>
+      </c>
+      <c r="I50" s="71">
+        <v>45986</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="15.75">
+      <c r="A51" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B51" s="71">
+        <v>46006</v>
+      </c>
+      <c r="C51" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D51" s="72">
+        <v>135473171</v>
+      </c>
+      <c r="E51" s="69">
+        <v>3450153498</v>
+      </c>
+      <c r="F51" s="73" t="s">
+        <v>193</v>
+      </c>
+      <c r="G51" s="70" t="s">
+        <v>34</v>
+      </c>
+      <c r="H51" s="75" t="s">
+        <v>194</v>
+      </c>
+      <c r="I51" s="71">
+        <v>45988</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="15.75">
+      <c r="A52" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B52" s="71">
+        <v>45988</v>
+      </c>
+      <c r="C52" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D52" s="72">
+        <v>135474791</v>
+      </c>
+      <c r="E52" s="69">
+        <v>3450153685</v>
+      </c>
+      <c r="F52" s="73" t="s">
+        <v>195</v>
+      </c>
+      <c r="G52" s="70" t="s">
+        <v>34</v>
+      </c>
+      <c r="H52" s="75" t="s">
+        <v>180</v>
+      </c>
+      <c r="I52" s="71">
+        <v>45988</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="15.75">
+      <c r="A53" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B53" s="71">
+        <v>45996</v>
+      </c>
+      <c r="C53" s="71">
+        <v>45993</v>
+      </c>
+      <c r="D53" s="72">
+        <v>135475190</v>
+      </c>
+      <c r="E53" s="69">
+        <v>3450153762</v>
+      </c>
+      <c r="F53" s="73" t="s">
+        <v>117</v>
+      </c>
+      <c r="G53" s="70" t="s">
+        <v>34</v>
+      </c>
+      <c r="H53" s="75" t="s">
+        <v>196</v>
+      </c>
+      <c r="I53" s="71">
+        <v>45987</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="15.75">
+      <c r="A54" s="70"/>
+      <c r="B54" s="71"/>
+      <c r="C54" s="71"/>
+      <c r="D54" s="72"/>
+      <c r="E54" s="69"/>
+      <c r="F54" s="73"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="74"/>
+      <c r="I54" s="71"/>
+    </row>
+    <row r="55" spans="1:9" ht="15.75">
+      <c r="A55" s="70"/>
+      <c r="B55" s="69"/>
+      <c r="C55" s="71"/>
+      <c r="D55" s="69"/>
+      <c r="E55" s="69"/>
+      <c r="F55" s="74"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="74"/>
+      <c r="I55" s="71"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="3">
+    <cfRule type="notContainsBlanks" priority="5">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:F32">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  <conditionalFormatting sqref="D54:F54 D2:F2 F3 E5:E53">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A32" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A54" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G33" xr:uid="{5FAA0C61-6912-46B8-8149-B719594B77CB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G55" xr:uid="{5FAA0C61-6912-46B8-8149-B719594B77CB}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3959,20 +5392,20 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="61"/>
+      <c r="B2" s="51"/>
       <c r="C2" s="25"/>
       <c r="D2" s="26"/>
       <c r="E2" s="17"/>
       <c r="F2" s="11"/>
       <c r="G2" s="19"/>
-      <c r="H2" s="62"/>
+      <c r="H2" s="52"/>
       <c r="I2" s="44"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="61"/>
+      <c r="B3" s="51"/>
       <c r="C3" s="25"/>
       <c r="D3" s="26"/>
       <c r="E3" s="17"/>
@@ -4000,18 +5433,18 @@
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="25"/>
-      <c r="D5" s="64"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="68"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="58"/>
       <c r="I5" s="49"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="61"/>
+      <c r="B6" s="51"/>
       <c r="C6" s="25"/>
       <c r="D6" s="22"/>
       <c r="E6" s="17"/>
@@ -4024,7 +5457,7 @@
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="61"/>
+      <c r="B7" s="51"/>
       <c r="C7" s="25"/>
       <c r="D7" s="22"/>
       <c r="E7" s="17"/>
@@ -4037,7 +5470,7 @@
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="61"/>
+      <c r="B8" s="51"/>
       <c r="C8" s="25"/>
       <c r="D8" s="22"/>
       <c r="E8" s="17"/>
@@ -4050,7 +5483,7 @@
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="61"/>
+      <c r="B9" s="51"/>
       <c r="C9" s="25"/>
       <c r="D9" s="22"/>
       <c r="E9" s="17"/>
@@ -4063,12 +5496,12 @@
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="61"/>
+      <c r="B10" s="51"/>
       <c r="C10" s="25"/>
       <c r="D10" s="22"/>
       <c r="E10" s="17"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="63"/>
+      <c r="G10" s="53"/>
       <c r="H10" s="12"/>
       <c r="I10" s="44"/>
     </row>
@@ -4076,7 +5509,7 @@
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="61"/>
+      <c r="B11" s="51"/>
       <c r="C11" s="25"/>
       <c r="D11" s="22"/>
       <c r="E11" s="17"/>
@@ -4089,12 +5522,12 @@
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="61"/>
+      <c r="B12" s="51"/>
       <c r="C12" s="25"/>
       <c r="D12" s="22"/>
       <c r="E12" s="17"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="63"/>
+      <c r="G12" s="53"/>
       <c r="H12" s="12"/>
       <c r="I12" s="44"/>
     </row>
@@ -4102,7 +5535,7 @@
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="61"/>
+      <c r="B13" s="51"/>
       <c r="C13" s="25"/>
       <c r="D13" s="22"/>
       <c r="E13" s="17"/>
@@ -4115,7 +5548,7 @@
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="61"/>
+      <c r="B14" s="51"/>
       <c r="C14" s="25"/>
       <c r="D14" s="22"/>
       <c r="E14" s="17"/>
@@ -4128,12 +5561,12 @@
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="61"/>
+      <c r="B15" s="51"/>
       <c r="C15" s="25"/>
       <c r="D15" s="22"/>
       <c r="E15" s="17"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="63"/>
+      <c r="G15" s="53"/>
       <c r="H15" s="12"/>
       <c r="I15" s="44"/>
     </row>
@@ -4141,7 +5574,7 @@
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="61"/>
+      <c r="B16" s="51"/>
       <c r="C16" s="25"/>
       <c r="D16" s="22"/>
       <c r="E16" s="17"/>
@@ -4154,7 +5587,7 @@
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="61"/>
+      <c r="B17" s="51"/>
       <c r="C17" s="25"/>
       <c r="D17" s="22"/>
       <c r="E17" s="17"/>
@@ -4211,7 +5644,7 @@
       <c r="D21" s="22"/>
       <c r="E21" s="17"/>
       <c r="F21" s="11"/>
-      <c r="G21" s="63"/>
+      <c r="G21" s="53"/>
       <c r="H21" s="12"/>
       <c r="I21" s="44"/>
     </row>
@@ -4232,10 +5665,10 @@
       <c r="A23" s="6"/>
       <c r="B23" s="7"/>
       <c r="C23" s="25"/>
-      <c r="D23" s="69"/>
-      <c r="E23" s="57"/>
+      <c r="D23" s="59"/>
+      <c r="E23" s="50"/>
       <c r="F23" s="31"/>
-      <c r="G23" s="70"/>
+      <c r="G23" s="60"/>
       <c r="H23" s="14"/>
     </row>
     <row r="24" spans="1:9">
@@ -7508,6 +8941,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-531147</_dlc_DocId>
@@ -7550,68 +8992,9 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="cda820598d61c00a5299587a11c0dc14">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0803c1971eb453546b9f8a0aa56ab91b" ns1:_="" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="522e863aef51f288a2c445becadad51a">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e2cd90bc508d2ca63574b1ae88af87c9" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
     <xsd:import namespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea"/>
     <xsd:import namespace="ea6c6725-5210-4d6a-93cc-4cf85111ac5e"/>
@@ -7660,12 +9043,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Propriedades da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Ação de IU da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
@@ -7674,12 +9057,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Valor do ID do Documento" ma:description="O valor do ID do documento atribuído a este item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
+    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Document ID Value" ma:description="The value of the document ID assigned to this item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="ID do Documento" ma:description="Ligação permanente a este documento." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
+    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="Document ID" ma:description="Permanent link to this document." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:URL">
@@ -7762,7 +9145,7 @@
         <xsd:restriction base="dms:DateTime"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Partilhado Com" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -7781,7 +9164,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Detalhes de Partilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -7814,7 +9197,7 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de Imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -7897,8 +9280,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -7987,18 +9370,68 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED44BF61-13B5-4B27-80E4-AE5B5A73F019}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0425E3F9-9E3A-4146-959B-131D6BB5AEC9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
--- a/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 01.12.2025 a 08.12.2025.xlsx
+++ b/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 01.12.2025 a 08.12.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/shirlei_witkowski_allianz_com_br/Documents/E-MAILS Santander Recusa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{85757B70-77AD-4AC7-B8D6-F3264521EA3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBB59DD7-6DB2-4737-927B-497EF9F3BDCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01.12" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="237">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -696,6 +696,126 @@
 , de INCÊNDIO E BOUBO para COMPREENSIVA, ocorre a redução de 1 cla
 sse debônus, assim sendo o correto bônus 0.&lt;br&gt;Com a correção fico
 u 10x R$ 423,80. Podemos emitir desta forma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIMBO </t>
+  </si>
+  <si>
+    <t>RICARDO LEDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>Controller</t>
+  </si>
+  <si>
+    <t>COMERCIAL FERREIRA LINCON LTDA CNPJ: 062787123000171</t>
+  </si>
+  <si>
+    <t>NUP CANCELAMENTO 02/12/2025</t>
+  </si>
+  <si>
+    <t>SIRLEY CRUZ MARTINS CPF: 43154115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIEGO RODRIGO CORREA DE OLIVEIRA             </t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 02.12.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADAIR ALONSO                                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedido do segurado </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SILVIO CESAR FERRI                           </t>
+  </si>
+  <si>
+    <t>FRUSTRADO *PRAZO EXP * SEGURADO N CORRIGIU OS PASSOS SOLICITADOS repique: Porta malas obstruido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GILSON DO NASCIMENTO DANTAS                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROSELI SOTO VIEIRA                           </t>
+  </si>
+  <si>
+    <t>repique: Frente e lateral do passageiro, Traseira e lateral do motorista, Painel com carro desligado, Chassi, Frente e lateral do motorista, Motor e placa, Traseira e lateral do passageiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULO FRANCISCO DA SILVA                     </t>
+  </si>
+  <si>
+    <t>FRUSTRADO *PRAZO EXP * SEGURADO N CORRIGIU OS PASSOS SOLICITADOS repique: Frente e lateral do passageiro, Traseira e lateral do motorista, Frente e lateral do motorista, Traseira e lateral do passageiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HUGO GABRIEL DE CARVALHO ARAUJO              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGNALDO SECUNDO DA SILVA                     </t>
+  </si>
+  <si>
+    <t>FRUSTRADO *PRAZO EXP * SEGURADO N CORRIGIU OS PASSOS SOLICITADOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCISCO ANALIO DE ARAUJO                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRISCILA RAMOS ALVES                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SALON GROOMING RONY PETERSON LTDA ME         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GILBERTO XAVIER DE PONTES                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FERNANDO CESAR DE GRANDE                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDIMILSON SANTOS SILVA FILHO                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCINALVA SANTOS BORGES                      </t>
+  </si>
+  <si>
+    <t>FRUSTRADO *PRAZO EXP * SEGURADO N CORRIGIU OS PASSOS SOLICITADOS repique: Motor e placa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCISCO ELIDERMIR REZENDE DA SILVA         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HILDO JOSE DA SILVA                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRISLEY ROBERSON LEOCADIO ME                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIVEA MARIANA DIAS DA SILVA                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GERSON FARIAS DE ALBUQUERQUE                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCELO MOLINA DOS SANTOS                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">O PARAIBA MOVEIS OUTLET LTDA ME              </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: HODOMETRO (VEICULO DESLIGADO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WELBER TADEU ZANDONA                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOAO FRANCISCO BARBOSA                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANNY BEATRIZ SILVA SALES                     </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXP. FOTOS NÃO CORRIGIDAS: Painel com carro ligado (Veiculo desligado).</t>
   </si>
 </sst>
 </file>
@@ -752,7 +872,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -762,6 +882,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -942,17 +1068,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -998,12 +1113,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1054,9 +1178,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1132,7 +1253,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1143,23 +1263,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1191,12 +1302,35 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1593,10 +1727,10 @@
       <c r="B2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="25">
+      <c r="C2" s="24">
         <v>45992</v>
       </c>
-      <c r="D2" s="43" t="s">
+      <c r="D2" s="42" t="s">
         <v>11</v>
       </c>
       <c r="E2" s="17">
@@ -1605,13 +1739,13 @@
       <c r="F2" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="42" t="s">
+      <c r="G2" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="45" t="s">
+      <c r="H2" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="44"/>
+      <c r="I2" s="43"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
@@ -1620,10 +1754,10 @@
       <c r="B3" s="7">
         <v>45988</v>
       </c>
-      <c r="C3" s="25">
+      <c r="C3" s="24">
         <v>45992</v>
       </c>
-      <c r="D3" s="43" t="s">
+      <c r="D3" s="42" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="17">
@@ -1632,13 +1766,13 @@
       <c r="F3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="42" t="s">
+      <c r="G3" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="45" t="s">
+      <c r="H3" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="44"/>
+      <c r="I3" s="43"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
@@ -1647,25 +1781,25 @@
       <c r="B4" s="7">
         <v>45989</v>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="24">
         <v>45992</v>
       </c>
-      <c r="D4" s="62" t="s">
+      <c r="D4" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="55">
+      <c r="E4" s="53">
         <v>3450166159</v>
       </c>
-      <c r="F4" s="56" t="s">
+      <c r="F4" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="42" t="s">
+      <c r="G4" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="45" t="s">
+      <c r="H4" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="44"/>
+      <c r="I4" s="43"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
@@ -1674,10 +1808,10 @@
       <c r="B5" s="7">
         <v>45980</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="24">
         <v>45992</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="21">
         <v>135474140</v>
       </c>
       <c r="E5" s="17">
@@ -1686,13 +1820,13 @@
       <c r="F5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="61" t="s">
+      <c r="G5" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="45" t="s">
+      <c r="H5" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="44">
+      <c r="I5" s="43">
         <v>45980</v>
       </c>
     </row>
@@ -1703,10 +1837,10 @@
       <c r="B6" s="7">
         <v>45980</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="24">
         <v>45992</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="21">
         <v>135474812</v>
       </c>
       <c r="E6" s="17">
@@ -1715,13 +1849,13 @@
       <c r="F6" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="61" t="s">
+      <c r="G6" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="45" t="s">
+      <c r="H6" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="I6" s="44">
+      <c r="I6" s="43">
         <v>45980</v>
       </c>
     </row>
@@ -1732,10 +1866,10 @@
       <c r="B7" s="7">
         <v>45980</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="24">
         <v>45992</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="21">
         <v>135468066</v>
       </c>
       <c r="E7" s="17">
@@ -1744,13 +1878,13 @@
       <c r="F7" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="61" t="s">
+      <c r="G7" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="45" t="s">
+      <c r="H7" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="I7" s="44">
+      <c r="I7" s="43">
         <v>45980</v>
       </c>
     </row>
@@ -1761,10 +1895,10 @@
       <c r="B8" s="7">
         <v>45980</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="24">
         <v>45992</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="21">
         <v>135475160</v>
       </c>
       <c r="E8" s="17">
@@ -1773,13 +1907,13 @@
       <c r="F8" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="61" t="s">
+      <c r="G8" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="45" t="s">
+      <c r="H8" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="I8" s="44">
+      <c r="I8" s="43">
         <v>45980</v>
       </c>
     </row>
@@ -1790,10 +1924,10 @@
       <c r="B9" s="7">
         <v>45980</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="24">
         <v>45992</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="21">
         <v>135475293</v>
       </c>
       <c r="E9" s="17">
@@ -1802,13 +1936,13 @@
       <c r="F9" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="61" t="s">
+      <c r="G9" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="H9" s="45" t="s">
+      <c r="H9" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="I9" s="44">
+      <c r="I9" s="43">
         <v>45980</v>
       </c>
     </row>
@@ -1819,10 +1953,10 @@
       <c r="B10" s="7">
         <v>45980</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="24">
         <v>45992</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="21">
         <v>135479583</v>
       </c>
       <c r="E10" s="17">
@@ -1831,13 +1965,13 @@
       <c r="F10" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="61" t="s">
+      <c r="G10" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="H10" s="45" t="s">
+      <c r="H10" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="I10" s="44">
+      <c r="I10" s="43">
         <v>45980</v>
       </c>
     </row>
@@ -1848,10 +1982,10 @@
       <c r="B11" s="7">
         <v>45982</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="24">
         <v>45992</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="21">
         <v>135498971</v>
       </c>
       <c r="E11" s="17">
@@ -1860,13 +1994,13 @@
       <c r="F11" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="61" t="s">
+      <c r="G11" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="H11" s="45" t="s">
+      <c r="H11" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="I11" s="44">
+      <c r="I11" s="43">
         <v>45982</v>
       </c>
     </row>
@@ -1877,10 +2011,10 @@
       <c r="B12" s="7">
         <v>45982</v>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="24">
         <v>45992</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="21">
         <v>135493667</v>
       </c>
       <c r="E12" s="17">
@@ -1889,13 +2023,13 @@
       <c r="F12" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="G12" s="61" t="s">
+      <c r="G12" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="H12" s="45" t="s">
+      <c r="H12" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="I12" s="44">
+      <c r="I12" s="43">
         <v>45982</v>
       </c>
     </row>
@@ -1906,10 +2040,10 @@
       <c r="B13" s="7">
         <v>45985</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="24">
         <v>45992</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="21">
         <v>135514119</v>
       </c>
       <c r="E13" s="17">
@@ -1918,13 +2052,13 @@
       <c r="F13" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="G13" s="61" t="s">
+      <c r="G13" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="H13" s="45" t="s">
+      <c r="H13" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="I13" s="44">
+      <c r="I13" s="43">
         <v>45985</v>
       </c>
     </row>
@@ -1935,10 +2069,10 @@
       <c r="B14" s="7">
         <v>45985</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="24">
         <v>45992</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="21">
         <v>135512202</v>
       </c>
       <c r="E14" s="17">
@@ -1947,13 +2081,13 @@
       <c r="F14" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="G14" s="61" t="s">
+      <c r="G14" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="H14" s="45" t="s">
+      <c r="H14" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="I14" s="44">
+      <c r="I14" s="43">
         <v>45985</v>
       </c>
     </row>
@@ -1964,10 +2098,10 @@
       <c r="B15" s="7">
         <v>45990</v>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="24">
         <v>45992</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="21">
         <v>135522219</v>
       </c>
       <c r="E15" s="17">
@@ -1976,13 +2110,13 @@
       <c r="F15" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="G15" s="61" t="s">
+      <c r="G15" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="H15" s="45" t="s">
+      <c r="H15" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="I15" s="44">
+      <c r="I15" s="43">
         <v>45988</v>
       </c>
     </row>
@@ -1993,10 +2127,10 @@
       <c r="B16" s="7">
         <v>45985</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="24">
         <v>45992</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="21">
         <v>135523239</v>
       </c>
       <c r="E16" s="17">
@@ -2005,13 +2139,13 @@
       <c r="F16" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="G16" s="61" t="s">
+      <c r="G16" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="45" t="s">
+      <c r="H16" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="I16" s="44">
+      <c r="I16" s="43">
         <v>45985</v>
       </c>
     </row>
@@ -2022,10 +2156,10 @@
       <c r="B17" s="7">
         <v>45985</v>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="24">
         <v>45992</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="21">
         <v>135522967</v>
       </c>
       <c r="E17" s="17">
@@ -2034,13 +2168,13 @@
       <c r="F17" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="G17" s="61" t="s">
+      <c r="G17" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="H17" s="45" t="s">
+      <c r="H17" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="I17" s="44">
+      <c r="I17" s="43">
         <v>45985</v>
       </c>
     </row>
@@ -2051,10 +2185,10 @@
       <c r="B18" s="7">
         <v>45982</v>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="24">
         <v>45992</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="21">
         <v>135492497</v>
       </c>
       <c r="E18" s="17">
@@ -2063,13 +2197,13 @@
       <c r="F18" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="G18" s="61" t="s">
+      <c r="G18" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="H18" s="45" t="s">
+      <c r="H18" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="I18" s="44">
+      <c r="I18" s="43">
         <v>45982</v>
       </c>
     </row>
@@ -2080,10 +2214,10 @@
       <c r="B19" s="7">
         <v>45980</v>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="24">
         <v>45992</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="21">
         <v>135478449</v>
       </c>
       <c r="E19" s="17">
@@ -2092,13 +2226,13 @@
       <c r="F19" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="G19" s="61" t="s">
+      <c r="G19" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="H19" s="45" t="s">
+      <c r="H19" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="I19" s="44">
+      <c r="I19" s="43">
         <v>45980</v>
       </c>
     </row>
@@ -2109,10 +2243,10 @@
       <c r="B20" s="7">
         <v>45986</v>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="24">
         <v>45992</v>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="21">
         <v>135529810</v>
       </c>
       <c r="E20" s="17">
@@ -2121,13 +2255,13 @@
       <c r="F20" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="G20" s="61" t="s">
+      <c r="G20" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="H20" s="45" t="s">
+      <c r="H20" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="I20" s="44">
+      <c r="I20" s="43">
         <v>45986</v>
       </c>
     </row>
@@ -2138,10 +2272,10 @@
       <c r="B21" s="7">
         <v>45980</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="24">
         <v>45992</v>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="21">
         <v>135534132</v>
       </c>
       <c r="E21" s="17">
@@ -2150,13 +2284,13 @@
       <c r="F21" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="G21" s="61" t="s">
+      <c r="G21" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="H21" s="45" t="s">
+      <c r="H21" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="I21" s="44">
+      <c r="I21" s="43">
         <v>45980</v>
       </c>
     </row>
@@ -2167,10 +2301,10 @@
       <c r="B22" s="7">
         <v>45986</v>
       </c>
-      <c r="C22" s="25">
+      <c r="C22" s="24">
         <v>45992</v>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="21">
         <v>135544398</v>
       </c>
       <c r="E22" s="17">
@@ -2179,13 +2313,13 @@
       <c r="F22" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="G22" s="61" t="s">
+      <c r="G22" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="H22" s="45" t="s">
+      <c r="H22" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="I22" s="44">
+      <c r="I22" s="43">
         <v>45986</v>
       </c>
     </row>
@@ -2196,10 +2330,10 @@
       <c r="B23" s="7">
         <v>45986</v>
       </c>
-      <c r="C23" s="25">
+      <c r="C23" s="24">
         <v>45992</v>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="21">
         <v>135546544</v>
       </c>
       <c r="E23" s="17">
@@ -2208,13 +2342,13 @@
       <c r="F23" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="G23" s="61" t="s">
+      <c r="G23" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="H23" s="45" t="s">
+      <c r="H23" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="I23" s="44">
+      <c r="I23" s="43">
         <v>45986</v>
       </c>
     </row>
@@ -2225,10 +2359,10 @@
       <c r="B24" s="7">
         <v>45980</v>
       </c>
-      <c r="C24" s="25">
+      <c r="C24" s="24">
         <v>45992</v>
       </c>
-      <c r="D24" s="22">
+      <c r="D24" s="21">
         <v>135533868</v>
       </c>
       <c r="E24" s="17">
@@ -2237,13 +2371,13 @@
       <c r="F24" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="G24" s="61" t="s">
+      <c r="G24" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="H24" s="45" t="s">
+      <c r="H24" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="I24" s="44">
+      <c r="I24" s="43">
         <v>45980</v>
       </c>
     </row>
@@ -2254,10 +2388,10 @@
       <c r="B25" s="7">
         <v>45986</v>
       </c>
-      <c r="C25" s="25">
+      <c r="C25" s="24">
         <v>45992</v>
       </c>
-      <c r="D25" s="22">
+      <c r="D25" s="21">
         <v>135535321</v>
       </c>
       <c r="E25" s="17">
@@ -2266,13 +2400,13 @@
       <c r="F25" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="G25" s="61" t="s">
+      <c r="G25" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="H25" s="45" t="s">
+      <c r="H25" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="I25" s="44">
+      <c r="I25" s="43">
         <v>45986</v>
       </c>
     </row>
@@ -2283,10 +2417,10 @@
       <c r="B26" s="7">
         <v>45980</v>
       </c>
-      <c r="C26" s="25">
+      <c r="C26" s="24">
         <v>45992</v>
       </c>
-      <c r="D26" s="22">
+      <c r="D26" s="21">
         <v>135533044</v>
       </c>
       <c r="E26" s="17">
@@ -2295,13 +2429,13 @@
       <c r="F26" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="G26" s="61" t="s">
+      <c r="G26" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="H26" s="45" t="s">
+      <c r="H26" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="I26" s="44">
+      <c r="I26" s="43">
         <v>45980</v>
       </c>
     </row>
@@ -2312,10 +2446,10 @@
       <c r="B27" s="7">
         <v>45986</v>
       </c>
-      <c r="C27" s="25">
+      <c r="C27" s="24">
         <v>45992</v>
       </c>
-      <c r="D27" s="22">
+      <c r="D27" s="21">
         <v>135546431</v>
       </c>
       <c r="E27" s="17">
@@ -2324,13 +2458,13 @@
       <c r="F27" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="G27" s="61" t="s">
+      <c r="G27" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="H27" s="45" t="s">
+      <c r="H27" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="I27" s="44">
+      <c r="I27" s="43">
         <v>45986</v>
       </c>
     </row>
@@ -2341,10 +2475,10 @@
       <c r="B28" s="7">
         <v>45986</v>
       </c>
-      <c r="C28" s="25">
+      <c r="C28" s="24">
         <v>45992</v>
       </c>
-      <c r="D28" s="22">
+      <c r="D28" s="21">
         <v>135545842</v>
       </c>
       <c r="E28" s="17">
@@ -2353,13 +2487,13 @@
       <c r="F28" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="G28" s="61" t="s">
+      <c r="G28" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="H28" s="45" t="s">
+      <c r="H28" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="I28" s="44">
+      <c r="I28" s="43">
         <v>45986</v>
       </c>
     </row>
@@ -2370,10 +2504,10 @@
       <c r="B29" s="7">
         <v>45986</v>
       </c>
-      <c r="C29" s="25">
+      <c r="C29" s="24">
         <v>45992</v>
       </c>
-      <c r="D29" s="22">
+      <c r="D29" s="21">
         <v>135529148</v>
       </c>
       <c r="E29" s="17">
@@ -2382,13 +2516,13 @@
       <c r="F29" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G29" s="61" t="s">
+      <c r="G29" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="H29" s="45" t="s">
+      <c r="H29" s="44" t="s">
         <v>58</v>
       </c>
-      <c r="I29" s="44">
+      <c r="I29" s="43">
         <v>45986</v>
       </c>
     </row>
@@ -2399,10 +2533,10 @@
       <c r="B30" s="7">
         <v>45982</v>
       </c>
-      <c r="C30" s="25">
+      <c r="C30" s="24">
         <v>45992</v>
       </c>
-      <c r="D30" s="22">
+      <c r="D30" s="21">
         <v>135536166</v>
       </c>
       <c r="E30" s="17">
@@ -2411,13 +2545,13 @@
       <c r="F30" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="G30" s="61" t="s">
+      <c r="G30" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="H30" s="45" t="s">
+      <c r="H30" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="I30" s="44">
+      <c r="I30" s="43">
         <v>45982</v>
       </c>
     </row>
@@ -2428,10 +2562,10 @@
       <c r="B31" s="7">
         <v>45987</v>
       </c>
-      <c r="C31" s="25">
+      <c r="C31" s="24">
         <v>45992</v>
       </c>
-      <c r="D31" s="22">
+      <c r="D31" s="21">
         <v>135557269</v>
       </c>
       <c r="E31" s="17">
@@ -2440,13 +2574,13 @@
       <c r="F31" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="G31" s="61" t="s">
+      <c r="G31" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="H31" s="45" t="s">
+      <c r="H31" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="I31" s="44">
+      <c r="I31" s="43">
         <v>45987</v>
       </c>
     </row>
@@ -2457,10 +2591,10 @@
       <c r="B32" s="7">
         <v>45982</v>
       </c>
-      <c r="C32" s="25">
+      <c r="C32" s="24">
         <v>45992</v>
       </c>
-      <c r="D32" s="22">
+      <c r="D32" s="21">
         <v>135494206</v>
       </c>
       <c r="E32" s="17">
@@ -2469,13 +2603,13 @@
       <c r="F32" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="G32" s="61" t="s">
+      <c r="G32" s="56" t="s">
         <v>63</v>
       </c>
-      <c r="H32" s="45" t="s">
+      <c r="H32" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="I32" s="44">
+      <c r="I32" s="43">
         <v>45987</v>
       </c>
     </row>
@@ -2486,10 +2620,10 @@
       <c r="B33" s="7">
         <v>45980</v>
       </c>
-      <c r="C33" s="25">
+      <c r="C33" s="24">
         <v>45992</v>
       </c>
-      <c r="D33" s="22">
+      <c r="D33" s="21">
         <v>135460854</v>
       </c>
       <c r="E33" s="17">
@@ -2498,13 +2632,13 @@
       <c r="F33" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="G33" s="61" t="s">
+      <c r="G33" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="H33" s="45" t="s">
+      <c r="H33" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="I33" s="44">
+      <c r="I33" s="43">
         <v>45980</v>
       </c>
     </row>
@@ -2515,10 +2649,10 @@
       <c r="B34" s="7">
         <v>45982</v>
       </c>
-      <c r="C34" s="25">
+      <c r="C34" s="24">
         <v>45992</v>
       </c>
-      <c r="D34" s="22">
+      <c r="D34" s="21">
         <v>135485806</v>
       </c>
       <c r="E34" s="17">
@@ -2527,13 +2661,13 @@
       <c r="F34" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="G34" s="61" t="s">
+      <c r="G34" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="H34" s="45" t="s">
+      <c r="H34" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="I34" s="44">
+      <c r="I34" s="43">
         <v>45982</v>
       </c>
     </row>
@@ -2544,10 +2678,10 @@
       <c r="B35" s="7">
         <v>45987</v>
       </c>
-      <c r="C35" s="25">
+      <c r="C35" s="24">
         <v>45992</v>
       </c>
-      <c r="D35" s="22">
+      <c r="D35" s="21">
         <v>135560592</v>
       </c>
       <c r="E35" s="17">
@@ -2556,13 +2690,13 @@
       <c r="F35" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="G35" s="61" t="s">
+      <c r="G35" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="H35" s="45" t="s">
+      <c r="H35" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="I35" s="44">
+      <c r="I35" s="43">
         <v>45987</v>
       </c>
     </row>
@@ -2573,10 +2707,10 @@
       <c r="B36" s="7">
         <v>45988</v>
       </c>
-      <c r="C36" s="25">
+      <c r="C36" s="24">
         <v>45992</v>
       </c>
-      <c r="D36" s="22">
+      <c r="D36" s="21">
         <v>135579805</v>
       </c>
       <c r="E36" s="17">
@@ -2585,13 +2719,13 @@
       <c r="F36" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="G36" s="61" t="s">
+      <c r="G36" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="H36" s="45" t="s">
+      <c r="H36" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="I36" s="44">
+      <c r="I36" s="43">
         <v>45988</v>
       </c>
     </row>
@@ -2602,10 +2736,10 @@
       <c r="B37" s="7">
         <v>45987</v>
       </c>
-      <c r="C37" s="25">
+      <c r="C37" s="24">
         <v>45992</v>
       </c>
-      <c r="D37" s="22">
+      <c r="D37" s="21">
         <v>135581568</v>
       </c>
       <c r="E37" s="17">
@@ -2614,13 +2748,13 @@
       <c r="F37" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="G37" s="61" t="s">
+      <c r="G37" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="H37" s="45" t="s">
+      <c r="H37" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="I37" s="44">
+      <c r="I37" s="43">
         <v>45987</v>
       </c>
     </row>
@@ -2631,10 +2765,10 @@
       <c r="B38" s="7">
         <v>45988</v>
       </c>
-      <c r="C38" s="25">
+      <c r="C38" s="24">
         <v>45992</v>
       </c>
-      <c r="D38" s="22">
+      <c r="D38" s="21">
         <v>135574821</v>
       </c>
       <c r="E38" s="17">
@@ -2643,13 +2777,13 @@
       <c r="F38" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="G38" s="61" t="s">
+      <c r="G38" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="H38" s="45" t="s">
+      <c r="H38" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="I38" s="44">
+      <c r="I38" s="43">
         <v>45988</v>
       </c>
     </row>
@@ -2660,10 +2794,10 @@
       <c r="B39" s="7">
         <v>45985</v>
       </c>
-      <c r="C39" s="25">
+      <c r="C39" s="24">
         <v>45992</v>
       </c>
-      <c r="D39" s="22">
+      <c r="D39" s="21">
         <v>135555960</v>
       </c>
       <c r="E39" s="17">
@@ -2672,13 +2806,13 @@
       <c r="F39" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="G39" s="61" t="s">
+      <c r="G39" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="H39" s="45" t="s">
+      <c r="H39" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="I39" s="44">
+      <c r="I39" s="43">
         <v>45985</v>
       </c>
     </row>
@@ -2689,10 +2823,10 @@
       <c r="B40" s="7">
         <v>45986</v>
       </c>
-      <c r="C40" s="25">
+      <c r="C40" s="24">
         <v>45992</v>
       </c>
-      <c r="D40" s="22">
+      <c r="D40" s="21">
         <v>135547329</v>
       </c>
       <c r="E40" s="17">
@@ -2701,13 +2835,13 @@
       <c r="F40" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="G40" s="61" t="s">
+      <c r="G40" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="H40" s="45" t="s">
+      <c r="H40" s="44" t="s">
         <v>73</v>
       </c>
-      <c r="I40" s="44">
+      <c r="I40" s="43">
         <v>45986</v>
       </c>
     </row>
@@ -2718,10 +2852,10 @@
       <c r="B41" s="7">
         <v>45989</v>
       </c>
-      <c r="C41" s="25">
+      <c r="C41" s="24">
         <v>45992</v>
       </c>
-      <c r="D41" s="22">
+      <c r="D41" s="21">
         <v>135595402</v>
       </c>
       <c r="E41" s="17">
@@ -2730,13 +2864,13 @@
       <c r="F41" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="G41" s="61" t="s">
+      <c r="G41" s="56" t="s">
         <v>75</v>
       </c>
-      <c r="H41" s="45" t="s">
+      <c r="H41" s="44" t="s">
         <v>76</v>
       </c>
-      <c r="I41" s="64">
+      <c r="I41" s="59">
         <v>45992</v>
       </c>
     </row>
@@ -2747,10 +2881,10 @@
       <c r="B42" s="7">
         <v>45982</v>
       </c>
-      <c r="C42" s="25">
+      <c r="C42" s="24">
         <v>45992</v>
       </c>
-      <c r="D42" s="22">
+      <c r="D42" s="21">
         <v>135491263</v>
       </c>
       <c r="E42" s="17">
@@ -2759,13 +2893,13 @@
       <c r="F42" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="G42" s="61" t="s">
+      <c r="G42" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="H42" s="45" t="s">
+      <c r="H42" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="I42" s="44">
+      <c r="I42" s="43">
         <v>45982</v>
       </c>
     </row>
@@ -2776,10 +2910,10 @@
       <c r="B43" s="7">
         <v>45985</v>
       </c>
-      <c r="C43" s="25">
+      <c r="C43" s="24">
         <v>45992</v>
       </c>
-      <c r="D43" s="22">
+      <c r="D43" s="21">
         <v>135516843</v>
       </c>
       <c r="E43" s="17">
@@ -2788,13 +2922,13 @@
       <c r="F43" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="G43" s="61" t="s">
+      <c r="G43" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="H43" s="46" t="s">
+      <c r="H43" s="45" t="s">
         <v>79</v>
       </c>
-      <c r="I43" s="44">
+      <c r="I43" s="43">
         <v>45985</v>
       </c>
     </row>
@@ -2805,10 +2939,10 @@
       <c r="B44" s="7">
         <v>45980</v>
       </c>
-      <c r="C44" s="25">
+      <c r="C44" s="24">
         <v>45992</v>
       </c>
-      <c r="D44" s="22">
+      <c r="D44" s="21">
         <v>135472699</v>
       </c>
       <c r="E44" s="17">
@@ -2817,13 +2951,13 @@
       <c r="F44" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="G44" s="61" t="s">
+      <c r="G44" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="H44" s="46" t="s">
+      <c r="H44" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="I44" s="44">
+      <c r="I44" s="43">
         <v>45980</v>
       </c>
     </row>
@@ -2834,10 +2968,10 @@
       <c r="B45" s="7">
         <v>45980</v>
       </c>
-      <c r="C45" s="25">
+      <c r="C45" s="24">
         <v>45992</v>
       </c>
-      <c r="D45" s="22">
+      <c r="D45" s="21">
         <v>135461886</v>
       </c>
       <c r="E45" s="17">
@@ -2846,13 +2980,13 @@
       <c r="F45" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="G45" s="61" t="s">
+      <c r="G45" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="H45" s="45" t="s">
+      <c r="H45" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="I45" s="44">
+      <c r="I45" s="43">
         <v>45980</v>
       </c>
     </row>
@@ -2863,10 +2997,10 @@
       <c r="B46" s="7">
         <v>45992</v>
       </c>
-      <c r="C46" s="25">
+      <c r="C46" s="24">
         <v>45992</v>
       </c>
-      <c r="D46" s="22">
+      <c r="D46" s="21">
         <v>135632322</v>
       </c>
       <c r="E46" s="17">
@@ -2875,13 +3009,13 @@
       <c r="F46" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="G46" s="61" t="s">
+      <c r="G46" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="H46" s="45" t="s">
+      <c r="H46" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="I46" s="44">
+      <c r="I46" s="43">
         <v>45992</v>
       </c>
     </row>
@@ -2892,10 +3026,10 @@
       <c r="B47" s="7">
         <v>45980</v>
       </c>
-      <c r="C47" s="25">
+      <c r="C47" s="24">
         <v>45992</v>
       </c>
-      <c r="D47" s="22">
+      <c r="D47" s="21">
         <v>135458498</v>
       </c>
       <c r="E47" s="17">
@@ -2904,13 +3038,13 @@
       <c r="F47" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="G47" s="61" t="s">
+      <c r="G47" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="H47" s="45" t="s">
+      <c r="H47" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="I47" s="44">
+      <c r="I47" s="43">
         <v>45980</v>
       </c>
     </row>
@@ -2921,10 +3055,10 @@
       <c r="B48" s="7">
         <v>45980</v>
       </c>
-      <c r="C48" s="25">
+      <c r="C48" s="24">
         <v>45992</v>
       </c>
-      <c r="D48" s="22">
+      <c r="D48" s="21">
         <v>135491743</v>
       </c>
       <c r="E48" s="17">
@@ -2933,13 +3067,13 @@
       <c r="F48" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="G48" s="61" t="s">
+      <c r="G48" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="H48" s="45" t="s">
+      <c r="H48" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="I48" s="44">
+      <c r="I48" s="43">
         <v>45980</v>
       </c>
     </row>
@@ -2950,10 +3084,10 @@
       <c r="B49" s="7">
         <v>45980</v>
       </c>
-      <c r="C49" s="25">
+      <c r="C49" s="24">
         <v>45992</v>
       </c>
-      <c r="D49" s="22">
+      <c r="D49" s="21">
         <v>135464003</v>
       </c>
       <c r="E49" s="17">
@@ -2962,13 +3096,13 @@
       <c r="F49" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="G49" s="61" t="s">
+      <c r="G49" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="H49" s="45" t="s">
+      <c r="H49" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="I49" s="44">
+      <c r="I49" s="43">
         <v>45980</v>
       </c>
     </row>
@@ -2979,10 +3113,10 @@
       <c r="B50" s="7">
         <v>45979</v>
       </c>
-      <c r="C50" s="25">
+      <c r="C50" s="24">
         <v>45992</v>
       </c>
-      <c r="D50" s="22">
+      <c r="D50" s="21">
         <v>135464315</v>
       </c>
       <c r="E50" s="17">
@@ -2991,13 +3125,13 @@
       <c r="F50" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="G50" s="61" t="s">
+      <c r="G50" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="H50" s="45" t="s">
+      <c r="H50" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="I50" s="44">
+      <c r="I50" s="43">
         <v>45979</v>
       </c>
     </row>
@@ -3008,10 +3142,10 @@
       <c r="B51" s="7">
         <v>45975</v>
       </c>
-      <c r="C51" s="25">
+      <c r="C51" s="24">
         <v>45992</v>
       </c>
-      <c r="D51" s="22">
+      <c r="D51" s="21">
         <v>135465557</v>
       </c>
       <c r="E51" s="17">
@@ -3020,13 +3154,13 @@
       <c r="F51" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="G51" s="61" t="s">
+      <c r="G51" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="H51" s="45" t="s">
+      <c r="H51" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="I51" s="44">
+      <c r="I51" s="43">
         <v>45975</v>
       </c>
     </row>
@@ -3037,10 +3171,10 @@
       <c r="B52" s="7">
         <v>45980</v>
       </c>
-      <c r="C52" s="25">
+      <c r="C52" s="24">
         <v>45992</v>
       </c>
-      <c r="D52" s="22">
+      <c r="D52" s="21">
         <v>135467783</v>
       </c>
       <c r="E52" s="17">
@@ -3049,13 +3183,13 @@
       <c r="F52" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="G52" s="61" t="s">
+      <c r="G52" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="H52" s="45" t="s">
+      <c r="H52" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="I52" s="44">
+      <c r="I52" s="43">
         <v>45980</v>
       </c>
     </row>
@@ -3066,10 +3200,10 @@
       <c r="B53" s="7">
         <v>45980</v>
       </c>
-      <c r="C53" s="25">
+      <c r="C53" s="24">
         <v>45992</v>
       </c>
-      <c r="D53" s="22">
+      <c r="D53" s="21">
         <v>135468824</v>
       </c>
       <c r="E53" s="17">
@@ -3078,13 +3212,13 @@
       <c r="F53" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="G53" s="61" t="s">
+      <c r="G53" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="H53" s="45" t="s">
+      <c r="H53" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="I53" s="44">
+      <c r="I53" s="43">
         <v>45980</v>
       </c>
     </row>
@@ -3095,10 +3229,10 @@
       <c r="B54" s="7">
         <v>45980</v>
       </c>
-      <c r="C54" s="25">
+      <c r="C54" s="24">
         <v>45992</v>
       </c>
-      <c r="D54" s="22">
+      <c r="D54" s="21">
         <v>135469361</v>
       </c>
       <c r="E54" s="17">
@@ -3107,13 +3241,13 @@
       <c r="F54" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="G54" s="61" t="s">
+      <c r="G54" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="H54" s="45" t="s">
+      <c r="H54" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="I54" s="44">
+      <c r="I54" s="43">
         <v>45980</v>
       </c>
     </row>
@@ -3124,10 +3258,10 @@
       <c r="B55" s="7">
         <v>45980</v>
       </c>
-      <c r="C55" s="25">
+      <c r="C55" s="24">
         <v>45992</v>
       </c>
-      <c r="D55" s="22">
+      <c r="D55" s="21">
         <v>135474843</v>
       </c>
       <c r="E55" s="17">
@@ -3136,13 +3270,13 @@
       <c r="F55" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="G55" s="61" t="s">
+      <c r="G55" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="H55" s="45" t="s">
+      <c r="H55" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="I55" s="44">
+      <c r="I55" s="43">
         <v>45980</v>
       </c>
     </row>
@@ -3153,10 +3287,10 @@
       <c r="B56" s="7">
         <v>45980</v>
       </c>
-      <c r="C56" s="25">
+      <c r="C56" s="24">
         <v>45992</v>
       </c>
-      <c r="D56" s="22">
+      <c r="D56" s="21">
         <v>135475874</v>
       </c>
       <c r="E56" s="17">
@@ -3165,13 +3299,13 @@
       <c r="F56" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="G56" s="61" t="s">
+      <c r="G56" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="H56" s="45" t="s">
+      <c r="H56" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="I56" s="44">
+      <c r="I56" s="43">
         <v>45980</v>
       </c>
     </row>
@@ -3182,10 +3316,10 @@
       <c r="B57" s="7">
         <v>45980</v>
       </c>
-      <c r="C57" s="25">
+      <c r="C57" s="24">
         <v>45992</v>
       </c>
-      <c r="D57" s="22">
+      <c r="D57" s="21">
         <v>135476431</v>
       </c>
       <c r="E57" s="17">
@@ -3194,13 +3328,13 @@
       <c r="F57" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="G57" s="61" t="s">
+      <c r="G57" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="H57" s="45" t="s">
+      <c r="H57" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="I57" s="44">
+      <c r="I57" s="43">
         <v>45980</v>
       </c>
     </row>
@@ -3211,10 +3345,10 @@
       <c r="B58" s="7">
         <v>45980</v>
       </c>
-      <c r="C58" s="25">
+      <c r="C58" s="24">
         <v>45992</v>
       </c>
-      <c r="D58" s="22">
+      <c r="D58" s="21">
         <v>135477461</v>
       </c>
       <c r="E58" s="17">
@@ -3223,13 +3357,13 @@
       <c r="F58" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="G58" s="61" t="s">
+      <c r="G58" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="H58" s="45" t="s">
+      <c r="H58" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="I58" s="44">
+      <c r="I58" s="43">
         <v>45980</v>
       </c>
     </row>
@@ -3240,10 +3374,10 @@
       <c r="B59" s="7">
         <v>45982</v>
       </c>
-      <c r="C59" s="25">
+      <c r="C59" s="24">
         <v>45992</v>
       </c>
-      <c r="D59" s="22">
+      <c r="D59" s="21">
         <v>135485394</v>
       </c>
       <c r="E59" s="17">
@@ -3252,13 +3386,13 @@
       <c r="F59" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="G59" s="61" t="s">
+      <c r="G59" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="H59" s="45" t="s">
+      <c r="H59" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="I59" s="44">
+      <c r="I59" s="43">
         <v>45982</v>
       </c>
     </row>
@@ -3269,10 +3403,10 @@
       <c r="B60" s="7">
         <v>45979</v>
       </c>
-      <c r="C60" s="25">
+      <c r="C60" s="24">
         <v>45992</v>
       </c>
-      <c r="D60" s="22">
+      <c r="D60" s="21">
         <v>135488494</v>
       </c>
       <c r="E60" s="17">
@@ -3281,13 +3415,13 @@
       <c r="F60" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="G60" s="61" t="s">
+      <c r="G60" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="H60" s="45" t="s">
+      <c r="H60" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="I60" s="44">
+      <c r="I60" s="43">
         <v>45979</v>
       </c>
     </row>
@@ -3298,10 +3432,10 @@
       <c r="B61" s="7">
         <v>45982</v>
       </c>
-      <c r="C61" s="25">
+      <c r="C61" s="24">
         <v>45992</v>
       </c>
-      <c r="D61" s="22">
+      <c r="D61" s="21">
         <v>135490205</v>
       </c>
       <c r="E61" s="17">
@@ -3310,13 +3444,13 @@
       <c r="F61" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="G61" s="61" t="s">
+      <c r="G61" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="H61" s="45" t="s">
+      <c r="H61" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="I61" s="44">
+      <c r="I61" s="43">
         <v>45982</v>
       </c>
     </row>
@@ -3327,10 +3461,10 @@
       <c r="B62" s="7">
         <v>45980</v>
       </c>
-      <c r="C62" s="25">
+      <c r="C62" s="24">
         <v>45992</v>
       </c>
-      <c r="D62" s="22">
+      <c r="D62" s="21">
         <v>135491118</v>
       </c>
       <c r="E62" s="17">
@@ -3339,13 +3473,13 @@
       <c r="F62" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="G62" s="61" t="s">
+      <c r="G62" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="H62" s="45" t="s">
+      <c r="H62" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="I62" s="44">
+      <c r="I62" s="43">
         <v>45980</v>
       </c>
     </row>
@@ -3356,10 +3490,10 @@
       <c r="B63" s="7">
         <v>45982</v>
       </c>
-      <c r="C63" s="25">
+      <c r="C63" s="24">
         <v>45992</v>
       </c>
-      <c r="D63" s="22">
+      <c r="D63" s="21">
         <v>135491355</v>
       </c>
       <c r="E63" s="17">
@@ -3368,13 +3502,13 @@
       <c r="F63" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="G63" s="61" t="s">
+      <c r="G63" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="H63" s="45" t="s">
+      <c r="H63" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="I63" s="44">
+      <c r="I63" s="43">
         <v>45982</v>
       </c>
     </row>
@@ -3385,10 +3519,10 @@
       <c r="B64" s="7">
         <v>45982</v>
       </c>
-      <c r="C64" s="25">
+      <c r="C64" s="24">
         <v>45992</v>
       </c>
-      <c r="D64" s="22">
+      <c r="D64" s="21">
         <v>135491432</v>
       </c>
       <c r="E64" s="17">
@@ -3397,13 +3531,13 @@
       <c r="F64" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="G64" s="61" t="s">
+      <c r="G64" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="H64" s="45" t="s">
+      <c r="H64" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="I64" s="44">
+      <c r="I64" s="43">
         <v>45982</v>
       </c>
     </row>
@@ -3411,13 +3545,13 @@
       <c r="A65" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B65" s="47">
+      <c r="B65" s="46">
         <v>45980</v>
       </c>
-      <c r="C65" s="25">
+      <c r="C65" s="24">
         <v>45992</v>
       </c>
-      <c r="D65" s="22">
+      <c r="D65" s="21">
         <v>135491465</v>
       </c>
       <c r="E65" s="17">
@@ -3426,13 +3560,13 @@
       <c r="F65" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="G65" s="61" t="s">
+      <c r="G65" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="H65" s="45" t="s">
+      <c r="H65" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="I65" s="44">
+      <c r="I65" s="43">
         <v>45980</v>
       </c>
     </row>
@@ -3443,10 +3577,10 @@
       <c r="B66" s="7">
         <v>45980</v>
       </c>
-      <c r="C66" s="25">
+      <c r="C66" s="24">
         <v>45992</v>
       </c>
-      <c r="D66" s="22">
+      <c r="D66" s="21">
         <v>135491559</v>
       </c>
       <c r="E66" s="17">
@@ -3455,13 +3589,13 @@
       <c r="F66" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="G66" s="61" t="s">
+      <c r="G66" s="56" t="s">
         <v>18</v>
       </c>
       <c r="H66" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="I66" s="44">
+      <c r="I66" s="43">
         <v>45980</v>
       </c>
     </row>
@@ -3472,10 +3606,10 @@
       <c r="B67" s="7">
         <v>45980</v>
       </c>
-      <c r="C67" s="25">
+      <c r="C67" s="24">
         <v>45992</v>
       </c>
-      <c r="D67" s="22">
+      <c r="D67" s="21">
         <v>135491650</v>
       </c>
       <c r="E67" s="17">
@@ -3484,13 +3618,13 @@
       <c r="F67" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="G67" s="61" t="s">
+      <c r="G67" s="56" t="s">
         <v>18</v>
       </c>
       <c r="H67" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="I67" s="44">
+      <c r="I67" s="43">
         <v>45980</v>
       </c>
     </row>
@@ -3501,10 +3635,10 @@
       <c r="B68" s="7">
         <v>45982</v>
       </c>
-      <c r="C68" s="25">
+      <c r="C68" s="24">
         <v>45992</v>
       </c>
-      <c r="D68" s="22">
+      <c r="D68" s="21">
         <v>135493212</v>
       </c>
       <c r="E68" s="17">
@@ -3513,13 +3647,13 @@
       <c r="F68" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="G68" s="61" t="s">
+      <c r="G68" s="56" t="s">
         <v>18</v>
       </c>
       <c r="H68" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="I68" s="44">
+      <c r="I68" s="43">
         <v>45982</v>
       </c>
     </row>
@@ -3530,10 +3664,10 @@
       <c r="B69" s="7">
         <v>45982</v>
       </c>
-      <c r="C69" s="25">
+      <c r="C69" s="24">
         <v>45992</v>
       </c>
-      <c r="D69" s="22">
+      <c r="D69" s="21">
         <v>135495564</v>
       </c>
       <c r="E69" s="17">
@@ -3542,13 +3676,13 @@
       <c r="F69" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="G69" s="61" t="s">
+      <c r="G69" s="56" t="s">
         <v>18</v>
       </c>
       <c r="H69" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="I69" s="44">
+      <c r="I69" s="43">
         <v>45982</v>
       </c>
     </row>
@@ -3559,10 +3693,10 @@
       <c r="B70" s="7">
         <v>45982</v>
       </c>
-      <c r="C70" s="25">
+      <c r="C70" s="24">
         <v>45992</v>
       </c>
-      <c r="D70" s="22">
+      <c r="D70" s="21">
         <v>135497503</v>
       </c>
       <c r="E70" s="17">
@@ -3571,13 +3705,13 @@
       <c r="F70" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="G70" s="61" t="s">
+      <c r="G70" s="56" t="s">
         <v>18</v>
       </c>
       <c r="H70" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="I70" s="44">
+      <c r="I70" s="43">
         <v>45982</v>
       </c>
     </row>
@@ -3588,10 +3722,10 @@
       <c r="B71" s="7">
         <v>45982</v>
       </c>
-      <c r="C71" s="25">
+      <c r="C71" s="24">
         <v>45992</v>
       </c>
-      <c r="D71" s="22">
+      <c r="D71" s="21">
         <v>135500468</v>
       </c>
       <c r="E71" s="17">
@@ -3600,13 +3734,13 @@
       <c r="F71" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="G71" s="61" t="s">
+      <c r="G71" s="56" t="s">
         <v>18</v>
       </c>
       <c r="H71" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="I71" s="44">
+      <c r="I71" s="43">
         <v>45982</v>
       </c>
     </row>
@@ -3617,10 +3751,10 @@
       <c r="B72" s="7">
         <v>45982</v>
       </c>
-      <c r="C72" s="25">
+      <c r="C72" s="24">
         <v>45992</v>
       </c>
-      <c r="D72" s="22">
+      <c r="D72" s="21">
         <v>135501247</v>
       </c>
       <c r="E72" s="17">
@@ -3629,13 +3763,13 @@
       <c r="F72" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="G72" s="61" t="s">
+      <c r="G72" s="56" t="s">
         <v>18</v>
       </c>
       <c r="H72" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="I72" s="44">
+      <c r="I72" s="43">
         <v>45982</v>
       </c>
     </row>
@@ -3646,10 +3780,10 @@
       <c r="B73" s="7">
         <v>45982</v>
       </c>
-      <c r="C73" s="25">
+      <c r="C73" s="24">
         <v>45992</v>
       </c>
-      <c r="D73" s="22">
+      <c r="D73" s="21">
         <v>135501543</v>
       </c>
       <c r="E73" s="17">
@@ -3658,70 +3792,70 @@
       <c r="F73" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="G73" s="61" t="s">
+      <c r="G73" s="56" t="s">
         <v>26</v>
       </c>
       <c r="H73" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="I73" s="44">
+      <c r="I73" s="43">
         <v>45982</v>
       </c>
     </row>
     <row r="74" spans="1:9">
       <c r="A74" s="6"/>
       <c r="B74" s="7"/>
-      <c r="C74" s="25"/>
-      <c r="D74" s="63"/>
-      <c r="E74" s="50"/>
-      <c r="F74" s="31"/>
-      <c r="G74" s="42"/>
+      <c r="C74" s="24"/>
+      <c r="D74" s="58"/>
+      <c r="E74" s="49"/>
+      <c r="F74" s="30"/>
+      <c r="G74" s="41"/>
       <c r="H74" s="12"/>
-      <c r="I74" s="44"/>
+      <c r="I74" s="43"/>
     </row>
     <row r="75" spans="1:9">
       <c r="A75" s="6"/>
       <c r="B75" s="7"/>
-      <c r="C75" s="25"/>
-      <c r="D75" s="43"/>
+      <c r="C75" s="24"/>
+      <c r="D75" s="42"/>
       <c r="E75" s="17"/>
       <c r="F75" s="11"/>
-      <c r="G75" s="42"/>
+      <c r="G75" s="41"/>
       <c r="H75" s="12"/>
-      <c r="I75" s="44"/>
+      <c r="I75" s="43"/>
     </row>
     <row r="76" spans="1:9">
       <c r="A76" s="6"/>
       <c r="B76" s="7"/>
-      <c r="C76" s="25"/>
-      <c r="D76" s="43"/>
+      <c r="C76" s="24"/>
+      <c r="D76" s="42"/>
       <c r="E76" s="17"/>
       <c r="F76" s="11"/>
-      <c r="G76" s="42"/>
+      <c r="G76" s="41"/>
       <c r="H76" s="12"/>
-      <c r="I76" s="44"/>
+      <c r="I76" s="43"/>
     </row>
     <row r="77" spans="1:9">
       <c r="A77" s="6"/>
       <c r="B77" s="7"/>
-      <c r="C77" s="25"/>
-      <c r="D77" s="43"/>
+      <c r="C77" s="24"/>
+      <c r="D77" s="42"/>
       <c r="E77" s="17"/>
       <c r="F77" s="11"/>
-      <c r="G77" s="42"/>
+      <c r="G77" s="41"/>
       <c r="H77" s="12"/>
-      <c r="I77" s="44"/>
+      <c r="I77" s="43"/>
     </row>
     <row r="78" spans="1:9">
       <c r="A78" s="6"/>
       <c r="B78" s="7"/>
-      <c r="C78" s="25"/>
-      <c r="D78" s="43"/>
+      <c r="C78" s="24"/>
+      <c r="D78" s="42"/>
       <c r="E78" s="17"/>
       <c r="F78" s="11"/>
-      <c r="G78" s="42"/>
+      <c r="G78" s="41"/>
       <c r="H78" s="12"/>
-      <c r="I78" s="49"/>
+      <c r="I78" s="48"/>
     </row>
     <row r="79" spans="1:9">
       <c r="A79" s="6"/>
@@ -3731,7 +3865,7 @@
       <c r="E79" s="8"/>
       <c r="F79" s="9"/>
       <c r="G79" s="6"/>
-      <c r="H79" s="48"/>
+      <c r="H79" s="47"/>
       <c r="I79" s="12"/>
     </row>
   </sheetData>
@@ -3769,1559 +3903,1559 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="67" t="s">
+      <c r="B1" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="67" t="s">
+      <c r="C1" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="65" t="s">
+      <c r="D1" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="65" t="s">
+      <c r="E1" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="66" t="s">
+      <c r="F1" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="66" t="s">
+      <c r="G1" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="68" t="s">
+      <c r="H1" s="63" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="66" t="s">
+      <c r="I1" s="61" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15.75">
-      <c r="A2" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="71">
+      <c r="A2" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="66">
         <v>46011</v>
       </c>
-      <c r="C2" s="71">
+      <c r="C2" s="66">
         <v>45993</v>
       </c>
-      <c r="D2" s="72" t="s">
+      <c r="D2" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="69">
+      <c r="E2" s="64">
         <v>3450167468</v>
       </c>
-      <c r="F2" s="73" t="s">
+      <c r="F2" s="68" t="s">
         <v>112</v>
       </c>
-      <c r="G2" s="70" t="s">
+      <c r="G2" s="65" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="73" t="s">
+      <c r="H2" s="68" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="71"/>
+      <c r="I2" s="66"/>
     </row>
     <row r="3" spans="1:9" ht="15.75">
-      <c r="A3" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="71">
+      <c r="A3" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="66">
         <v>45986</v>
       </c>
-      <c r="C3" s="71">
+      <c r="C3" s="66">
         <v>45993</v>
       </c>
-      <c r="D3" s="72" t="s">
+      <c r="D3" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="69">
+      <c r="E3" s="64">
         <v>3450158602</v>
       </c>
-      <c r="F3" s="73" t="s">
+      <c r="F3" s="68" t="s">
         <v>114</v>
       </c>
-      <c r="G3" s="70" t="s">
+      <c r="G3" s="65" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="73" t="s">
+      <c r="H3" s="68" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="71"/>
+      <c r="I3" s="66"/>
     </row>
     <row r="4" spans="1:9" ht="15.75">
-      <c r="A4" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="71">
+      <c r="A4" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="66">
         <v>45989</v>
       </c>
-      <c r="C4" s="71">
+      <c r="C4" s="66">
         <v>45993</v>
       </c>
-      <c r="D4" s="72">
+      <c r="D4" s="67">
         <v>135472314</v>
       </c>
-      <c r="E4" s="69">
+      <c r="E4" s="64">
         <v>3450153410</v>
       </c>
-      <c r="F4" s="73" t="s">
+      <c r="F4" s="68" t="s">
         <v>115</v>
       </c>
-      <c r="G4" s="70" t="s">
+      <c r="G4" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="74" t="s">
+      <c r="H4" s="69" t="s">
         <v>116</v>
       </c>
-      <c r="I4" s="71">
+      <c r="I4" s="66">
         <v>45988</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75">
-      <c r="A5" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="71">
+      <c r="A5" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="66">
         <v>45996</v>
       </c>
-      <c r="C5" s="71">
+      <c r="C5" s="66">
         <v>45993</v>
       </c>
-      <c r="D5" s="72">
+      <c r="D5" s="67">
         <v>135476128</v>
       </c>
-      <c r="E5" s="69">
+      <c r="E5" s="64">
         <v>3450153861</v>
       </c>
-      <c r="F5" s="73" t="s">
+      <c r="F5" s="68" t="s">
         <v>117</v>
       </c>
-      <c r="G5" s="70" t="s">
+      <c r="G5" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="74" t="s">
+      <c r="H5" s="69" t="s">
         <v>118</v>
       </c>
-      <c r="I5" s="71">
+      <c r="I5" s="66">
         <v>45987</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75">
-      <c r="A6" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="71">
+      <c r="A6" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="66">
         <v>45988</v>
       </c>
-      <c r="C6" s="71">
+      <c r="C6" s="66">
         <v>45993</v>
       </c>
-      <c r="D6" s="72">
+      <c r="D6" s="67">
         <v>135474963</v>
       </c>
-      <c r="E6" s="69">
+      <c r="E6" s="64">
         <v>3450153729</v>
       </c>
-      <c r="F6" s="73" t="s">
+      <c r="F6" s="68" t="s">
         <v>119</v>
       </c>
-      <c r="G6" s="70" t="s">
+      <c r="G6" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="H6" s="74" t="s">
+      <c r="H6" s="69" t="s">
         <v>120</v>
       </c>
-      <c r="I6" s="71">
+      <c r="I6" s="66">
         <v>45987</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75">
-      <c r="A7" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="71">
+      <c r="A7" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="66">
         <v>45985</v>
       </c>
-      <c r="C7" s="71">
+      <c r="C7" s="66">
         <v>45993</v>
       </c>
-      <c r="D7" s="72">
+      <c r="D7" s="67">
         <v>135522118</v>
       </c>
-      <c r="E7" s="69">
+      <c r="E7" s="64">
         <v>3450157634</v>
       </c>
-      <c r="F7" s="73" t="s">
+      <c r="F7" s="68" t="s">
         <v>121</v>
       </c>
-      <c r="G7" s="70" t="s">
+      <c r="G7" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="H7" s="74" t="s">
+      <c r="H7" s="69" t="s">
         <v>122</v>
       </c>
-      <c r="I7" s="71">
+      <c r="I7" s="66">
         <v>45985</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.75">
-      <c r="A8" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="71">
+      <c r="A8" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="66">
         <v>45986</v>
       </c>
-      <c r="C8" s="71">
+      <c r="C8" s="66">
         <v>45993</v>
       </c>
-      <c r="D8" s="72">
+      <c r="D8" s="67">
         <v>135533831</v>
       </c>
-      <c r="E8" s="69">
+      <c r="E8" s="64">
         <v>3450158536</v>
       </c>
-      <c r="F8" s="73" t="s">
+      <c r="F8" s="68" t="s">
         <v>123</v>
       </c>
-      <c r="G8" s="70" t="s">
+      <c r="G8" s="65" t="s">
         <v>75</v>
       </c>
-      <c r="H8" s="74" t="s">
+      <c r="H8" s="69" t="s">
         <v>124</v>
       </c>
-      <c r="I8" s="71">
+      <c r="I8" s="66">
         <v>45992</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.75">
-      <c r="A9" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="71">
+      <c r="A9" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="66">
         <v>45982</v>
       </c>
-      <c r="C9" s="71">
+      <c r="C9" s="66">
         <v>45993</v>
       </c>
-      <c r="D9" s="72">
+      <c r="D9" s="67">
         <v>135538973</v>
       </c>
-      <c r="E9" s="69">
+      <c r="E9" s="64">
         <v>3450155423</v>
       </c>
-      <c r="F9" s="73" t="s">
+      <c r="F9" s="68" t="s">
         <v>125</v>
       </c>
-      <c r="G9" s="70" t="s">
+      <c r="G9" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="74" t="s">
+      <c r="H9" s="69" t="s">
         <v>126</v>
       </c>
-      <c r="I9" s="71">
+      <c r="I9" s="66">
         <v>45988</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75">
-      <c r="A10" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="71">
+      <c r="A10" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="66">
         <v>45985</v>
       </c>
-      <c r="C10" s="71">
+      <c r="C10" s="66">
         <v>45993</v>
       </c>
-      <c r="D10" s="72">
+      <c r="D10" s="67">
         <v>135517415</v>
       </c>
-      <c r="E10" s="69">
+      <c r="E10" s="64">
         <v>3450157140</v>
       </c>
-      <c r="F10" s="73" t="s">
+      <c r="F10" s="68" t="s">
         <v>127</v>
       </c>
-      <c r="G10" s="70" t="s">
+      <c r="G10" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="H10" s="74" t="s">
+      <c r="H10" s="69" t="s">
         <v>128</v>
       </c>
-      <c r="I10" s="71">
+      <c r="I10" s="66">
         <v>45985</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.75">
-      <c r="A11" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="71">
+      <c r="A11" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="66">
         <v>45986</v>
       </c>
-      <c r="C11" s="71">
+      <c r="C11" s="66">
         <v>45993</v>
       </c>
-      <c r="D11" s="72">
+      <c r="D11" s="67">
         <v>135547880</v>
       </c>
-      <c r="E11" s="69">
+      <c r="E11" s="64">
         <v>3450159955</v>
       </c>
-      <c r="F11" s="73" t="s">
+      <c r="F11" s="68" t="s">
         <v>129</v>
       </c>
-      <c r="G11" s="70" t="s">
+      <c r="G11" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="H11" s="74" t="s">
+      <c r="H11" s="69" t="s">
         <v>130</v>
       </c>
-      <c r="I11" s="71">
+      <c r="I11" s="66">
         <v>45986</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75">
-      <c r="A12" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="71">
+      <c r="A12" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="66">
         <v>45985</v>
       </c>
-      <c r="C12" s="71">
+      <c r="C12" s="66">
         <v>45993</v>
       </c>
-      <c r="D12" s="72">
+      <c r="D12" s="67">
         <v>135559942</v>
       </c>
-      <c r="E12" s="69">
+      <c r="E12" s="64">
         <v>3450157073</v>
       </c>
-      <c r="F12" s="73" t="s">
+      <c r="F12" s="68" t="s">
         <v>131</v>
       </c>
-      <c r="G12" s="70" t="s">
+      <c r="G12" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="H12" s="74" t="s">
+      <c r="H12" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="I12" s="71">
+      <c r="I12" s="66">
         <v>45985</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15.75">
-      <c r="A13" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="71">
+      <c r="A13" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="66">
         <v>45987</v>
       </c>
-      <c r="C13" s="71">
+      <c r="C13" s="66">
         <v>45993</v>
       </c>
-      <c r="D13" s="72">
+      <c r="D13" s="67">
         <v>135567017</v>
       </c>
-      <c r="E13" s="69">
+      <c r="E13" s="64">
         <v>3450161924</v>
       </c>
-      <c r="F13" s="73" t="s">
+      <c r="F13" s="68" t="s">
         <v>132</v>
       </c>
-      <c r="G13" s="70" t="s">
+      <c r="G13" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="H13" s="74" t="s">
+      <c r="H13" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="I13" s="71">
+      <c r="I13" s="66">
         <v>46017</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15.75">
-      <c r="A14" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="71">
+      <c r="A14" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="66">
         <v>45988</v>
       </c>
-      <c r="C14" s="71">
+      <c r="C14" s="66">
         <v>45993</v>
       </c>
-      <c r="D14" s="72">
+      <c r="D14" s="67">
         <v>135573429</v>
       </c>
-      <c r="E14" s="69">
+      <c r="E14" s="64">
         <v>3450162232</v>
       </c>
-      <c r="F14" s="73" t="s">
+      <c r="F14" s="68" t="s">
         <v>133</v>
       </c>
-      <c r="G14" s="70" t="s">
+      <c r="G14" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="H14" s="74" t="s">
+      <c r="H14" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="I14" s="71">
+      <c r="I14" s="66">
         <v>45988</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15.75">
-      <c r="A15" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="71">
+      <c r="A15" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="66">
         <v>45987</v>
       </c>
-      <c r="C15" s="71">
+      <c r="C15" s="66">
         <v>45993</v>
       </c>
-      <c r="D15" s="72">
+      <c r="D15" s="67">
         <v>135555249</v>
       </c>
-      <c r="E15" s="69">
+      <c r="E15" s="64">
         <v>3450160329</v>
       </c>
-      <c r="F15" s="73" t="s">
+      <c r="F15" s="68" t="s">
         <v>134</v>
       </c>
-      <c r="G15" s="70" t="s">
+      <c r="G15" s="65" t="s">
         <v>75</v>
       </c>
-      <c r="H15" s="74" t="s">
+      <c r="H15" s="69" t="s">
         <v>124</v>
       </c>
-      <c r="I15" s="71">
+      <c r="I15" s="66">
         <v>45992</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15.75">
-      <c r="A16" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="71">
+      <c r="A16" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="66">
         <v>45987</v>
       </c>
-      <c r="C16" s="71">
+      <c r="C16" s="66">
         <v>45993</v>
       </c>
-      <c r="D16" s="72">
+      <c r="D16" s="67">
         <v>135559287</v>
       </c>
-      <c r="E16" s="69">
+      <c r="E16" s="64">
         <v>3450160967</v>
       </c>
-      <c r="F16" s="73" t="s">
+      <c r="F16" s="68" t="s">
         <v>135</v>
       </c>
-      <c r="G16" s="70" t="s">
+      <c r="G16" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="74" t="s">
+      <c r="H16" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="I16" s="71">
+      <c r="I16" s="66">
         <v>45987</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15.75">
-      <c r="A17" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="71">
+      <c r="A17" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="66">
         <v>45985</v>
       </c>
-      <c r="C17" s="71">
+      <c r="C17" s="66">
         <v>45993</v>
       </c>
-      <c r="D17" s="72">
+      <c r="D17" s="67">
         <v>135579972</v>
       </c>
-      <c r="E17" s="69">
+      <c r="E17" s="64">
         <v>3450158162</v>
       </c>
-      <c r="F17" s="73" t="s">
+      <c r="F17" s="68" t="s">
         <v>136</v>
       </c>
-      <c r="G17" s="70" t="s">
+      <c r="G17" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="H17" s="74" t="s">
+      <c r="H17" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="I17" s="71">
+      <c r="I17" s="66">
         <v>45985</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15.75">
-      <c r="A18" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="71">
+      <c r="A18" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="66">
         <v>45987</v>
       </c>
-      <c r="C18" s="71">
+      <c r="C18" s="66">
         <v>45993</v>
       </c>
-      <c r="D18" s="72">
+      <c r="D18" s="67">
         <v>135583928</v>
       </c>
-      <c r="E18" s="69">
+      <c r="E18" s="64">
         <v>3450161451</v>
       </c>
-      <c r="F18" s="73" t="s">
+      <c r="F18" s="68" t="s">
         <v>137</v>
       </c>
-      <c r="G18" s="70" t="s">
+      <c r="G18" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="H18" s="74" t="s">
+      <c r="H18" s="69" t="s">
         <v>138</v>
       </c>
-      <c r="I18" s="71">
+      <c r="I18" s="66">
         <v>45993</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15.75">
-      <c r="A19" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="71">
+      <c r="A19" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="66">
         <v>45988</v>
       </c>
-      <c r="C19" s="71">
+      <c r="C19" s="66">
         <v>45993</v>
       </c>
-      <c r="D19" s="72">
+      <c r="D19" s="67">
         <v>135578989</v>
       </c>
-      <c r="E19" s="69">
+      <c r="E19" s="64">
         <v>3450162826</v>
       </c>
-      <c r="F19" s="73" t="s">
+      <c r="F19" s="68" t="s">
         <v>139</v>
       </c>
-      <c r="G19" s="70" t="s">
+      <c r="G19" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="H19" s="74" t="s">
+      <c r="H19" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="I19" s="71">
+      <c r="I19" s="66">
         <v>45988</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15.75">
-      <c r="A20" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="71">
+      <c r="A20" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="66">
         <v>45988</v>
       </c>
-      <c r="C20" s="71">
+      <c r="C20" s="66">
         <v>45993</v>
       </c>
-      <c r="D20" s="72">
+      <c r="D20" s="67">
         <v>135606960</v>
       </c>
-      <c r="E20" s="69">
+      <c r="E20" s="64">
         <v>3450162727</v>
       </c>
-      <c r="F20" s="73" t="s">
+      <c r="F20" s="68" t="s">
         <v>140</v>
       </c>
-      <c r="G20" s="70" t="s">
+      <c r="G20" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="H20" s="74" t="s">
+      <c r="H20" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="I20" s="71">
+      <c r="I20" s="66">
         <v>45988</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15.75">
-      <c r="A21" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B21" s="71">
+      <c r="A21" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="66">
         <v>45986</v>
       </c>
-      <c r="C21" s="71">
+      <c r="C21" s="66">
         <v>45993</v>
       </c>
-      <c r="D21" s="72">
+      <c r="D21" s="67">
         <v>135574132</v>
       </c>
-      <c r="E21" s="69">
+      <c r="E21" s="64">
         <v>3450159438</v>
       </c>
-      <c r="F21" s="73" t="s">
+      <c r="F21" s="68" t="s">
         <v>141</v>
       </c>
-      <c r="G21" s="70" t="s">
+      <c r="G21" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="H21" s="74" t="s">
+      <c r="H21" s="69" t="s">
         <v>142</v>
       </c>
-      <c r="I21" s="71">
+      <c r="I21" s="66">
         <v>45986</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15.75">
-      <c r="A22" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B22" s="71">
+      <c r="A22" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="66">
         <v>45987</v>
       </c>
-      <c r="C22" s="71">
+      <c r="C22" s="66">
         <v>45993</v>
       </c>
-      <c r="D22" s="72">
+      <c r="D22" s="67">
         <v>135552819</v>
       </c>
-      <c r="E22" s="69">
+      <c r="E22" s="64">
         <v>3450160098</v>
       </c>
-      <c r="F22" s="73" t="s">
+      <c r="F22" s="68" t="s">
         <v>143</v>
       </c>
-      <c r="G22" s="70" t="s">
+      <c r="G22" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="H22" s="74" t="s">
+      <c r="H22" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="I22" s="71">
+      <c r="I22" s="66">
         <v>45987</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15.75">
-      <c r="A23" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B23" s="71">
+      <c r="A23" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="66">
         <v>46011</v>
       </c>
-      <c r="C23" s="71">
+      <c r="C23" s="66">
         <v>45993</v>
       </c>
-      <c r="D23" s="72">
+      <c r="D23" s="67">
         <v>135622491</v>
       </c>
-      <c r="E23" s="69">
+      <c r="E23" s="64">
         <v>3450166434</v>
       </c>
-      <c r="F23" s="73" t="s">
+      <c r="F23" s="68" t="s">
         <v>144</v>
       </c>
-      <c r="G23" s="70" t="s">
+      <c r="G23" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="H23" s="74" t="s">
+      <c r="H23" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="I23" s="71">
+      <c r="I23" s="66">
         <v>46011</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15.75">
-      <c r="A24" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B24" s="71">
+      <c r="A24" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="66">
         <v>45992</v>
       </c>
-      <c r="C24" s="71">
+      <c r="C24" s="66">
         <v>45993</v>
       </c>
-      <c r="D24" s="72">
+      <c r="D24" s="67">
         <v>135633604</v>
       </c>
-      <c r="E24" s="69">
+      <c r="E24" s="64">
         <v>3450168062</v>
       </c>
-      <c r="F24" s="73" t="s">
+      <c r="F24" s="68" t="s">
         <v>145</v>
       </c>
-      <c r="G24" s="70" t="s">
+      <c r="G24" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="H24" s="74" t="s">
+      <c r="H24" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="I24" s="71">
+      <c r="I24" s="66">
         <v>45992</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15.75">
-      <c r="A25" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B25" s="71">
+      <c r="A25" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="66">
         <v>45992</v>
       </c>
-      <c r="C25" s="71">
+      <c r="C25" s="66">
         <v>45993</v>
       </c>
-      <c r="D25" s="72">
+      <c r="D25" s="67">
         <v>135636611</v>
       </c>
-      <c r="E25" s="69">
+      <c r="E25" s="64">
         <v>3450168293</v>
       </c>
-      <c r="F25" s="73" t="s">
+      <c r="F25" s="68" t="s">
         <v>146</v>
       </c>
-      <c r="G25" s="70" t="s">
+      <c r="G25" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="H25" s="74" t="s">
+      <c r="H25" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="I25" s="71">
+      <c r="I25" s="66">
         <v>45992</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15.75">
-      <c r="A26" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B26" s="71">
+      <c r="A26" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="66">
         <v>45992</v>
       </c>
-      <c r="C26" s="71">
+      <c r="C26" s="66">
         <v>45993</v>
       </c>
-      <c r="D26" s="72">
+      <c r="D26" s="67">
         <v>135424805</v>
       </c>
-      <c r="E26" s="69">
+      <c r="E26" s="64">
         <v>3450148966</v>
       </c>
-      <c r="F26" s="73" t="s">
+      <c r="F26" s="68" t="s">
         <v>147</v>
       </c>
-      <c r="G26" s="70" t="s">
+      <c r="G26" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="H26" s="74" t="s">
+      <c r="H26" s="69" t="s">
         <v>148</v>
       </c>
-      <c r="I26" s="71">
+      <c r="I26" s="66">
         <v>45985</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15.75">
-      <c r="A27" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B27" s="71">
+      <c r="A27" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="66">
         <v>46009</v>
       </c>
-      <c r="C27" s="71">
+      <c r="C27" s="66">
         <v>45993</v>
       </c>
-      <c r="D27" s="72">
+      <c r="D27" s="67">
         <v>135461082</v>
       </c>
-      <c r="E27" s="69">
+      <c r="E27" s="64">
         <v>3450152134</v>
       </c>
-      <c r="F27" s="73" t="s">
+      <c r="F27" s="68" t="s">
         <v>149</v>
       </c>
-      <c r="G27" s="70" t="s">
+      <c r="G27" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="H27" s="74" t="s">
+      <c r="H27" s="69" t="s">
         <v>150</v>
       </c>
-      <c r="I27" s="71">
+      <c r="I27" s="66">
         <v>45988</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15.75">
-      <c r="A28" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B28" s="71">
+      <c r="A28" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="66">
         <v>45980</v>
       </c>
-      <c r="C28" s="71">
+      <c r="C28" s="66">
         <v>45993</v>
       </c>
-      <c r="D28" s="72">
+      <c r="D28" s="67">
         <v>135467713</v>
       </c>
-      <c r="E28" s="69">
+      <c r="E28" s="64">
         <v>3450152981</v>
       </c>
-      <c r="F28" s="73" t="s">
+      <c r="F28" s="68" t="s">
         <v>151</v>
       </c>
-      <c r="G28" s="70" t="s">
+      <c r="G28" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="H28" s="74" t="s">
+      <c r="H28" s="69" t="s">
         <v>152</v>
       </c>
-      <c r="I28" s="71">
+      <c r="I28" s="66">
         <v>45988</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15.75">
-      <c r="A29" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B29" s="71">
+      <c r="A29" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="66">
         <v>45980</v>
       </c>
-      <c r="C29" s="71">
+      <c r="C29" s="66">
         <v>45993</v>
       </c>
-      <c r="D29" s="72">
+      <c r="D29" s="67">
         <v>135476188</v>
       </c>
-      <c r="E29" s="69">
+      <c r="E29" s="64">
         <v>3450153872</v>
       </c>
-      <c r="F29" s="73" t="s">
+      <c r="F29" s="68" t="s">
         <v>153</v>
       </c>
-      <c r="G29" s="70" t="s">
+      <c r="G29" s="65" t="s">
         <v>13</v>
       </c>
-      <c r="H29" s="73" t="s">
+      <c r="H29" s="68" t="s">
         <v>154</v>
       </c>
-      <c r="I29" s="71">
+      <c r="I29" s="66">
         <v>45980</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15.75">
-      <c r="A30" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B30" s="71">
+      <c r="A30" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="66">
         <v>45982</v>
       </c>
-      <c r="C30" s="71">
+      <c r="C30" s="66">
         <v>45993</v>
       </c>
-      <c r="D30" s="72">
+      <c r="D30" s="67">
         <v>135551705</v>
       </c>
-      <c r="E30" s="69">
+      <c r="E30" s="64">
         <v>3450155247</v>
       </c>
-      <c r="F30" s="73" t="s">
+      <c r="F30" s="68" t="s">
         <v>155</v>
       </c>
-      <c r="G30" s="70" t="s">
+      <c r="G30" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="H30" s="73" t="s">
+      <c r="H30" s="68" t="s">
         <v>156</v>
       </c>
-      <c r="I30" s="71">
+      <c r="I30" s="66">
         <v>45982</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15.75">
-      <c r="A31" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B31" s="71">
+      <c r="A31" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="66">
         <v>45987</v>
       </c>
-      <c r="C31" s="71">
+      <c r="C31" s="66">
         <v>45993</v>
       </c>
-      <c r="D31" s="72">
+      <c r="D31" s="67">
         <v>135558261</v>
       </c>
-      <c r="E31" s="69">
+      <c r="E31" s="64">
         <v>3450160769</v>
       </c>
-      <c r="F31" s="73" t="s">
+      <c r="F31" s="68" t="s">
         <v>157</v>
       </c>
-      <c r="G31" s="70" t="s">
+      <c r="G31" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="H31" s="74" t="s">
+      <c r="H31" s="69" t="s">
         <v>158</v>
       </c>
-      <c r="I31" s="71">
+      <c r="I31" s="66">
         <v>45987</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15.75">
-      <c r="A32" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B32" s="71">
+      <c r="A32" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="66">
         <v>45987</v>
       </c>
-      <c r="C32" s="71">
+      <c r="C32" s="66">
         <v>45993</v>
       </c>
-      <c r="D32" s="72">
+      <c r="D32" s="67">
         <v>135561802</v>
       </c>
-      <c r="E32" s="69">
+      <c r="E32" s="64">
         <v>3450161385</v>
       </c>
-      <c r="F32" s="73" t="s">
+      <c r="F32" s="68" t="s">
         <v>159</v>
       </c>
-      <c r="G32" s="70" t="s">
+      <c r="G32" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="H32" s="74" t="s">
+      <c r="H32" s="69" t="s">
         <v>160</v>
       </c>
-      <c r="I32" s="71">
+      <c r="I32" s="66">
         <v>45987</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15.75">
-      <c r="A33" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B33" s="71">
+      <c r="A33" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="66">
         <v>45987</v>
       </c>
-      <c r="C33" s="71">
+      <c r="C33" s="66">
         <v>45993</v>
       </c>
-      <c r="D33" s="72">
+      <c r="D33" s="67">
         <v>135565511</v>
       </c>
-      <c r="E33" s="69">
+      <c r="E33" s="64">
         <v>3450161781</v>
       </c>
-      <c r="F33" s="73" t="s">
+      <c r="F33" s="68" t="s">
         <v>161</v>
       </c>
-      <c r="G33" s="70" t="s">
+      <c r="G33" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="H33" s="74" t="s">
+      <c r="H33" s="69" t="s">
         <v>162</v>
       </c>
-      <c r="I33" s="71">
+      <c r="I33" s="66">
         <v>45987</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="15.75">
-      <c r="A34" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B34" s="71">
+      <c r="A34" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="66">
         <v>45985</v>
       </c>
-      <c r="C34" s="71">
+      <c r="C34" s="66">
         <v>45993</v>
       </c>
-      <c r="D34" s="72">
+      <c r="D34" s="67">
         <v>135521668</v>
       </c>
-      <c r="E34" s="69">
+      <c r="E34" s="64">
         <v>3450157579</v>
       </c>
-      <c r="F34" s="73" t="s">
+      <c r="F34" s="68" t="s">
         <v>163</v>
       </c>
-      <c r="G34" s="70" t="s">
+      <c r="G34" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="H34" s="74" t="s">
+      <c r="H34" s="69" t="s">
         <v>164</v>
       </c>
-      <c r="I34" s="71">
+      <c r="I34" s="66">
         <v>45985</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15.75">
-      <c r="A35" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B35" s="71">
+      <c r="A35" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="66">
         <v>45987</v>
       </c>
-      <c r="C35" s="71">
+      <c r="C35" s="66">
         <v>45993</v>
       </c>
-      <c r="D35" s="72">
+      <c r="D35" s="67">
         <v>135567034</v>
       </c>
-      <c r="E35" s="69">
+      <c r="E35" s="64">
         <v>3450161935</v>
       </c>
-      <c r="F35" s="73" t="s">
+      <c r="F35" s="68" t="s">
         <v>165</v>
       </c>
-      <c r="G35" s="70" t="s">
+      <c r="G35" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="H35" s="74" t="s">
+      <c r="H35" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="I35" s="71">
+      <c r="I35" s="66">
         <v>45987</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="15.75">
-      <c r="A36" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B36" s="71">
+      <c r="A36" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" s="66">
         <v>45985</v>
       </c>
-      <c r="C36" s="71">
+      <c r="C36" s="66">
         <v>45993</v>
       </c>
-      <c r="D36" s="72">
+      <c r="D36" s="67">
         <v>135559199</v>
       </c>
-      <c r="E36" s="69">
+      <c r="E36" s="64">
         <v>3450157711</v>
       </c>
-      <c r="F36" s="73" t="s">
+      <c r="F36" s="68" t="s">
         <v>166</v>
       </c>
-      <c r="G36" s="70" t="s">
+      <c r="G36" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="H36" s="74" t="s">
+      <c r="H36" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="I36" s="71">
+      <c r="I36" s="66">
         <v>45985</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15.75">
-      <c r="A37" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B37" s="71">
+      <c r="A37" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="66">
         <v>45987</v>
       </c>
-      <c r="C37" s="71">
+      <c r="C37" s="66">
         <v>45993</v>
       </c>
-      <c r="D37" s="72">
+      <c r="D37" s="67">
         <v>135556960</v>
       </c>
-      <c r="E37" s="69">
+      <c r="E37" s="64">
         <v>3450160549</v>
       </c>
-      <c r="F37" s="73" t="s">
+      <c r="F37" s="68" t="s">
         <v>167</v>
       </c>
-      <c r="G37" s="70" t="s">
+      <c r="G37" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="H37" s="74" t="s">
+      <c r="H37" s="69" t="s">
         <v>168</v>
       </c>
-      <c r="I37" s="71">
+      <c r="I37" s="66">
         <v>45987</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15.75">
-      <c r="A38" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B38" s="71">
+      <c r="A38" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" s="66">
         <v>45986</v>
       </c>
-      <c r="C38" s="71">
+      <c r="C38" s="66">
         <v>45993</v>
       </c>
-      <c r="D38" s="72">
+      <c r="D38" s="67">
         <v>135547182</v>
       </c>
-      <c r="E38" s="69">
+      <c r="E38" s="64">
         <v>3450159780</v>
       </c>
-      <c r="F38" s="73" t="s">
+      <c r="F38" s="68" t="s">
         <v>169</v>
       </c>
-      <c r="G38" s="70" t="s">
+      <c r="G38" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="H38" s="74" t="s">
+      <c r="H38" s="69" t="s">
         <v>170</v>
       </c>
-      <c r="I38" s="71">
+      <c r="I38" s="66">
         <v>45986</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="15.75">
-      <c r="A39" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B39" s="71">
+      <c r="A39" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39" s="66">
         <v>45986</v>
       </c>
-      <c r="C39" s="71">
+      <c r="C39" s="66">
         <v>45993</v>
       </c>
-      <c r="D39" s="72">
+      <c r="D39" s="67">
         <v>135530271</v>
       </c>
-      <c r="E39" s="69">
+      <c r="E39" s="64">
         <v>3450158239</v>
       </c>
-      <c r="F39" s="73" t="s">
+      <c r="F39" s="68" t="s">
         <v>171</v>
       </c>
-      <c r="G39" s="70" t="s">
+      <c r="G39" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="H39" s="74" t="s">
+      <c r="H39" s="69" t="s">
         <v>172</v>
       </c>
-      <c r="I39" s="71">
+      <c r="I39" s="66">
         <v>45986</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15.75">
-      <c r="A40" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B40" s="71">
+      <c r="A40" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" s="66">
         <v>45985</v>
       </c>
-      <c r="C40" s="71">
+      <c r="C40" s="66">
         <v>45993</v>
       </c>
-      <c r="D40" s="72">
+      <c r="D40" s="67">
         <v>135519157</v>
       </c>
-      <c r="E40" s="69">
+      <c r="E40" s="64">
         <v>3450157315</v>
       </c>
-      <c r="F40" s="73" t="s">
+      <c r="F40" s="68" t="s">
         <v>173</v>
       </c>
-      <c r="G40" s="70" t="s">
+      <c r="G40" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="H40" s="74" t="s">
+      <c r="H40" s="69" t="s">
         <v>174</v>
       </c>
-      <c r="I40" s="71">
+      <c r="I40" s="66">
         <v>45985</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="15.75">
-      <c r="A41" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B41" s="71">
+      <c r="A41" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" s="66">
         <v>45987</v>
       </c>
-      <c r="C41" s="71">
+      <c r="C41" s="66">
         <v>45993</v>
       </c>
-      <c r="D41" s="72">
+      <c r="D41" s="67">
         <v>135561675</v>
       </c>
-      <c r="E41" s="69">
+      <c r="E41" s="64">
         <v>3450161341</v>
       </c>
-      <c r="F41" s="73" t="s">
+      <c r="F41" s="68" t="s">
         <v>175</v>
       </c>
-      <c r="G41" s="70" t="s">
+      <c r="G41" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="H41" s="74" t="s">
+      <c r="H41" s="69" t="s">
         <v>176</v>
       </c>
-      <c r="I41" s="71">
+      <c r="I41" s="66">
         <v>45987</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="15.75">
-      <c r="A42" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B42" s="71">
+      <c r="A42" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" s="66">
         <v>45985</v>
       </c>
-      <c r="C42" s="71">
+      <c r="C42" s="66">
         <v>45993</v>
       </c>
-      <c r="D42" s="72">
+      <c r="D42" s="67">
         <v>135559785</v>
       </c>
-      <c r="E42" s="69">
+      <c r="E42" s="64">
         <v>3450157360</v>
       </c>
-      <c r="F42" s="73" t="s">
+      <c r="F42" s="68" t="s">
         <v>177</v>
       </c>
-      <c r="G42" s="70" t="s">
+      <c r="G42" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="H42" s="74" t="s">
+      <c r="H42" s="69" t="s">
         <v>178</v>
       </c>
-      <c r="I42" s="71">
+      <c r="I42" s="66">
         <v>45985</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15.75">
-      <c r="A43" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B43" s="71">
+      <c r="A43" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B43" s="66">
         <v>46010</v>
       </c>
-      <c r="C43" s="71">
+      <c r="C43" s="66">
         <v>45993</v>
       </c>
-      <c r="D43" s="72">
+      <c r="D43" s="67">
         <v>135459425</v>
       </c>
-      <c r="E43" s="69">
+      <c r="E43" s="64">
         <v>3450151969</v>
       </c>
-      <c r="F43" s="73" t="s">
+      <c r="F43" s="68" t="s">
         <v>179</v>
       </c>
-      <c r="G43" s="70" t="s">
+      <c r="G43" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="H43" s="75" t="s">
+      <c r="H43" s="69" t="s">
         <v>180</v>
       </c>
-      <c r="I43" s="71">
+      <c r="I43" s="66">
         <v>45980</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15.75">
-      <c r="A44" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B44" s="71">
+      <c r="A44" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B44" s="66">
         <v>45982</v>
       </c>
-      <c r="C44" s="71">
+      <c r="C44" s="66">
         <v>45993</v>
       </c>
-      <c r="D44" s="72">
+      <c r="D44" s="67">
         <v>135462249</v>
       </c>
-      <c r="E44" s="69">
+      <c r="E44" s="64">
         <v>3450152277</v>
       </c>
-      <c r="F44" s="73" t="s">
+      <c r="F44" s="68" t="s">
         <v>181</v>
       </c>
-      <c r="G44" s="70" t="s">
+      <c r="G44" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="H44" s="75" t="s">
+      <c r="H44" s="69" t="s">
         <v>182</v>
       </c>
-      <c r="I44" s="71">
+      <c r="I44" s="66">
         <v>45987</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="15.75">
-      <c r="A45" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B45" s="71">
+      <c r="A45" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B45" s="66">
         <v>45990</v>
       </c>
-      <c r="C45" s="71">
+      <c r="C45" s="66">
         <v>45993</v>
       </c>
-      <c r="D45" s="72">
+      <c r="D45" s="67">
         <v>135464234</v>
       </c>
-      <c r="E45" s="69">
+      <c r="E45" s="64">
         <v>3450152431</v>
       </c>
-      <c r="F45" s="73" t="s">
+      <c r="F45" s="68" t="s">
         <v>183</v>
       </c>
-      <c r="G45" s="70" t="s">
+      <c r="G45" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="H45" s="75" t="s">
+      <c r="H45" s="69" t="s">
         <v>180</v>
       </c>
-      <c r="I45" s="71">
+      <c r="I45" s="66">
         <v>45990</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="15.75">
-      <c r="A46" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B46" s="71">
+      <c r="A46" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46" s="66">
         <v>45996</v>
       </c>
-      <c r="C46" s="71">
+      <c r="C46" s="66">
         <v>45993</v>
       </c>
-      <c r="D46" s="72">
+      <c r="D46" s="67">
         <v>135465443</v>
       </c>
-      <c r="E46" s="69">
+      <c r="E46" s="64">
         <v>3450152640</v>
       </c>
-      <c r="F46" s="73" t="s">
+      <c r="F46" s="68" t="s">
         <v>184</v>
       </c>
-      <c r="G46" s="70" t="s">
+      <c r="G46" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="H46" s="75" t="s">
+      <c r="H46" s="69" t="s">
         <v>180</v>
       </c>
-      <c r="I46" s="71">
+      <c r="I46" s="66">
         <v>45988</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15.75">
-      <c r="A47" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B47" s="71">
+      <c r="A47" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B47" s="66">
         <v>46001</v>
       </c>
-      <c r="C47" s="71">
+      <c r="C47" s="66">
         <v>45993</v>
       </c>
-      <c r="D47" s="72">
+      <c r="D47" s="67">
         <v>135467241</v>
       </c>
-      <c r="E47" s="69">
+      <c r="E47" s="64">
         <v>3450152915</v>
       </c>
-      <c r="F47" s="73" t="s">
+      <c r="F47" s="68" t="s">
         <v>185</v>
       </c>
-      <c r="G47" s="70" t="s">
+      <c r="G47" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="H47" s="75" t="s">
+      <c r="H47" s="69" t="s">
         <v>186</v>
       </c>
-      <c r="I47" s="71">
+      <c r="I47" s="66">
         <v>46001</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15.75">
-      <c r="A48" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B48" s="71">
+      <c r="A48" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B48" s="66">
         <v>45980</v>
       </c>
-      <c r="C48" s="71">
+      <c r="C48" s="66">
         <v>45993</v>
       </c>
-      <c r="D48" s="72">
+      <c r="D48" s="67">
         <v>135468654</v>
       </c>
-      <c r="E48" s="69">
+      <c r="E48" s="64">
         <v>3450153091</v>
       </c>
-      <c r="F48" s="73" t="s">
+      <c r="F48" s="68" t="s">
         <v>187</v>
       </c>
-      <c r="G48" s="70" t="s">
+      <c r="G48" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="H48" s="75" t="s">
+      <c r="H48" s="69" t="s">
         <v>188</v>
       </c>
-      <c r="I48" s="71">
+      <c r="I48" s="66">
         <v>45988</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15.75">
-      <c r="A49" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B49" s="71">
+      <c r="A49" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49" s="66">
         <v>45984</v>
       </c>
-      <c r="C49" s="71">
+      <c r="C49" s="66">
         <v>45993</v>
       </c>
-      <c r="D49" s="72">
+      <c r="D49" s="67">
         <v>135471047</v>
       </c>
-      <c r="E49" s="69">
+      <c r="E49" s="64">
         <v>3450153289</v>
       </c>
-      <c r="F49" s="73" t="s">
+      <c r="F49" s="68" t="s">
         <v>189</v>
       </c>
-      <c r="G49" s="70" t="s">
+      <c r="G49" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="H49" s="75" t="s">
+      <c r="H49" s="69" t="s">
         <v>190</v>
       </c>
-      <c r="I49" s="71">
+      <c r="I49" s="66">
         <v>45988</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15.75">
-      <c r="A50" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B50" s="77">
+      <c r="A50" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" s="71">
         <v>46000</v>
       </c>
-      <c r="C50" s="71">
+      <c r="C50" s="66">
         <v>45993</v>
       </c>
-      <c r="D50" s="72">
+      <c r="D50" s="67">
         <v>135471126</v>
       </c>
-      <c r="E50" s="69">
+      <c r="E50" s="64">
         <v>3450153290</v>
       </c>
-      <c r="F50" s="73" t="s">
+      <c r="F50" s="68" t="s">
         <v>191</v>
       </c>
-      <c r="G50" s="76" t="s">
+      <c r="G50" s="70" t="s">
         <v>34</v>
       </c>
-      <c r="H50" s="75" t="s">
+      <c r="H50" s="69" t="s">
         <v>192</v>
       </c>
-      <c r="I50" s="71">
+      <c r="I50" s="66">
         <v>45986</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15.75">
-      <c r="A51" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B51" s="71">
+      <c r="A51" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B51" s="66">
         <v>46006</v>
       </c>
-      <c r="C51" s="71">
+      <c r="C51" s="66">
         <v>45993</v>
       </c>
-      <c r="D51" s="72">
+      <c r="D51" s="67">
         <v>135473171</v>
       </c>
-      <c r="E51" s="69">
+      <c r="E51" s="64">
         <v>3450153498</v>
       </c>
-      <c r="F51" s="73" t="s">
+      <c r="F51" s="68" t="s">
         <v>193</v>
       </c>
-      <c r="G51" s="70" t="s">
+      <c r="G51" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="H51" s="75" t="s">
+      <c r="H51" s="69" t="s">
         <v>194</v>
       </c>
-      <c r="I51" s="71">
+      <c r="I51" s="66">
         <v>45988</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15.75">
-      <c r="A52" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B52" s="71">
+      <c r="A52" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B52" s="66">
         <v>45988</v>
       </c>
-      <c r="C52" s="71">
+      <c r="C52" s="66">
         <v>45993</v>
       </c>
-      <c r="D52" s="72">
+      <c r="D52" s="67">
         <v>135474791</v>
       </c>
-      <c r="E52" s="69">
+      <c r="E52" s="64">
         <v>3450153685</v>
       </c>
-      <c r="F52" s="73" t="s">
+      <c r="F52" s="68" t="s">
         <v>195</v>
       </c>
-      <c r="G52" s="70" t="s">
+      <c r="G52" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="H52" s="75" t="s">
+      <c r="H52" s="69" t="s">
         <v>180</v>
       </c>
-      <c r="I52" s="71">
+      <c r="I52" s="66">
         <v>45988</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15.75">
-      <c r="A53" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B53" s="71">
+      <c r="A53" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B53" s="66">
         <v>45996</v>
       </c>
-      <c r="C53" s="71">
+      <c r="C53" s="66">
         <v>45993</v>
       </c>
-      <c r="D53" s="72">
+      <c r="D53" s="67">
         <v>135475190</v>
       </c>
-      <c r="E53" s="69">
+      <c r="E53" s="64">
         <v>3450153762</v>
       </c>
-      <c r="F53" s="73" t="s">
+      <c r="F53" s="68" t="s">
         <v>117</v>
       </c>
-      <c r="G53" s="70" t="s">
+      <c r="G53" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="H53" s="75" t="s">
+      <c r="H53" s="69" t="s">
         <v>196</v>
       </c>
-      <c r="I53" s="71">
+      <c r="I53" s="66">
         <v>45987</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15.75">
-      <c r="A54" s="70"/>
-      <c r="B54" s="71"/>
-      <c r="C54" s="71"/>
-      <c r="D54" s="72"/>
-      <c r="E54" s="69"/>
-      <c r="F54" s="73"/>
-      <c r="G54" s="70"/>
-      <c r="H54" s="74"/>
-      <c r="I54" s="71"/>
+      <c r="A54" s="65"/>
+      <c r="B54" s="66"/>
+      <c r="C54" s="66"/>
+      <c r="D54" s="67"/>
+      <c r="E54" s="64"/>
+      <c r="F54" s="68"/>
+      <c r="G54" s="65"/>
+      <c r="H54" s="69"/>
+      <c r="I54" s="66"/>
     </row>
     <row r="55" spans="1:9" ht="15.75">
-      <c r="A55" s="70"/>
-      <c r="B55" s="69"/>
-      <c r="C55" s="71"/>
-      <c r="D55" s="69"/>
-      <c r="E55" s="69"/>
-      <c r="F55" s="74"/>
-      <c r="G55" s="70"/>
-      <c r="H55" s="74"/>
-      <c r="I55" s="71"/>
+      <c r="A55" s="65"/>
+      <c r="B55" s="64"/>
+      <c r="C55" s="66"/>
+      <c r="D55" s="64"/>
+      <c r="E55" s="64"/>
+      <c r="F55" s="69"/>
+      <c r="G55" s="65"/>
+      <c r="H55" s="69"/>
+      <c r="I55" s="66"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
@@ -5346,7 +5480,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BD26F43-5C8A-4C67-93F6-3B4E17ED8491}">
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="15.85546875" style="16" customWidth="1"/>
@@ -5356,7 +5490,7 @@
     <col min="6" max="6" width="30.140625" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31.5703125" customWidth="1"/>
-    <col min="9" max="9" width="21" style="24" customWidth="1"/>
+    <col min="9" max="9" width="21" style="23" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -5384,7 +5518,7 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="28" t="s">
+      <c r="I1" s="27" t="s">
         <v>8</v>
       </c>
     </row>
@@ -5392,472 +5526,835 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="44"/>
+      <c r="B2" s="50">
+        <v>45999</v>
+      </c>
+      <c r="C2" s="24">
+        <v>45994</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="E2" s="17">
+        <v>3450159163</v>
+      </c>
+      <c r="F2" s="73" t="s">
+        <v>198</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="45" t="s">
+        <v>199</v>
+      </c>
+      <c r="I2" s="43"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="44"/>
+      <c r="B3" s="50">
+        <v>45989</v>
+      </c>
+      <c r="C3" s="24">
+        <v>45994</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="E3" s="72">
+        <v>3450166302</v>
+      </c>
+      <c r="F3" s="74" t="s">
+        <v>200</v>
+      </c>
+      <c r="G3" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="H3" s="45" t="s">
+        <v>201</v>
+      </c>
+      <c r="I3" s="43"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="46"/>
-      <c r="I4" s="44"/>
+      <c r="B4" s="50">
+        <v>45992</v>
+      </c>
+      <c r="C4" s="24">
+        <v>45994</v>
+      </c>
+      <c r="D4" s="52" t="s">
+        <v>197</v>
+      </c>
+      <c r="E4" s="75">
+        <v>3450167820</v>
+      </c>
+      <c r="F4" s="76" t="s">
+        <v>202</v>
+      </c>
+      <c r="G4" s="77" t="s">
+        <v>75</v>
+      </c>
+      <c r="H4" s="55" t="s">
+        <v>201</v>
+      </c>
+      <c r="I4" s="48"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="49"/>
+      <c r="B5" s="7">
+        <v>45986</v>
+      </c>
+      <c r="C5" s="24">
+        <v>45994</v>
+      </c>
+      <c r="D5" s="21">
+        <v>135533519</v>
+      </c>
+      <c r="E5" s="17">
+        <v>3450158481</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="G5" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="I5" s="43">
+        <v>45993</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="44"/>
+      <c r="B6" s="50">
+        <v>45987</v>
+      </c>
+      <c r="C6" s="24">
+        <v>45994</v>
+      </c>
+      <c r="D6" s="21">
+        <v>135558402</v>
+      </c>
+      <c r="E6" s="17">
+        <v>3450160802</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="G6" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="I6" s="43">
+        <v>45993</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="51"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="44"/>
+      <c r="B7" s="50">
+        <v>46011</v>
+      </c>
+      <c r="C7" s="24">
+        <v>45994</v>
+      </c>
+      <c r="D7" s="21">
+        <v>135582657</v>
+      </c>
+      <c r="E7" s="17">
+        <v>3450161616</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="G7" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="I7" s="43">
+        <v>46011</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="51"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="44"/>
+      <c r="B8" s="50">
+        <v>45986</v>
+      </c>
+      <c r="C8" s="24">
+        <v>45994</v>
+      </c>
+      <c r="D8" s="21">
+        <v>135576695</v>
+      </c>
+      <c r="E8" s="17">
+        <v>3450158998</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="G8" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="43">
+        <v>45986</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="51"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="44"/>
+      <c r="B9" s="50">
+        <v>45988</v>
+      </c>
+      <c r="C9" s="24">
+        <v>45994</v>
+      </c>
+      <c r="D9" s="21">
+        <v>135573735</v>
+      </c>
+      <c r="E9" s="17">
+        <v>3450162276</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="G9" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="I9" s="43">
+        <v>45988</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="51"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="44"/>
+      <c r="B10" s="50">
+        <v>45986</v>
+      </c>
+      <c r="C10" s="24">
+        <v>45994</v>
+      </c>
+      <c r="D10" s="21">
+        <v>135577253</v>
+      </c>
+      <c r="E10" s="17">
+        <v>3450158833</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="G10" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="I10" s="43">
+        <v>45986</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="51"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="44"/>
+      <c r="B11" s="50">
+        <v>45988</v>
+      </c>
+      <c r="C11" s="24">
+        <v>45994</v>
+      </c>
+      <c r="D11" s="21">
+        <v>135585027</v>
+      </c>
+      <c r="E11" s="17">
+        <v>3450163673</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="G11" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="43">
+        <v>45988</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="51"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="53"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="44"/>
+      <c r="B12" s="50">
+        <v>45989</v>
+      </c>
+      <c r="C12" s="24">
+        <v>45994</v>
+      </c>
+      <c r="D12" s="21">
+        <v>135600339</v>
+      </c>
+      <c r="E12" s="17">
+        <v>3450165059</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="G12" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="I12" s="43">
+        <v>45989</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="51"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="44"/>
+      <c r="B13" s="50">
+        <v>45989</v>
+      </c>
+      <c r="C13" s="24">
+        <v>45994</v>
+      </c>
+      <c r="D13" s="21">
+        <v>135609801</v>
+      </c>
+      <c r="E13" s="17">
+        <v>3450166258</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="G13" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="43">
+        <v>45989</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="51"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="44"/>
+      <c r="B14" s="50">
+        <v>45989</v>
+      </c>
+      <c r="C14" s="24">
+        <v>45994</v>
+      </c>
+      <c r="D14" s="21">
+        <v>135596142</v>
+      </c>
+      <c r="E14" s="17">
+        <v>3450164707</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="G14" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="I14" s="43">
+        <v>45993</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="51"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="53"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="44"/>
+      <c r="B15" s="50">
+        <v>45989</v>
+      </c>
+      <c r="C15" s="24">
+        <v>45994</v>
+      </c>
+      <c r="D15" s="21">
+        <v>135615125</v>
+      </c>
+      <c r="E15" s="17">
+        <v>3450166962</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="G15" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="43">
+        <v>45989</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="51"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="44"/>
+      <c r="B16" s="50">
+        <v>46017</v>
+      </c>
+      <c r="C16" s="24">
+        <v>45994</v>
+      </c>
+      <c r="D16" s="21">
+        <v>135631884</v>
+      </c>
+      <c r="E16" s="17">
+        <v>3450167798</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="G16" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="I16" s="43">
+        <v>45993</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="51"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="44"/>
+      <c r="B17" s="50">
+        <v>45992</v>
+      </c>
+      <c r="C17" s="24">
+        <v>45994</v>
+      </c>
+      <c r="D17" s="21">
+        <v>135642942</v>
+      </c>
+      <c r="E17" s="17">
+        <v>3450168821</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="G17" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="43">
+        <v>45992</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="44"/>
+      <c r="B18" s="7">
+        <v>45993</v>
+      </c>
+      <c r="C18" s="24">
+        <v>45994</v>
+      </c>
+      <c r="D18" s="21">
+        <v>135655094</v>
+      </c>
+      <c r="E18" s="17">
+        <v>3450169350</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="G18" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="43">
+        <v>45993</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="44"/>
+      <c r="B19" s="7">
+        <v>45987</v>
+      </c>
+      <c r="C19" s="24">
+        <v>45994</v>
+      </c>
+      <c r="D19" s="21">
+        <v>135580945</v>
+      </c>
+      <c r="E19" s="17">
+        <v>3450162067</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="G19" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="I19" s="43">
+        <v>45987</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="44"/>
+      <c r="B20" s="7">
+        <v>45988</v>
+      </c>
+      <c r="C20" s="24">
+        <v>45994</v>
+      </c>
+      <c r="D20" s="21">
+        <v>135581020</v>
+      </c>
+      <c r="E20" s="17">
+        <v>3450163222</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="G20" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="I20" s="43">
+        <v>45988</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="53"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="44"/>
+      <c r="B21" s="7">
+        <v>45987</v>
+      </c>
+      <c r="C21" s="24">
+        <v>45994</v>
+      </c>
+      <c r="D21" s="21">
+        <v>135551622</v>
+      </c>
+      <c r="E21" s="17">
+        <v>3450160054</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="G21" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="I21" s="43">
+        <v>45987</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="44"/>
+      <c r="B22" s="7">
+        <v>45993</v>
+      </c>
+      <c r="C22" s="24">
+        <v>45994</v>
+      </c>
+      <c r="D22" s="21">
+        <v>135662360</v>
+      </c>
+      <c r="E22" s="17">
+        <v>3450169965</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="G22" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="43">
+        <v>45993</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="59"/>
-      <c r="E23" s="50"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="60"/>
-      <c r="H23" s="14"/>
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>45980</v>
+      </c>
+      <c r="C23" s="24">
+        <v>45994</v>
+      </c>
+      <c r="D23" s="21">
+        <v>135477306</v>
+      </c>
+      <c r="E23" s="17">
+        <v>3450153960</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="G23" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="H23" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="I23" s="43">
+        <v>45993</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="9"/>
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>45988</v>
+      </c>
+      <c r="C24" s="24">
+        <v>45994</v>
+      </c>
+      <c r="D24" s="21">
+        <v>135581856</v>
+      </c>
+      <c r="E24" s="17">
+        <v>3450163354</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="G24" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="H24" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="I24" s="43">
+        <v>45993</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="9"/>
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="7">
+        <v>46011</v>
+      </c>
+      <c r="C25" s="24">
+        <v>45994</v>
+      </c>
+      <c r="D25" s="21">
+        <v>135487438</v>
+      </c>
+      <c r="E25" s="17">
+        <v>3450154345</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="G25" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="H25" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="I25" s="43">
+        <v>45993</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="9"/>
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="7">
+        <v>45987</v>
+      </c>
+      <c r="C26" s="24">
+        <v>45994</v>
+      </c>
+      <c r="D26" s="21">
+        <v>135561219</v>
+      </c>
+      <c r="E26" s="17">
+        <v>3450161286</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="G26" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H26" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="I26" s="43">
+        <v>45987</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="9"/>
+      <c r="A27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="7">
+        <v>46012</v>
+      </c>
+      <c r="C27" s="24">
+        <v>45994</v>
+      </c>
+      <c r="D27" s="21">
+        <v>135492844</v>
+      </c>
+      <c r="E27" s="17">
+        <v>3450154940</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="G27" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="H27" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="I27" s="43">
+        <v>45993</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="9"/>
+      <c r="A28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="7">
+        <v>45994</v>
+      </c>
+      <c r="C28" s="24">
+        <v>45994</v>
+      </c>
+      <c r="D28" s="21">
+        <v>135544155</v>
+      </c>
+      <c r="E28" s="17">
+        <v>3450159141</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="G28" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="H28" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="I28" s="43">
+        <v>45993</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="6"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="9"/>
+      <c r="A29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="7">
+        <v>45988</v>
+      </c>
+      <c r="C29" s="24">
+        <v>45994</v>
+      </c>
+      <c r="D29" s="21">
+        <v>135581566</v>
+      </c>
+      <c r="E29" s="17">
+        <v>3450163310</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="G29" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H29" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="I29" s="43">
+        <v>45988</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6"/>
       <c r="B30" s="7"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="9"/>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="6"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="21"/>
-      <c r="H31" s="9"/>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="6"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="21"/>
-      <c r="H32" s="9"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="6"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="9"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="6"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="9"/>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="6"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="9"/>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="6"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="9"/>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="6"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="9"/>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="6"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="9"/>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="6"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="9"/>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="6"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="9"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="78"/>
+      <c r="E30" s="49"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="79"/>
+      <c r="H30" s="14"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="3">
+    <cfRule type="notContainsBlanks" priority="4">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A23:A33" xr:uid="{F535CD1B-7EC8-4CD4-9DE2-4943F25AAD12}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A30" xr:uid="{F535CD1B-7EC8-4CD4-9DE2-4943F25AAD12}">
       <formula1>#REF!</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G33" xr:uid="{9AF2051F-77D3-4586-8B0A-6A9380E3F6D6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A29" xr:uid="{E44F5A38-408F-4061-943F-128F4E144D8E}">
+      <formula1>$J$2</formula1>
+    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C29 B2:B4 B6:B17" xr:uid="{7AD82A11-4EC7-4EF9-95FB-52EC6839A0E7}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G30" xr:uid="{9AF2051F-77D3-4586-8B0A-6A9380E3F6D6}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A22" xr:uid="{E44F5A38-408F-4061-943F-128F4E144D8E}">
-      <formula1>$J$2</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B17" xr:uid="{7AD82A11-4EC7-4EF9-95FB-52EC6839A0E7}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5912,40 +6409,40 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="26"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="25"/>
       <c r="E2" s="8"/>
       <c r="F2" s="11"/>
-      <c r="G2" s="27"/>
+      <c r="G2" s="26"/>
       <c r="H2" s="9"/>
-      <c r="I2" s="24"/>
+      <c r="I2" s="23"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="26"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="25"/>
       <c r="E3" s="8"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="27"/>
+      <c r="G3" s="26"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="24"/>
+      <c r="I3" s="23"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="26"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="25"/>
       <c r="E4" s="8"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="27"/>
+      <c r="G4" s="26"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="24"/>
+      <c r="I4" s="23"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
@@ -5953,12 +6450,12 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
-      <c r="D5" s="26"/>
+      <c r="D5" s="25"/>
       <c r="E5" s="8"/>
       <c r="F5" s="11"/>
-      <c r="G5" s="27"/>
+      <c r="G5" s="26"/>
       <c r="H5" s="9"/>
-      <c r="I5" s="24"/>
+      <c r="I5" s="23"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
@@ -5966,12 +6463,12 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="26"/>
+      <c r="D6" s="25"/>
       <c r="E6" s="8"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="27"/>
+      <c r="G6" s="26"/>
       <c r="H6" s="9"/>
-      <c r="I6" s="24"/>
+      <c r="I6" s="23"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
@@ -5979,12 +6476,12 @@
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
-      <c r="D7" s="26"/>
+      <c r="D7" s="25"/>
       <c r="E7" s="8"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="27"/>
+      <c r="G7" s="26"/>
       <c r="H7" s="9"/>
-      <c r="I7" s="24"/>
+      <c r="I7" s="23"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
@@ -5992,12 +6489,12 @@
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
-      <c r="D8" s="26"/>
+      <c r="D8" s="25"/>
       <c r="E8" s="8"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="27"/>
+      <c r="G8" s="26"/>
       <c r="H8" s="9"/>
-      <c r="I8" s="24"/>
+      <c r="I8" s="23"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
@@ -6005,12 +6502,12 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
-      <c r="D9" s="26"/>
+      <c r="D9" s="25"/>
       <c r="E9" s="8"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="27"/>
+      <c r="G9" s="26"/>
       <c r="H9" s="9"/>
-      <c r="I9" s="24"/>
+      <c r="I9" s="23"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
@@ -6018,12 +6515,12 @@
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
-      <c r="D10" s="26"/>
+      <c r="D10" s="25"/>
       <c r="E10" s="8"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="27"/>
+      <c r="G10" s="26"/>
       <c r="H10" s="9"/>
-      <c r="I10" s="24"/>
+      <c r="I10" s="23"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
@@ -6031,12 +6528,12 @@
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
-      <c r="D11" s="26"/>
+      <c r="D11" s="25"/>
       <c r="E11" s="8"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="27"/>
+      <c r="G11" s="26"/>
       <c r="H11" s="9"/>
-      <c r="I11" s="24"/>
+      <c r="I11" s="23"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
@@ -6044,12 +6541,12 @@
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
-      <c r="D12" s="26"/>
+      <c r="D12" s="25"/>
       <c r="E12" s="8"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="27"/>
+      <c r="G12" s="26"/>
       <c r="H12" s="9"/>
-      <c r="I12" s="24"/>
+      <c r="I12" s="23"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
@@ -6057,12 +6554,12 @@
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
-      <c r="D13" s="26"/>
+      <c r="D13" s="25"/>
       <c r="E13" s="8"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="27"/>
+      <c r="G13" s="26"/>
       <c r="H13" s="9"/>
-      <c r="I13" s="24"/>
+      <c r="I13" s="23"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
@@ -6070,12 +6567,12 @@
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
-      <c r="D14" s="26"/>
+      <c r="D14" s="25"/>
       <c r="E14" s="8"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="27"/>
+      <c r="G14" s="26"/>
       <c r="H14" s="9"/>
-      <c r="I14" s="24"/>
+      <c r="I14" s="23"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
@@ -6083,23 +6580,23 @@
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
-      <c r="D15" s="26"/>
+      <c r="D15" s="25"/>
       <c r="E15" s="8"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="27"/>
+      <c r="G15" s="26"/>
       <c r="H15" s="9"/>
-      <c r="I15" s="24"/>
+      <c r="I15" s="23"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
-      <c r="D16" s="26"/>
+      <c r="D16" s="25"/>
       <c r="E16" s="8"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="27"/>
+      <c r="G16" s="26"/>
       <c r="H16" s="9"/>
-      <c r="I16" s="24"/>
+      <c r="I16" s="23"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6"/>
@@ -6110,7 +6607,7 @@
       <c r="F17" s="11"/>
       <c r="G17" s="6"/>
       <c r="H17" s="9"/>
-      <c r="I17" s="24"/>
+      <c r="I17" s="23"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6"/>
@@ -6121,7 +6618,7 @@
       <c r="F18" s="11"/>
       <c r="G18" s="6"/>
       <c r="H18" s="9"/>
-      <c r="I18" s="24"/>
+      <c r="I18" s="23"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
@@ -6132,7 +6629,7 @@
       <c r="F19" s="12"/>
       <c r="G19" s="6"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="24"/>
+      <c r="I19" s="23"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
@@ -6143,7 +6640,7 @@
       <c r="F20" s="14"/>
       <c r="G20" s="6"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="24"/>
+      <c r="I20" s="23"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
@@ -6562,63 +7059,63 @@
         <v>9</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="22"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="17"/>
       <c r="F2" s="11"/>
       <c r="G2" s="19"/>
       <c r="H2" s="9"/>
-      <c r="I2" s="24"/>
+      <c r="I2" s="23"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="22"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="17"/>
       <c r="F3" s="11"/>
       <c r="G3" s="19"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="33"/>
+      <c r="I3" s="32"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="22"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="21"/>
       <c r="E4" s="17"/>
       <c r="F4" s="11"/>
       <c r="G4" s="19"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="24"/>
+      <c r="I4" s="23"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="22"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="21"/>
       <c r="E5" s="17"/>
       <c r="F5" s="11"/>
       <c r="G5" s="19"/>
       <c r="H5" s="9"/>
-      <c r="I5" s="24"/>
+      <c r="I5" s="23"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="20"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="31"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="30"/>
       <c r="G6" s="6"/>
       <c r="H6" s="9"/>
-      <c r="I6" s="24"/>
+      <c r="I6" s="23"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6"/>
@@ -7145,7 +7642,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="39" t="s">
+      <c r="H1" s="38" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -7157,232 +7654,232 @@
         <v>9</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="22"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="17"/>
       <c r="F2" s="18"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="24"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="23"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="22"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="17"/>
       <c r="F3" s="18"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="24"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="23"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="22"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="21"/>
       <c r="E4" s="17"/>
       <c r="F4" s="18"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="24"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="23"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="22"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="21"/>
       <c r="E5" s="17"/>
       <c r="F5" s="18"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="24"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="23"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="7"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="22"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="21"/>
       <c r="E6" s="17"/>
       <c r="F6" s="18"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="24"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="23"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="7"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="22"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="21"/>
       <c r="E7" s="17"/>
       <c r="F7" s="18"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="24"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="23"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="7"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="22"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="21"/>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="24"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="23"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="7"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="22"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="21"/>
       <c r="E9" s="17"/>
       <c r="F9" s="18"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="24"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="23"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="7"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="22"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="21"/>
       <c r="E10" s="17"/>
       <c r="F10" s="18"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="24"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="23"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="7"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="22"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="21"/>
       <c r="E11" s="17"/>
       <c r="F11" s="18"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="24"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="23"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="7"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="22"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="21"/>
       <c r="E12" s="17"/>
       <c r="F12" s="18"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="34"/>
-      <c r="I12" s="24"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="23"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="7"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="22"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="21"/>
       <c r="E13" s="17"/>
       <c r="F13" s="18"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="24"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="33"/>
+      <c r="I13" s="23"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="7"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="22"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="21"/>
       <c r="E14" s="17"/>
       <c r="F14" s="18"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="24"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="23"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="7"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="22"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="21"/>
       <c r="E15" s="17"/>
       <c r="F15" s="18"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="24"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="23"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="7"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="22"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="21"/>
       <c r="E16" s="17"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="24"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="23"/>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="26" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="7"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="22"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="21"/>
       <c r="E17" s="17"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="24"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="23"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B18" s="7"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="22"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="21"/>
       <c r="E18" s="17"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="34"/>
-      <c r="I18" s="24"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="23"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
       <c r="B19" s="8"/>
       <c r="C19" s="7"/>
       <c r="D19" s="20"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="28"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="24"/>
+      <c r="I19" s="23"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
@@ -7391,9 +7888,9 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="14"/>
-      <c r="G20" s="29"/>
+      <c r="G20" s="28"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="24"/>
+      <c r="I20" s="23"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
@@ -7402,9 +7899,9 @@
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="9"/>
-      <c r="G21" s="29"/>
+      <c r="G21" s="28"/>
       <c r="H21" s="9"/>
-      <c r="I21" s="24"/>
+      <c r="I21" s="23"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6"/>
@@ -7413,9 +7910,9 @@
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="9"/>
-      <c r="G22" s="29"/>
+      <c r="G22" s="28"/>
       <c r="H22" s="9"/>
-      <c r="I22" s="24"/>
+      <c r="I22" s="23"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6"/>
@@ -7424,9 +7921,9 @@
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="9"/>
-      <c r="G23" s="29"/>
+      <c r="G23" s="28"/>
       <c r="H23" s="9"/>
-      <c r="I23" s="24"/>
+      <c r="I23" s="23"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6"/>
@@ -7435,9 +7932,9 @@
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9"/>
-      <c r="G24" s="29"/>
+      <c r="G24" s="28"/>
       <c r="H24" s="9"/>
-      <c r="I24" s="24"/>
+      <c r="I24" s="23"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6"/>
@@ -7448,7 +7945,7 @@
       <c r="F25" s="9"/>
       <c r="G25" s="6"/>
       <c r="H25" s="9"/>
-      <c r="I25" s="24"/>
+      <c r="I25" s="23"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6"/>
@@ -7459,7 +7956,7 @@
       <c r="F26" s="9"/>
       <c r="G26" s="6"/>
       <c r="H26" s="9"/>
-      <c r="I26" s="24"/>
+      <c r="I26" s="23"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6"/>
@@ -7470,7 +7967,7 @@
       <c r="F27" s="9"/>
       <c r="G27" s="6"/>
       <c r="H27" s="9"/>
-      <c r="I27" s="24"/>
+      <c r="I27" s="23"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6"/>
@@ -7481,7 +7978,7 @@
       <c r="F28" s="9"/>
       <c r="G28" s="6"/>
       <c r="H28" s="9"/>
-      <c r="I28" s="24"/>
+      <c r="I28" s="23"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6"/>
@@ -7492,7 +7989,7 @@
       <c r="F29" s="9"/>
       <c r="G29" s="6"/>
       <c r="H29" s="9"/>
-      <c r="I29" s="24"/>
+      <c r="I29" s="23"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6"/>
@@ -7503,7 +8000,7 @@
       <c r="F30" s="9"/>
       <c r="G30" s="6"/>
       <c r="H30" s="9"/>
-      <c r="I30" s="24"/>
+      <c r="I30" s="23"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6"/>
@@ -7514,7 +8011,7 @@
       <c r="F31" s="9"/>
       <c r="G31" s="6"/>
       <c r="H31" s="9"/>
-      <c r="I31" s="24"/>
+      <c r="I31" s="23"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6"/>
@@ -7525,7 +8022,7 @@
       <c r="F32" s="9"/>
       <c r="G32" s="6"/>
       <c r="H32" s="9"/>
-      <c r="I32" s="24"/>
+      <c r="I32" s="23"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6"/>
@@ -7536,7 +8033,7 @@
       <c r="F33" s="9"/>
       <c r="G33" s="6"/>
       <c r="H33" s="9"/>
-      <c r="I33" s="24"/>
+      <c r="I33" s="23"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="6"/>
@@ -7547,7 +8044,7 @@
       <c r="F34" s="9"/>
       <c r="G34" s="6"/>
       <c r="H34" s="9"/>
-      <c r="I34" s="24"/>
+      <c r="I34" s="23"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="6"/>
@@ -7558,7 +8055,7 @@
       <c r="F35" s="9"/>
       <c r="G35" s="6"/>
       <c r="H35" s="9"/>
-      <c r="I35" s="24"/>
+      <c r="I35" s="23"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
@@ -7848,494 +8345,494 @@
         <v>9</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="43"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="42"/>
       <c r="E2" s="17"/>
       <c r="F2" s="11"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="44"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="43"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="43"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="42"/>
       <c r="E3" s="17"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="44"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="43"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="43"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="42"/>
       <c r="E4" s="17"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="44"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="43"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="43"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="42"/>
       <c r="E5" s="17"/>
       <c r="F5" s="11"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="44"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="43"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="7"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="43"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="42"/>
       <c r="E6" s="17"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="44"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="43"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="7"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="43"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="42"/>
       <c r="E7" s="17"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="44"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="43"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="7"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="43"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="42"/>
       <c r="E8" s="17"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="44"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="43"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="7"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="43"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="42"/>
       <c r="E9" s="17"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="44"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="43"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="7"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="43"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="42"/>
       <c r="E10" s="17"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="45"/>
-      <c r="I10" s="44"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="43"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="7"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="43"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="42"/>
       <c r="E11" s="17"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="44"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="43"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="7"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="43"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="42"/>
       <c r="E12" s="17"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="44"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="43"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="7"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="43"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="42"/>
       <c r="E13" s="17"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="44"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="43"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="7"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="43"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="42"/>
       <c r="E14" s="17"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="44"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="43"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="7"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="43"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="42"/>
       <c r="E15" s="17"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="44"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="44"/>
+      <c r="I15" s="43"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="7"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="43"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="42"/>
       <c r="E16" s="17"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="45"/>
-      <c r="I16" s="44"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="43"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="26" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="7"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="43"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="42"/>
       <c r="E17" s="17"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="44"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="44"/>
+      <c r="I17" s="43"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B18" s="7"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="43"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="42"/>
       <c r="E18" s="17"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="44"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="43"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
       <c r="B19" s="7"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="43"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="42"/>
       <c r="E19" s="17"/>
       <c r="F19" s="11"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="44"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="43"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
       <c r="B20" s="7"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="43"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="42"/>
       <c r="E20" s="17"/>
       <c r="F20" s="11"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="44"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="43"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
       <c r="B21" s="7"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="43"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="42"/>
       <c r="E21" s="17"/>
       <c r="F21" s="11"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="44"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="43"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6"/>
       <c r="B22" s="7"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="43"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="42"/>
       <c r="E22" s="17"/>
       <c r="F22" s="11"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="44"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="43"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6"/>
       <c r="B23" s="7"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="43"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="42"/>
       <c r="E23" s="17"/>
       <c r="F23" s="11"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="44"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="43"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6"/>
       <c r="B24" s="7"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="43"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="42"/>
       <c r="E24" s="17"/>
       <c r="F24" s="11"/>
-      <c r="G24" s="42"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="44"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="43"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6"/>
       <c r="B25" s="7"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="43"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="42"/>
       <c r="E25" s="17"/>
       <c r="F25" s="11"/>
-      <c r="G25" s="42"/>
-      <c r="H25" s="45"/>
-      <c r="I25" s="44"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="43"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6"/>
       <c r="B26" s="7"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="43"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="42"/>
       <c r="E26" s="17"/>
       <c r="F26" s="11"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="45"/>
-      <c r="I26" s="44"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="43"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6"/>
       <c r="B27" s="7"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="43"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="42"/>
       <c r="E27" s="17"/>
       <c r="F27" s="11"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="45"/>
-      <c r="I27" s="44"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="43"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6"/>
       <c r="B28" s="7"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="43"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="42"/>
       <c r="E28" s="17"/>
       <c r="F28" s="11"/>
-      <c r="G28" s="42"/>
-      <c r="H28" s="45"/>
-      <c r="I28" s="44"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="43"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6"/>
-      <c r="B29" s="47"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="43"/>
+      <c r="B29" s="46"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="42"/>
       <c r="E29" s="17"/>
       <c r="F29" s="11"/>
-      <c r="G29" s="42"/>
-      <c r="H29" s="45"/>
-      <c r="I29" s="44"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="44"/>
+      <c r="I29" s="43"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6"/>
       <c r="B30" s="7"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="43"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="42"/>
       <c r="E30" s="17"/>
       <c r="F30" s="11"/>
-      <c r="G30" s="42"/>
+      <c r="G30" s="41"/>
       <c r="H30" s="12"/>
-      <c r="I30" s="44"/>
+      <c r="I30" s="43"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6"/>
       <c r="B31" s="7"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="43"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="42"/>
       <c r="E31" s="17"/>
       <c r="F31" s="11"/>
-      <c r="G31" s="42"/>
+      <c r="G31" s="41"/>
       <c r="H31" s="12"/>
-      <c r="I31" s="44"/>
+      <c r="I31" s="43"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6"/>
       <c r="B32" s="7"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="43"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="42"/>
       <c r="E32" s="17"/>
       <c r="F32" s="11"/>
-      <c r="G32" s="42"/>
+      <c r="G32" s="41"/>
       <c r="H32" s="12"/>
-      <c r="I32" s="44"/>
+      <c r="I32" s="43"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6"/>
       <c r="B33" s="7"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="43"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="42"/>
       <c r="E33" s="17"/>
       <c r="F33" s="11"/>
-      <c r="G33" s="42"/>
+      <c r="G33" s="41"/>
       <c r="H33" s="12"/>
-      <c r="I33" s="44"/>
+      <c r="I33" s="43"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="6"/>
       <c r="B34" s="7"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="43"/>
+      <c r="C34" s="24"/>
+      <c r="D34" s="42"/>
       <c r="E34" s="17"/>
       <c r="F34" s="11"/>
-      <c r="G34" s="42"/>
+      <c r="G34" s="41"/>
       <c r="H34" s="12"/>
-      <c r="I34" s="44"/>
+      <c r="I34" s="43"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="6"/>
       <c r="B35" s="7"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="43"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="42"/>
       <c r="E35" s="17"/>
       <c r="F35" s="11"/>
-      <c r="G35" s="42"/>
+      <c r="G35" s="41"/>
       <c r="H35" s="12"/>
-      <c r="I35" s="44"/>
+      <c r="I35" s="43"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
       <c r="B36" s="7"/>
-      <c r="C36" s="25"/>
-      <c r="D36" s="43"/>
+      <c r="C36" s="24"/>
+      <c r="D36" s="42"/>
       <c r="E36" s="17"/>
       <c r="F36" s="11"/>
-      <c r="G36" s="42"/>
+      <c r="G36" s="41"/>
       <c r="H36" s="12"/>
-      <c r="I36" s="44"/>
+      <c r="I36" s="43"/>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="6"/>
       <c r="B37" s="7"/>
-      <c r="C37" s="25"/>
-      <c r="D37" s="43"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="42"/>
       <c r="E37" s="17"/>
       <c r="F37" s="11"/>
-      <c r="G37" s="42"/>
+      <c r="G37" s="41"/>
       <c r="H37" s="12"/>
-      <c r="I37" s="44"/>
+      <c r="I37" s="43"/>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="6"/>
       <c r="B38" s="7"/>
-      <c r="C38" s="25"/>
-      <c r="D38" s="43"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="42"/>
       <c r="E38" s="17"/>
       <c r="F38" s="11"/>
-      <c r="G38" s="42"/>
+      <c r="G38" s="41"/>
       <c r="H38" s="12"/>
-      <c r="I38" s="44"/>
+      <c r="I38" s="43"/>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="6"/>
       <c r="B39" s="7"/>
-      <c r="C39" s="25"/>
-      <c r="D39" s="43"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="42"/>
       <c r="E39" s="17"/>
       <c r="F39" s="11"/>
-      <c r="G39" s="42"/>
+      <c r="G39" s="41"/>
       <c r="H39" s="12"/>
-      <c r="I39" s="44"/>
+      <c r="I39" s="43"/>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="6"/>
       <c r="B40" s="7"/>
-      <c r="C40" s="25"/>
-      <c r="D40" s="43"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="42"/>
       <c r="E40" s="17"/>
       <c r="F40" s="11"/>
-      <c r="G40" s="42"/>
+      <c r="G40" s="41"/>
       <c r="H40" s="12"/>
-      <c r="I40" s="44"/>
+      <c r="I40" s="43"/>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="6"/>
       <c r="B41" s="7"/>
-      <c r="C41" s="25"/>
-      <c r="D41" s="43"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="42"/>
       <c r="E41" s="17"/>
       <c r="F41" s="11"/>
-      <c r="G41" s="42"/>
+      <c r="G41" s="41"/>
       <c r="H41" s="12"/>
-      <c r="I41" s="44"/>
+      <c r="I41" s="43"/>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="6"/>
       <c r="B42" s="7"/>
-      <c r="C42" s="25"/>
-      <c r="D42" s="43"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="42"/>
       <c r="E42" s="17"/>
       <c r="F42" s="11"/>
-      <c r="G42" s="42"/>
+      <c r="G42" s="41"/>
       <c r="H42" s="12"/>
-      <c r="I42" s="44"/>
+      <c r="I42" s="43"/>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="6"/>
       <c r="B43" s="8"/>
       <c r="C43" s="7"/>
-      <c r="D43" s="30"/>
+      <c r="D43" s="29"/>
       <c r="E43" s="17"/>
       <c r="F43" s="12"/>
-      <c r="G43" s="42"/>
+      <c r="G43" s="41"/>
       <c r="H43" s="12"/>
       <c r="I43" s="12"/>
     </row>
@@ -8419,494 +8916,494 @@
         <v>9</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="43"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="42"/>
       <c r="E2" s="17"/>
       <c r="F2" s="11"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="44"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="43"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="43"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="42"/>
       <c r="E3" s="17"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="44"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="43"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="43"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="42"/>
       <c r="E4" s="17"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="44"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="43"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="43"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="42"/>
       <c r="E5" s="17"/>
       <c r="F5" s="11"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="44"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="43"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="7"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="43"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="42"/>
       <c r="E6" s="17"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="44"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="43"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="7"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="43"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="42"/>
       <c r="E7" s="17"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="44"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="43"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="7"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="43"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="42"/>
       <c r="E8" s="17"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="44"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="43"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="7"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="43"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="42"/>
       <c r="E9" s="17"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="44"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="43"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="7"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="43"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="42"/>
       <c r="E10" s="17"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="45"/>
-      <c r="I10" s="44"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="43"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="7"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="43"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="42"/>
       <c r="E11" s="17"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="44"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="43"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="7"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="43"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="42"/>
       <c r="E12" s="17"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="44"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="43"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="7"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="43"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="42"/>
       <c r="E13" s="17"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="44"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="43"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="7"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="43"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="42"/>
       <c r="E14" s="17"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="44"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="43"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="7"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="43"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="42"/>
       <c r="E15" s="17"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="44"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="44"/>
+      <c r="I15" s="43"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="7"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="43"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="42"/>
       <c r="E16" s="17"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="45"/>
-      <c r="I16" s="44"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="43"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="26" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="7"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="43"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="42"/>
       <c r="E17" s="17"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="44"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="44"/>
+      <c r="I17" s="43"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B18" s="7"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="43"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="42"/>
       <c r="E18" s="17"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="44"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="43"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
       <c r="B19" s="7"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="43"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="42"/>
       <c r="E19" s="17"/>
       <c r="F19" s="11"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="44"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="43"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
       <c r="B20" s="7"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="43"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="42"/>
       <c r="E20" s="17"/>
       <c r="F20" s="11"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="44"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="43"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
       <c r="B21" s="7"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="43"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="42"/>
       <c r="E21" s="17"/>
       <c r="F21" s="11"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="44"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="43"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6"/>
       <c r="B22" s="7"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="43"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="42"/>
       <c r="E22" s="17"/>
       <c r="F22" s="11"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="44"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="43"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6"/>
       <c r="B23" s="7"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="43"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="42"/>
       <c r="E23" s="17"/>
       <c r="F23" s="11"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="44"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="43"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6"/>
       <c r="B24" s="7"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="43"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="42"/>
       <c r="E24" s="17"/>
       <c r="F24" s="11"/>
-      <c r="G24" s="42"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="44"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="43"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6"/>
       <c r="B25" s="7"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="43"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="42"/>
       <c r="E25" s="17"/>
       <c r="F25" s="11"/>
-      <c r="G25" s="42"/>
-      <c r="H25" s="45"/>
-      <c r="I25" s="44"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="43"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6"/>
       <c r="B26" s="7"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="43"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="42"/>
       <c r="E26" s="17"/>
       <c r="F26" s="11"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="45"/>
-      <c r="I26" s="44"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="43"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6"/>
       <c r="B27" s="7"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="43"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="42"/>
       <c r="E27" s="17"/>
       <c r="F27" s="11"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="45"/>
-      <c r="I27" s="44"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="43"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6"/>
       <c r="B28" s="7"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="43"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="42"/>
       <c r="E28" s="17"/>
       <c r="F28" s="11"/>
-      <c r="G28" s="42"/>
-      <c r="H28" s="45"/>
-      <c r="I28" s="44"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="43"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6"/>
-      <c r="B29" s="47"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="43"/>
+      <c r="B29" s="46"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="42"/>
       <c r="E29" s="17"/>
       <c r="F29" s="11"/>
-      <c r="G29" s="42"/>
-      <c r="H29" s="45"/>
-      <c r="I29" s="44"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="44"/>
+      <c r="I29" s="43"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6"/>
       <c r="B30" s="7"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="43"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="42"/>
       <c r="E30" s="17"/>
       <c r="F30" s="11"/>
-      <c r="G30" s="42"/>
+      <c r="G30" s="41"/>
       <c r="H30" s="12"/>
-      <c r="I30" s="44"/>
+      <c r="I30" s="43"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6"/>
       <c r="B31" s="7"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="43"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="42"/>
       <c r="E31" s="17"/>
       <c r="F31" s="11"/>
-      <c r="G31" s="42"/>
+      <c r="G31" s="41"/>
       <c r="H31" s="12"/>
-      <c r="I31" s="44"/>
+      <c r="I31" s="43"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6"/>
       <c r="B32" s="7"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="43"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="42"/>
       <c r="E32" s="17"/>
       <c r="F32" s="11"/>
-      <c r="G32" s="42"/>
+      <c r="G32" s="41"/>
       <c r="H32" s="12"/>
-      <c r="I32" s="44"/>
+      <c r="I32" s="43"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6"/>
       <c r="B33" s="7"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="43"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="42"/>
       <c r="E33" s="17"/>
       <c r="F33" s="11"/>
-      <c r="G33" s="42"/>
+      <c r="G33" s="41"/>
       <c r="H33" s="12"/>
-      <c r="I33" s="44"/>
+      <c r="I33" s="43"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="6"/>
       <c r="B34" s="7"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="43"/>
+      <c r="C34" s="24"/>
+      <c r="D34" s="42"/>
       <c r="E34" s="17"/>
       <c r="F34" s="11"/>
-      <c r="G34" s="42"/>
+      <c r="G34" s="41"/>
       <c r="H34" s="12"/>
-      <c r="I34" s="44"/>
+      <c r="I34" s="43"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="6"/>
       <c r="B35" s="7"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="43"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="42"/>
       <c r="E35" s="17"/>
       <c r="F35" s="11"/>
-      <c r="G35" s="42"/>
+      <c r="G35" s="41"/>
       <c r="H35" s="12"/>
-      <c r="I35" s="44"/>
+      <c r="I35" s="43"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
       <c r="B36" s="7"/>
-      <c r="C36" s="25"/>
-      <c r="D36" s="43"/>
+      <c r="C36" s="24"/>
+      <c r="D36" s="42"/>
       <c r="E36" s="17"/>
       <c r="F36" s="11"/>
-      <c r="G36" s="42"/>
+      <c r="G36" s="41"/>
       <c r="H36" s="12"/>
-      <c r="I36" s="44"/>
+      <c r="I36" s="43"/>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="6"/>
       <c r="B37" s="7"/>
-      <c r="C37" s="25"/>
-      <c r="D37" s="43"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="42"/>
       <c r="E37" s="17"/>
       <c r="F37" s="11"/>
-      <c r="G37" s="42"/>
+      <c r="G37" s="41"/>
       <c r="H37" s="12"/>
-      <c r="I37" s="44"/>
+      <c r="I37" s="43"/>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="6"/>
       <c r="B38" s="7"/>
-      <c r="C38" s="25"/>
-      <c r="D38" s="43"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="42"/>
       <c r="E38" s="17"/>
       <c r="F38" s="11"/>
-      <c r="G38" s="42"/>
+      <c r="G38" s="41"/>
       <c r="H38" s="12"/>
-      <c r="I38" s="44"/>
+      <c r="I38" s="43"/>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="6"/>
       <c r="B39" s="7"/>
-      <c r="C39" s="25"/>
-      <c r="D39" s="43"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="42"/>
       <c r="E39" s="17"/>
       <c r="F39" s="11"/>
-      <c r="G39" s="42"/>
+      <c r="G39" s="41"/>
       <c r="H39" s="12"/>
-      <c r="I39" s="44"/>
+      <c r="I39" s="43"/>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="6"/>
       <c r="B40" s="7"/>
-      <c r="C40" s="25"/>
-      <c r="D40" s="43"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="42"/>
       <c r="E40" s="17"/>
       <c r="F40" s="11"/>
-      <c r="G40" s="42"/>
+      <c r="G40" s="41"/>
       <c r="H40" s="12"/>
-      <c r="I40" s="44"/>
+      <c r="I40" s="43"/>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="6"/>
       <c r="B41" s="7"/>
-      <c r="C41" s="25"/>
-      <c r="D41" s="43"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="42"/>
       <c r="E41" s="17"/>
       <c r="F41" s="11"/>
-      <c r="G41" s="42"/>
+      <c r="G41" s="41"/>
       <c r="H41" s="12"/>
-      <c r="I41" s="44"/>
+      <c r="I41" s="43"/>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="6"/>
       <c r="B42" s="7"/>
-      <c r="C42" s="25"/>
-      <c r="D42" s="43"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="42"/>
       <c r="E42" s="17"/>
       <c r="F42" s="11"/>
-      <c r="G42" s="42"/>
+      <c r="G42" s="41"/>
       <c r="H42" s="12"/>
-      <c r="I42" s="44"/>
+      <c r="I42" s="43"/>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="6"/>
       <c r="B43" s="8"/>
       <c r="C43" s="7"/>
-      <c r="D43" s="30"/>
+      <c r="D43" s="29"/>
       <c r="E43" s="17"/>
       <c r="F43" s="12"/>
-      <c r="G43" s="42"/>
+      <c r="G43" s="41"/>
       <c r="H43" s="12"/>
       <c r="I43" s="12"/>
     </row>
@@ -8942,6 +9439,56 @@
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
@@ -8949,7 +9496,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-531147</_dlc_DocId>
@@ -8992,7 +9539,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="522e863aef51f288a2c445becadad51a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e2cd90bc508d2ca63574b1ae88af87c9" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -9370,68 +9917,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED44BF61-13B5-4B27-80E4-AE5B5A73F019}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
--- a/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 01.12.2025 a 08.12.2025.xlsx
+++ b/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 01.12.2025 a 08.12.2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/shirlei_witkowski_allianz_com_br/Documents/E-MAILS Santander Recusa/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/12. Dezembro/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBB59DD7-6DB2-4737-927B-497EF9F3BDCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B5FD206-DF08-45BE-8696-51A6A4A87315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01.12" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="284">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">LIMBO </t>
   </si>
   <si>
-    <t>RICARDO LEDO DE SOUZA</t>
+    <t>RICARDO LEDO DE SOUZA CPF 17745077818</t>
   </si>
   <si>
     <t>Controller</t>
@@ -816,13 +816,155 @@
   </si>
   <si>
     <t>FRUSTRADO, PRAZO PARA REENVIO EXP. FOTOS NÃO CORRIGIDAS: Painel com carro ligado (Veiculo desligado).</t>
+  </si>
+  <si>
+    <t>WILLIAN CORREA CPF- 05052187980</t>
+  </si>
+  <si>
+    <t>Duplicidade com a vc</t>
+  </si>
+  <si>
+    <t>REGINA GUIMARAES STUDART CPF- 88799727749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADRIANO PEREIRA DA SILVA                     </t>
+  </si>
+  <si>
+    <t>Favor enviar cópia do endosso de cancelamento da apólice 2025/202
+6 através desse e-mail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCIO FRANCISCO PEREIRA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUA LIMA ALVES                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA HELENA FERREIRA VICENTIN               </t>
+  </si>
+  <si>
+    <t>Nup - Cancelamento 03.12.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDREIA LOURENCO MARTINHAO                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRUSTRADO *PRAZO EXP * SEGURADO N CORRIGIU OS PASSOS SOLICITADOS repique: Painel com carro desligado, Chassi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUELEN SILVA LIMA DE JESUS                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TARCISIO LOPES DE CARVALHO                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELIANA DE JESUS                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">J M MATOS SERVICOS DE ESTETICA LTDA ME       </t>
+  </si>
+  <si>
+    <t>FRUSTRADO *PRAZO EXP * SEGURADO N CORRIGIU OS PASSOS SOLICITADOS repique: Frente passageiro, Documento do veículo, Frente motorista, Traseira passageiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDUARDO DA MOTA                              </t>
+  </si>
+  <si>
+    <t>FRUSTRADO *PRAZO EXP * SEGURADO N CORRIGIU OS PASSOS SOLICITADOS repique: Frente e lateral do passageiro, Frente e lateral do motorista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUILHERME FREITAS DE ABREU                   </t>
+  </si>
+  <si>
+    <t>RECUSA: FRUSTRADO repique: Frente e lateral do passageiro, Painel com carro desligado, Chassi, Frente e lateral do motorista, Motor e placa, Traseira e lateral do passageiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALTMANN GROUP LTDA ME                        </t>
+  </si>
+  <si>
+    <t>**FRUSTRADO** CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: CHASSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSMAR BARROS DOMINGUES                       </t>
+  </si>
+  <si>
+    <t>FRUSTRADO *PRAZO EXP * SEGURADO N CORRIGIU OS PASSOS SOLICITADOS repique: Frente e lateral do passageiro, Painel com carro desligado, Frente e lateral do motorista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIRCE TEIXEIRA GONCALVES                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDILAINE DA SILVA RODRIGUES                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANTONIA REGINA FREITAS RIBEIRO DE LIMA       </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS:CRLV (Não enviado). Traseira e lat. dir. (Não tirou foto). Hodômetro (Desligado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUDES CLEONE DE SOUZA SANTOS                 </t>
+  </si>
+  <si>
+    <t>FRUSTRADO *PRAZO EXP * SEGURADO N CORRIGIU OS PASSOS SOLICITADOS repique: Painel com a motocicleta desligada // eliminador de rabeta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAFAELA SILVA SANTOS COMUNICACOES LTDA ME    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEIDE APARECIDA VIEIRA                       </t>
+  </si>
+  <si>
+    <t>Recusa: Divergência de Placa e Chassi do veiculo apresentado (BZR7749 / 9C6SG3310K0041065) com os dados cadastrados na proposta (BZR4479 / 9C6SG3310L0041749)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIEL BOABAID DALCANALE                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCIA HELENA POSCAI                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELIONAI REZENDE DE CASTRO                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KELVIN BREDA MATIAS                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENERGIA FORTE MULTISERVICOS LTDA ME          </t>
+  </si>
+  <si>
+    <t>falta de vistoria</t>
+  </si>
+  <si>
+    <t>AVECENTER IND E COM VAREJISTA DE EQUIPAMENTOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAGA COMPANY BRASIL LTDA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAUDIA MARIA DA SILVA ROCHA                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MICHEL CORTES LAMBERTI                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">WILSON REIS DOS PASSOS                       </t>
+  </si>
+  <si>
+    <t>LIMBO</t>
+  </si>
+  <si>
+    <t>INJEMAX LTDA ME</t>
+  </si>
+  <si>
+    <t>Não</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -870,6 +1012,13 @@
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF414141"/>
+      <name val="Allianz Neo"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1127,7 +1276,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1332,6 +1481,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6409,366 +6566,904 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="23"/>
+      <c r="B2" s="24">
+        <v>45994</v>
+      </c>
+      <c r="C2" s="24">
+        <v>45995</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="8">
+        <v>3450171725</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="G2" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="I2" s="43"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="23"/>
+      <c r="B3" s="24">
+        <v>45999</v>
+      </c>
+      <c r="C3" s="24">
+        <v>45995</v>
+      </c>
+      <c r="D3" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="8">
+        <v>3450171043</v>
+      </c>
+      <c r="F3" s="54" t="s">
+        <v>239</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="I3" s="43"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="23"/>
+      <c r="B4" s="24">
+        <v>45985</v>
+      </c>
+      <c r="C4" s="24">
+        <v>45995</v>
+      </c>
+      <c r="D4" s="21">
+        <v>135498261</v>
+      </c>
+      <c r="E4" s="80">
+        <v>3450155544</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="G4" s="81" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="82" t="s">
+        <v>241</v>
+      </c>
+      <c r="I4" s="43">
+        <v>45988</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="23"/>
+      <c r="B5" s="7">
+        <v>45980</v>
+      </c>
+      <c r="C5" s="24">
+        <v>45995</v>
+      </c>
+      <c r="D5" s="21">
+        <v>135508040</v>
+      </c>
+      <c r="E5" s="80">
+        <v>3450152893</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="G5" s="81" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" s="43">
+        <v>45980</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="23"/>
+      <c r="B6" s="7">
+        <v>45985</v>
+      </c>
+      <c r="C6" s="24">
+        <v>45995</v>
+      </c>
+      <c r="D6" s="21">
+        <v>135518927</v>
+      </c>
+      <c r="E6" s="80">
+        <v>3450157271</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="G6" s="81" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" s="43">
+        <v>45985</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="23"/>
+      <c r="B7" s="7">
+        <v>45998</v>
+      </c>
+      <c r="C7" s="24">
+        <v>45995</v>
+      </c>
+      <c r="D7" s="21">
+        <v>135574859</v>
+      </c>
+      <c r="E7" s="80">
+        <v>3450162364</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="G7" s="81" t="s">
+        <v>75</v>
+      </c>
+      <c r="H7" s="47" t="s">
+        <v>245</v>
+      </c>
+      <c r="I7" s="43">
+        <v>45994</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="23"/>
+      <c r="B8" s="7">
+        <v>45987</v>
+      </c>
+      <c r="C8" s="24">
+        <v>45995</v>
+      </c>
+      <c r="D8" s="21">
+        <v>135602448</v>
+      </c>
+      <c r="E8" s="80">
+        <v>3450160318</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="G8" s="81" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="47" t="s">
+        <v>247</v>
+      </c>
+      <c r="I8" s="43">
+        <v>45987</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="23"/>
+      <c r="B9" s="7">
+        <v>45989</v>
+      </c>
+      <c r="C9" s="24">
+        <v>45995</v>
+      </c>
+      <c r="D9" s="21">
+        <v>135607689</v>
+      </c>
+      <c r="E9" s="80">
+        <v>3450165873</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="G9" s="81" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="47" t="s">
+        <v>216</v>
+      </c>
+      <c r="I9" s="43">
+        <v>45989</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="23"/>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="B10" s="7">
+        <v>45989</v>
+      </c>
+      <c r="C10" s="24">
+        <v>45995</v>
+      </c>
+      <c r="D10" s="21">
+        <v>135616350</v>
+      </c>
+      <c r="E10" s="80">
+        <v>3450167127</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="G10" s="81" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" s="43">
+        <v>45989</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="15.75">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="23"/>
+      <c r="B11" s="7">
+        <v>45989</v>
+      </c>
+      <c r="C11" s="24">
+        <v>45995</v>
+      </c>
+      <c r="D11" s="21">
+        <v>135603102</v>
+      </c>
+      <c r="E11" s="80">
+        <v>3450165422</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="G11" s="81" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" s="83" t="s">
+        <v>164</v>
+      </c>
+      <c r="I11" s="43">
+        <v>45989</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="23"/>
-    </row>
-    <row r="13" spans="1:9">
+      <c r="B12" s="7">
+        <v>45989</v>
+      </c>
+      <c r="C12" s="24">
+        <v>45995</v>
+      </c>
+      <c r="D12" s="21">
+        <v>135617144</v>
+      </c>
+      <c r="E12" s="80">
+        <v>3450167226</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="G12" s="81" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" s="47" t="s">
+        <v>252</v>
+      </c>
+      <c r="I12" s="43">
+        <v>45989</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="15.75">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="23"/>
+      <c r="B13" s="7">
+        <v>45989</v>
+      </c>
+      <c r="C13" s="24">
+        <v>45995</v>
+      </c>
+      <c r="D13" s="21">
+        <v>135608598</v>
+      </c>
+      <c r="E13" s="80">
+        <v>3450165983</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="G13" s="81" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="83" t="s">
+        <v>254</v>
+      </c>
+      <c r="I13" s="43">
+        <v>45989</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="23"/>
+      <c r="B14" s="7">
+        <v>45989</v>
+      </c>
+      <c r="C14" s="24">
+        <v>45995</v>
+      </c>
+      <c r="D14" s="21">
+        <v>135613210</v>
+      </c>
+      <c r="E14" s="80">
+        <v>3450166599</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="G14" s="81" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" s="47" t="s">
+        <v>256</v>
+      </c>
+      <c r="I14" s="43">
+        <v>45989</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="23"/>
+      <c r="B15" s="7">
+        <v>45989</v>
+      </c>
+      <c r="C15" s="24">
+        <v>45995</v>
+      </c>
+      <c r="D15" s="21">
+        <v>135616894</v>
+      </c>
+      <c r="E15" s="80">
+        <v>3450167193</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="G15" s="81" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="47" t="s">
+        <v>258</v>
+      </c>
+      <c r="I15" s="43">
+        <v>45989</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="6"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="23"/>
+      <c r="A16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="7">
+        <v>45989</v>
+      </c>
+      <c r="C16" s="24">
+        <v>45995</v>
+      </c>
+      <c r="D16" s="21">
+        <v>135597411</v>
+      </c>
+      <c r="E16" s="80">
+        <v>3450164784</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="G16" s="81" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="47" t="s">
+        <v>260</v>
+      </c>
+      <c r="I16" s="43">
+        <v>45989</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="6"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="23"/>
+      <c r="A17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="7">
+        <v>45989</v>
+      </c>
+      <c r="C17" s="24">
+        <v>45995</v>
+      </c>
+      <c r="D17" s="21">
+        <v>135616932</v>
+      </c>
+      <c r="E17" s="80">
+        <v>3450167204</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="43">
+        <v>45989</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="23"/>
+      <c r="A18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="7">
+        <v>45988</v>
+      </c>
+      <c r="C18" s="24">
+        <v>45995</v>
+      </c>
+      <c r="D18" s="21">
+        <v>135607242</v>
+      </c>
+      <c r="E18" s="80">
+        <v>3450162859</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="H18" s="47" t="s">
+        <v>164</v>
+      </c>
+      <c r="I18" s="43">
+        <v>45988</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="23"/>
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7">
+        <v>45989</v>
+      </c>
+      <c r="C19" s="24">
+        <v>45995</v>
+      </c>
+      <c r="D19" s="21">
+        <v>135608569</v>
+      </c>
+      <c r="E19" s="80">
+        <v>3450165972</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="H19" s="47" t="s">
+        <v>264</v>
+      </c>
+      <c r="I19" s="43">
+        <v>45989</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="23"/>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="6"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="9"/>
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>45989</v>
+      </c>
+      <c r="C20" s="24">
+        <v>45995</v>
+      </c>
+      <c r="D20" s="21">
+        <v>135604720</v>
+      </c>
+      <c r="E20" s="80">
+        <v>3450165675</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="H20" s="47" t="s">
+        <v>266</v>
+      </c>
+      <c r="I20" s="43">
+        <v>45989</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="15.75">
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>45993</v>
+      </c>
+      <c r="C21" s="24">
+        <v>45995</v>
+      </c>
+      <c r="D21" s="21">
+        <v>135658305</v>
+      </c>
+      <c r="E21" s="80">
+        <v>3450169680</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="H21" s="83" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="43">
+        <v>45993</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="9"/>
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7">
+        <v>45994</v>
+      </c>
+      <c r="C22" s="24">
+        <v>45995</v>
+      </c>
+      <c r="D22" s="21">
+        <v>135681487</v>
+      </c>
+      <c r="E22" s="80">
+        <v>3450171241</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="G22" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22" s="47" t="s">
+        <v>269</v>
+      </c>
+      <c r="I22" s="43">
+        <v>45994</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="9"/>
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>45981</v>
+      </c>
+      <c r="C23" s="24">
+        <v>45995</v>
+      </c>
+      <c r="D23" s="21">
+        <v>135492193</v>
+      </c>
+      <c r="E23" s="80">
+        <v>3450153058</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="H23" s="47" t="s">
+        <v>206</v>
+      </c>
+      <c r="I23" s="43">
+        <v>45993</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="9"/>
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>45998</v>
+      </c>
+      <c r="C24" s="24">
+        <v>45995</v>
+      </c>
+      <c r="D24" s="21">
+        <v>135510893</v>
+      </c>
+      <c r="E24" s="80">
+        <v>3450156424</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="H24" s="47" t="s">
+        <v>206</v>
+      </c>
+      <c r="I24" s="43">
+        <v>45993</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="9"/>
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="7">
+        <v>45985</v>
+      </c>
+      <c r="C25" s="24">
+        <v>45995</v>
+      </c>
+      <c r="D25" s="21">
+        <v>135508650</v>
+      </c>
+      <c r="E25" s="80">
+        <v>3450156149</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="G25" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H25" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="I25" s="43">
+        <v>45985</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="9"/>
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="7">
+        <v>45985</v>
+      </c>
+      <c r="C26" s="24">
+        <v>45995</v>
+      </c>
+      <c r="D26" s="21">
+        <v>135509673</v>
+      </c>
+      <c r="E26" s="80">
+        <v>3450156314</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="G26" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H26" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="I26" s="43">
+        <v>45985</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="9"/>
+      <c r="A27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="7">
+        <v>45985</v>
+      </c>
+      <c r="C27" s="24">
+        <v>45995</v>
+      </c>
+      <c r="D27" s="21">
+        <v>135515765</v>
+      </c>
+      <c r="E27" s="80">
+        <v>3450157062</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="G27" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H27" s="47" t="s">
+        <v>275</v>
+      </c>
+      <c r="I27" s="43">
+        <v>45985</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="9"/>
+      <c r="A28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="7">
+        <v>45985</v>
+      </c>
+      <c r="C28" s="24">
+        <v>45995</v>
+      </c>
+      <c r="D28" s="21">
+        <v>135517113</v>
+      </c>
+      <c r="E28" s="80">
+        <v>3450157139</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="G28" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H28" s="47" t="s">
+        <v>275</v>
+      </c>
+      <c r="I28" s="43">
+        <v>45985</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="6"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="9"/>
+      <c r="A29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="7">
+        <v>45985</v>
+      </c>
+      <c r="C29" s="24">
+        <v>45995</v>
+      </c>
+      <c r="D29" s="21">
+        <v>135517549</v>
+      </c>
+      <c r="E29" s="80">
+        <v>3450157161</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="G29" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H29" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="I29" s="43">
+        <v>45985</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="6"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="9"/>
+      <c r="A30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="7">
+        <v>45985</v>
+      </c>
+      <c r="C30" s="24">
+        <v>45995</v>
+      </c>
+      <c r="D30" s="21">
+        <v>135520409</v>
+      </c>
+      <c r="E30" s="80">
+        <v>3450157480</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="G30" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H30" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="I30" s="43">
+        <v>45985</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="6"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="9"/>
+      <c r="A31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="7">
+        <v>45985</v>
+      </c>
+      <c r="C31" s="24">
+        <v>45995</v>
+      </c>
+      <c r="D31" s="21">
+        <v>135520535</v>
+      </c>
+      <c r="E31" s="80">
+        <v>3450157491</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="G31" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H31" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="I31" s="43">
+        <v>45985</v>
+      </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="6"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="9"/>
+      <c r="A32" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="7">
+        <v>45985</v>
+      </c>
+      <c r="C32" s="24">
+        <v>45995</v>
+      </c>
+      <c r="D32" s="21">
+        <v>135522141</v>
+      </c>
+      <c r="E32" s="80">
+        <v>3450157645</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="G32" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H32" s="47" t="s">
+        <v>275</v>
+      </c>
+      <c r="I32" s="43">
+        <v>45985</v>
+      </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="6"/>
       <c r="B33" s="8"/>
       <c r="C33" s="7"/>
-      <c r="D33" s="8"/>
+      <c r="D33" s="20"/>
       <c r="E33" s="8"/>
-      <c r="F33" s="9"/>
+      <c r="F33" s="14"/>
       <c r="G33" s="6"/>
       <c r="H33" s="9"/>
     </row>
@@ -6994,12 +7689,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="5">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A18" xr:uid="{69840FBE-03D6-48CB-B553-2E7186E1B4BD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A32" xr:uid="{69840FBE-03D6-48CB-B553-2E7186E1B4BD}">
       <formula1>$J$2</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G41" xr:uid="{AF5C7196-9DAE-4339-82D4-9412023E2B2A}">
@@ -7058,14 +7753,30 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="23"/>
+      <c r="B2" s="7">
+        <v>45759</v>
+      </c>
+      <c r="C2" s="7">
+        <v>45789</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>281</v>
+      </c>
+      <c r="E2" s="17">
+        <v>3450173496</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="I2" s="23" t="s">
+        <v>283</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
@@ -9438,65 +10149,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-531147</_dlc_DocId>
@@ -9539,7 +10191,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="522e863aef51f288a2c445becadad51a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e2cd90bc508d2ca63574b1ae88af87c9" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -9917,18 +10569,77 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D4EFA99-97F1-4AD8-8739-0BF52BF73A7C}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED44BF61-13B5-4B27-80E4-AE5B5A73F019}"/>
 </file>
--- a/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 01.12.2025 a 08.12.2025.xlsx
+++ b/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 01.12.2025 a 08.12.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/12. Dezembro/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{69DB2067-1512-47BC-83B5-30E8D713844E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D333A203-4588-4233-9D20-57DA98637FA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01.12" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1101" uniqueCount="374">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -1095,6 +1095,171 @@
   </si>
   <si>
     <t>LUIZ FERNANDO DA SILVA CAVALHEIRO CPF 05242311177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JACQUELINE AZAMBUJA RIES                     </t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 05.12.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THOMAZ ANTONIO LICARIAO ROCHA                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conforme consulta na central de bônus, identificamos que a
+apólice consta ativa na congênere, para que possamos prosseguir
+coma liberação do bloqueio será necessário a apresentação do en
+dosso de cancelamento emitido, a atualização junto a Central de Bô
+nus. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCOS ROBERTO BATISTA                       </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não
+há possibilidade efetuar a transferência de bônus para o(a) senhor
+(a) MARCOS ROBERTO BATISTA , pois este não consta como condutor na
+apólice anterior. &lt;br&gt;&lt;br&gt;Neste caso estamos nesta data efetuand
+o a recusa desta proposta. &lt;br&gt;&lt;br&gt;Orientamos transmitir um novo p
+rocesso como Seguro Novo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOAO DE MONTE CASTRO                         </t>
+  </si>
+  <si>
+    <t>***FRUSTRADO**CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO: Documento de outro veículo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODAIR MIGUEL JUNIOR                          </t>
+  </si>
+  <si>
+    <t>FRUSTRADO *PRAZO EXP *repique: Frente passageiro, Traseira motorista, Chassi, Frente motorista, Traseira passageiro, AIR BAG ACIONADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATRICIA MACHADO SOARES                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRUSTRADO *PRAZO EXP * SEGURADO N FEZ O ENVIO DE TODAS AS FOTOS // CRLV DE OUTEO VEÍC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDRESSA FERNANDA SILVA DOS SANTOS           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FERNANDA NEVES PETROLE                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HIDROJERT SANEAMENTO E SERVICOS LTDA ME      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: Frente e lateral do passageiro e do motorista, Traseira e lateral do motorista, (Não enquadrada) Chassi (Local incorreto) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCO AURELIO VERDERIO LOPES                 </t>
+  </si>
+  <si>
+    <t>**FRUSTRADO** CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA:HODÔMETRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JP ENGENHARIA LTDA ME                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE GOMES                                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUVELINA APARECIDA DA SILVA DUO              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAFAEL FERREIRA SANTOS                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEREZA RACHEL GONZALES DA SILVA              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALTER JOSE CARDOZO                          </t>
+  </si>
+  <si>
+    <t>FRUSTRADO *PRAZO EXP * SEGURADO N CORRIGIU OS PASSOS SOLICITADOS repique: Frente e lateral do passageiro, Traseira e lateral do motorista, Porta malas aberto, Chassi, Frente e lateral do motorista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SILVIMAR JOSE DA SILVA                       </t>
+  </si>
+  <si>
+    <t>FRUSTRADO *PRAZO EXP * SEGURADO N CORRIGIU OS PASSOS SOLICITADOS repique: Frente e lateral do passageiro, Documento do veículo, Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISRAEL DA SILVA PESSANHA                     </t>
+  </si>
+  <si>
+    <t>Fotos que tiveram repique: Frente e lateral do passageiro, Traseira e lateral do motorista, Painel com carro ligado, Porta malas aberto, Documento , Chassi, Frente e lateral do mot, Motor e placa, Traseira e lateral do pas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMANDA COSTA FALEIROS BARBOSA ROCHA          </t>
+  </si>
+  <si>
+    <t>CBE:CPF/CNPJ NAO CONF. /RENOVACAO FORA DO PRAZO /BON
+US INCORRETO /SEGURADO ATUAL OU ANTERIOR PJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CELSO MOREIRA DE LIMA                        </t>
+  </si>
+  <si>
+    <t>C
+onforme CBE houve sinistro na apólice anterior, portanto a renovaç
+ão correta é externa com sinistro. &lt;br&gt;Com a correção do Tipo de R
+enovação, ficou 10x R$ 306,46. Podemos emitir desta forma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESPACIAL PUBLICIDADE E COMUNICACAO LTDA ME   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RODRIGO ANTONIO DOS SANTOS COSTA             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE RIBEIRO JUNIOR                          </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não
+há possibilidade efetuar a transferência de bônus para o(a) senhor
+(a) SUELEN SILVA LIMA DE JESUS, pois este não consta como condutor
+na apólice anterior. &lt;br&gt;&lt;br&gt;Neste caso estamos nesta data efetu
+ando a recusa desta proposta. &lt;br&gt;&lt;br&gt;Orientamos transmitir um nov
+o processo comoSeguro Novo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUANA COMERCIO DE VARIEDADES LTDA ME         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALAMO ASSOALHOS E COMPENSADOS LTDA EPP       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRUSTRADO *PRAZO EXP * SEGURADO N CORRIGIU OS PASSOS SOLICITADOS repique: Chassi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MICHEL RODRIGUES MARIA                       </t>
+  </si>
+  <si>
+    <t>**FRUSTRADO** CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA:DOCUMENTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRISTIMAR MOREIRA GOMES                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">***FRUSTRADO**CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO: Local incorreto do Chassi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIO RICCI NETO                             </t>
+  </si>
+  <si>
+    <t>FRUSTRADO *PRAZO EXP * SEGURADO N CORRIGIU OS PASSOS SOLICITADOS repique: Frente e lateral do passageiro, Traseira e lateral do motorista, Chassi, Frente e lateral do motorista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULO ADRIEL OLIVEIRA DA SILVA               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GABRIEL ALVES SANTANA                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRUSTRADO *PRAZO EXP * SEGURADO N CORRIGIU OS PASSOS SOLICITADOS repique: Painel com carro DESligado, Chassi </t>
   </si>
 </sst>
 </file>
@@ -1178,7 +1343,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -1408,12 +1573,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1622,9 +1798,25 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8110,7 +8302,7 @@
       <c r="G9" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="H9" s="80" t="s">
+      <c r="H9" s="42" t="s">
         <v>150</v>
       </c>
       <c r="I9" s="38">
@@ -8429,7 +8621,7 @@
       <c r="G20" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="H20" s="80" t="s">
+      <c r="H20" s="42" t="s">
         <v>307</v>
       </c>
       <c r="I20" s="38">
@@ -9015,7 +9207,7 @@
       <c r="G2" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="81" t="s">
+      <c r="H2" s="80" t="s">
         <v>317</v>
       </c>
       <c r="I2" s="38">
@@ -9044,7 +9236,7 @@
       <c r="G3" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="H3" s="81" t="s">
+      <c r="H3" s="80" t="s">
         <v>319</v>
       </c>
       <c r="I3" s="38">
@@ -9073,7 +9265,7 @@
       <c r="G4" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="81" t="s">
+      <c r="H4" s="80" t="s">
         <v>321</v>
       </c>
       <c r="I4" s="38">
@@ -9102,7 +9294,7 @@
       <c r="G5" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="82" t="s">
+      <c r="H5" s="81" t="s">
         <v>323</v>
       </c>
       <c r="I5" s="54">
@@ -10216,7 +10408,7 @@
     <col min="5" max="5" width="25.85546875" customWidth="1"/>
     <col min="6" max="6" width="20.7109375" customWidth="1"/>
     <col min="7" max="7" width="25" customWidth="1"/>
-    <col min="8" max="8" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="24.5703125" customWidth="1"/>
     <col min="9" max="9" width="22" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10259,16 +10451,16 @@
       <c r="C2" s="22">
         <v>45999</v>
       </c>
-      <c r="D2" s="37" t="s">
+      <c r="D2" s="52" t="s">
         <v>281</v>
       </c>
-      <c r="E2" s="15">
+      <c r="E2" s="48">
         <v>3450159691</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="49" t="s">
         <v>324</v>
       </c>
-      <c r="G2" s="36" t="s">
+      <c r="G2" s="86" t="s">
         <v>13</v>
       </c>
       <c r="H2" s="39" t="s">
@@ -10280,405 +10472,967 @@
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="38"/>
+      <c r="B3" s="7">
+        <v>45988</v>
+      </c>
+      <c r="C3" s="22">
+        <v>45999</v>
+      </c>
+      <c r="D3" s="88">
+        <v>135580271</v>
+      </c>
+      <c r="E3" s="15">
+        <v>3450163079</v>
+      </c>
+      <c r="F3" s="82" t="s">
+        <v>325</v>
+      </c>
+      <c r="G3" s="36" t="s">
+        <v>75</v>
+      </c>
+      <c r="H3" s="83" t="s">
+        <v>326</v>
+      </c>
+      <c r="I3" s="38">
+        <v>45996</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="38"/>
+      <c r="B4" s="7">
+        <v>45988</v>
+      </c>
+      <c r="C4" s="22">
+        <v>45999</v>
+      </c>
+      <c r="D4" s="88">
+        <v>135585551</v>
+      </c>
+      <c r="E4" s="15">
+        <v>3450163740</v>
+      </c>
+      <c r="F4" s="82" t="s">
+        <v>327</v>
+      </c>
+      <c r="G4" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="89" t="s">
+        <v>328</v>
+      </c>
+      <c r="I4" s="38">
+        <v>45989</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="38"/>
+      <c r="B5" s="7">
+        <v>45989</v>
+      </c>
+      <c r="C5" s="22">
+        <v>45999</v>
+      </c>
+      <c r="D5" s="88">
+        <v>135600758</v>
+      </c>
+      <c r="E5" s="15">
+        <v>3450165092</v>
+      </c>
+      <c r="F5" s="82" t="s">
+        <v>329</v>
+      </c>
+      <c r="G5" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="89" t="s">
+        <v>330</v>
+      </c>
+      <c r="I5" s="38">
+        <v>45999</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="38"/>
+      <c r="B6" s="7">
+        <v>45992</v>
+      </c>
+      <c r="C6" s="22">
+        <v>45999</v>
+      </c>
+      <c r="D6" s="88">
+        <v>135629178</v>
+      </c>
+      <c r="E6" s="15">
+        <v>3450167600</v>
+      </c>
+      <c r="F6" s="82" t="s">
+        <v>331</v>
+      </c>
+      <c r="G6" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="83" t="s">
+        <v>332</v>
+      </c>
+      <c r="I6" s="38">
+        <v>45992</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="40"/>
-      <c r="I7" s="38"/>
+      <c r="B7" s="7">
+        <v>45989</v>
+      </c>
+      <c r="C7" s="22">
+        <v>45999</v>
+      </c>
+      <c r="D7" s="88">
+        <v>135627751</v>
+      </c>
+      <c r="E7" s="15">
+        <v>3450166038</v>
+      </c>
+      <c r="F7" s="82" t="s">
+        <v>333</v>
+      </c>
+      <c r="G7" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" s="84" t="s">
+        <v>334</v>
+      </c>
+      <c r="I7" s="38">
+        <v>45989</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="38"/>
+      <c r="B8" s="7">
+        <v>45989</v>
+      </c>
+      <c r="C8" s="22">
+        <v>45999</v>
+      </c>
+      <c r="D8" s="88">
+        <v>135632527</v>
+      </c>
+      <c r="E8" s="15">
+        <v>3450165532</v>
+      </c>
+      <c r="F8" s="82" t="s">
+        <v>335</v>
+      </c>
+      <c r="G8" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="84" t="s">
+        <v>336</v>
+      </c>
+      <c r="I8" s="38">
+        <v>45989</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="38"/>
+      <c r="B9" s="7">
+        <v>45992</v>
+      </c>
+      <c r="C9" s="22">
+        <v>45999</v>
+      </c>
+      <c r="D9" s="88">
+        <v>135642181</v>
+      </c>
+      <c r="E9" s="15">
+        <v>3450168788</v>
+      </c>
+      <c r="F9" s="82" t="s">
+        <v>337</v>
+      </c>
+      <c r="G9" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="83" t="s">
+        <v>216</v>
+      </c>
+      <c r="I9" s="38">
+        <v>45992</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="38"/>
+      <c r="B10" s="7">
+        <v>45993</v>
+      </c>
+      <c r="C10" s="22">
+        <v>45999</v>
+      </c>
+      <c r="D10" s="88">
+        <v>135661683</v>
+      </c>
+      <c r="E10" s="15">
+        <v>3450169900</v>
+      </c>
+      <c r="F10" s="82" t="s">
+        <v>338</v>
+      </c>
+      <c r="G10" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="83" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="38">
+        <v>45993</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="38"/>
+      <c r="B11" s="7">
+        <v>45993</v>
+      </c>
+      <c r="C11" s="22">
+        <v>45999</v>
+      </c>
+      <c r="D11" s="88">
+        <v>135656070</v>
+      </c>
+      <c r="E11" s="15">
+        <v>3450169481</v>
+      </c>
+      <c r="F11" s="82" t="s">
+        <v>339</v>
+      </c>
+      <c r="G11" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" s="83" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="38">
+        <v>45993</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="38"/>
+      <c r="B12" s="7">
+        <v>45993</v>
+      </c>
+      <c r="C12" s="22">
+        <v>45999</v>
+      </c>
+      <c r="D12" s="88">
+        <v>135655680</v>
+      </c>
+      <c r="E12" s="15">
+        <v>3450169437</v>
+      </c>
+      <c r="F12" s="82" t="s">
+        <v>298</v>
+      </c>
+      <c r="G12" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" s="83" t="s">
+        <v>340</v>
+      </c>
+      <c r="I12" s="38">
+        <v>45993</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="38"/>
+      <c r="B13" s="7">
+        <v>45994</v>
+      </c>
+      <c r="C13" s="22">
+        <v>45999</v>
+      </c>
+      <c r="D13" s="88">
+        <v>135675052</v>
+      </c>
+      <c r="E13" s="15">
+        <v>3450170625</v>
+      </c>
+      <c r="F13" s="82" t="s">
+        <v>341</v>
+      </c>
+      <c r="G13" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="83" t="s">
+        <v>342</v>
+      </c>
+      <c r="I13" s="38">
+        <v>45994</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="38"/>
+      <c r="B14" s="7">
+        <v>45996</v>
+      </c>
+      <c r="C14" s="22">
+        <v>45999</v>
+      </c>
+      <c r="D14" s="88">
+        <v>135728160</v>
+      </c>
+      <c r="E14" s="15">
+        <v>3450174827</v>
+      </c>
+      <c r="F14" s="82" t="s">
+        <v>343</v>
+      </c>
+      <c r="G14" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="83" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="38">
+        <v>45996</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="38"/>
+      <c r="B15" s="7">
+        <v>45996</v>
+      </c>
+      <c r="C15" s="22">
+        <v>45999</v>
+      </c>
+      <c r="D15" s="88">
+        <v>135730475</v>
+      </c>
+      <c r="E15" s="15">
+        <v>3450175058</v>
+      </c>
+      <c r="F15" s="82" t="s">
+        <v>344</v>
+      </c>
+      <c r="G15" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" s="83" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="38">
+        <v>45996</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="38"/>
+      <c r="B16" s="7">
+        <v>45997</v>
+      </c>
+      <c r="C16" s="22">
+        <v>45999</v>
+      </c>
+      <c r="D16" s="88">
+        <v>135740065</v>
+      </c>
+      <c r="E16" s="15">
+        <v>3450175619</v>
+      </c>
+      <c r="F16" s="82" t="s">
+        <v>345</v>
+      </c>
+      <c r="G16" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="83" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="38">
+        <v>45997</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="38"/>
+      <c r="B17" s="7">
+        <v>45993</v>
+      </c>
+      <c r="C17" s="22">
+        <v>45999</v>
+      </c>
+      <c r="D17" s="88">
+        <v>135654069</v>
+      </c>
+      <c r="E17" s="15">
+        <v>3450169261</v>
+      </c>
+      <c r="F17" s="82" t="s">
+        <v>346</v>
+      </c>
+      <c r="G17" s="36" t="s">
+        <v>75</v>
+      </c>
+      <c r="H17" s="83" t="s">
+        <v>326</v>
+      </c>
+      <c r="I17" s="38">
+        <v>45996</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="38"/>
+      <c r="B18" s="7">
+        <v>45988</v>
+      </c>
+      <c r="C18" s="22">
+        <v>45999</v>
+      </c>
+      <c r="D18" s="88">
+        <v>135576150</v>
+      </c>
+      <c r="E18" s="15">
+        <v>3450162496</v>
+      </c>
+      <c r="F18" s="82" t="s">
+        <v>347</v>
+      </c>
+      <c r="G18" s="36" t="s">
+        <v>75</v>
+      </c>
+      <c r="H18" s="83" t="s">
+        <v>326</v>
+      </c>
+      <c r="I18" s="38">
+        <v>45996</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="39"/>
-      <c r="I19" s="38"/>
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7">
+        <v>45989</v>
+      </c>
+      <c r="C19" s="22">
+        <v>45999</v>
+      </c>
+      <c r="D19" s="88">
+        <v>135622007</v>
+      </c>
+      <c r="E19" s="15">
+        <v>3450166764</v>
+      </c>
+      <c r="F19" s="82" t="s">
+        <v>348</v>
+      </c>
+      <c r="G19" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="H19" s="83" t="s">
+        <v>349</v>
+      </c>
+      <c r="I19" s="38">
+        <v>45989</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="38"/>
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>45989</v>
+      </c>
+      <c r="C20" s="22">
+        <v>45999</v>
+      </c>
+      <c r="D20" s="88">
+        <v>135609744</v>
+      </c>
+      <c r="E20" s="15">
+        <v>3450166236</v>
+      </c>
+      <c r="F20" s="82" t="s">
+        <v>350</v>
+      </c>
+      <c r="G20" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="H20" s="83" t="s">
+        <v>351</v>
+      </c>
+      <c r="I20" s="38">
+        <v>45989</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="38"/>
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>45989</v>
+      </c>
+      <c r="C21" s="22">
+        <v>45999</v>
+      </c>
+      <c r="D21" s="88">
+        <v>135611907</v>
+      </c>
+      <c r="E21" s="15">
+        <v>3450166489</v>
+      </c>
+      <c r="F21" s="82" t="s">
+        <v>352</v>
+      </c>
+      <c r="G21" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" s="83" t="s">
+        <v>353</v>
+      </c>
+      <c r="I21" s="38">
+        <v>45989</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="38"/>
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7">
+        <v>45993</v>
+      </c>
+      <c r="C22" s="22">
+        <v>45999</v>
+      </c>
+      <c r="D22" s="88">
+        <v>135670333</v>
+      </c>
+      <c r="E22" s="15">
+        <v>3450169701</v>
+      </c>
+      <c r="F22" s="82" t="s">
+        <v>354</v>
+      </c>
+      <c r="G22" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="H22" s="89" t="s">
+        <v>355</v>
+      </c>
+      <c r="I22" s="38">
+        <v>45993</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="36"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="38"/>
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>46005</v>
+      </c>
+      <c r="C23" s="22">
+        <v>45999</v>
+      </c>
+      <c r="D23" s="88">
+        <v>135569060</v>
+      </c>
+      <c r="E23" s="15">
+        <v>3450162155</v>
+      </c>
+      <c r="F23" s="82" t="s">
+        <v>356</v>
+      </c>
+      <c r="G23" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="H23" s="89" t="s">
+        <v>357</v>
+      </c>
+      <c r="I23" s="38">
+        <v>45992</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="36"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="38"/>
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>45992</v>
+      </c>
+      <c r="C24" s="22">
+        <v>45999</v>
+      </c>
+      <c r="D24" s="88">
+        <v>135635401</v>
+      </c>
+      <c r="E24" s="15">
+        <v>3450168216</v>
+      </c>
+      <c r="F24" s="82" t="s">
+        <v>358</v>
+      </c>
+      <c r="G24" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="H24" s="83" t="s">
+        <v>19</v>
+      </c>
+      <c r="I24" s="38">
+        <v>45992</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="36"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="38"/>
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="7">
+        <v>45988</v>
+      </c>
+      <c r="C25" s="22">
+        <v>45999</v>
+      </c>
+      <c r="D25" s="88">
+        <v>135591228</v>
+      </c>
+      <c r="E25" s="15">
+        <v>3450164465</v>
+      </c>
+      <c r="F25" s="82" t="s">
+        <v>359</v>
+      </c>
+      <c r="G25" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="H25" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="I25" s="38">
+        <v>45993</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="37"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="36"/>
-      <c r="H26" s="39"/>
-      <c r="I26" s="38"/>
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="7">
+        <v>45991</v>
+      </c>
+      <c r="C26" s="22">
+        <v>45999</v>
+      </c>
+      <c r="D26" s="88">
+        <v>135580003</v>
+      </c>
+      <c r="E26" s="15">
+        <v>3450163035</v>
+      </c>
+      <c r="F26" s="82" t="s">
+        <v>360</v>
+      </c>
+      <c r="G26" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="H26" s="89" t="s">
+        <v>150</v>
+      </c>
+      <c r="I26" s="38">
+        <v>45989</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="36"/>
-      <c r="H27" s="39"/>
-      <c r="I27" s="38"/>
+      <c r="A27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="7">
+        <v>45989</v>
+      </c>
+      <c r="C27" s="22">
+        <v>45999</v>
+      </c>
+      <c r="D27" s="88">
+        <v>135601184</v>
+      </c>
+      <c r="E27" s="15">
+        <v>3450165180</v>
+      </c>
+      <c r="F27" s="82" t="s">
+        <v>248</v>
+      </c>
+      <c r="G27" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="H27" s="89" t="s">
+        <v>361</v>
+      </c>
+      <c r="I27" s="90">
+        <v>45999</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="37"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="36"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="38"/>
+      <c r="A28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="7">
+        <v>45993</v>
+      </c>
+      <c r="C28" s="22">
+        <v>45999</v>
+      </c>
+      <c r="D28" s="88">
+        <v>135653926</v>
+      </c>
+      <c r="E28" s="15">
+        <v>3450169240</v>
+      </c>
+      <c r="F28" s="82" t="s">
+        <v>362</v>
+      </c>
+      <c r="G28" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="H28" s="83" t="s">
+        <v>32</v>
+      </c>
+      <c r="I28" s="38">
+        <v>45993</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="6"/>
-      <c r="B29" s="41"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="37"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="36"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="38"/>
+      <c r="A29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="41">
+        <v>45992</v>
+      </c>
+      <c r="C29" s="22">
+        <v>45999</v>
+      </c>
+      <c r="D29" s="88">
+        <v>135633453</v>
+      </c>
+      <c r="E29" s="15">
+        <v>3450168029</v>
+      </c>
+      <c r="F29" s="82" t="s">
+        <v>30</v>
+      </c>
+      <c r="G29" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="H29" s="83" t="s">
+        <v>32</v>
+      </c>
+      <c r="I29" s="38">
+        <v>45992</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="6"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="37"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="38"/>
+      <c r="A30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="7">
+        <v>45992</v>
+      </c>
+      <c r="C30" s="22">
+        <v>45999</v>
+      </c>
+      <c r="D30" s="88">
+        <v>135637074</v>
+      </c>
+      <c r="E30" s="15">
+        <v>3450168359</v>
+      </c>
+      <c r="F30" s="82" t="s">
+        <v>363</v>
+      </c>
+      <c r="G30" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="H30" s="85" t="s">
+        <v>364</v>
+      </c>
+      <c r="I30" s="38">
+        <v>45992</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="6"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="37"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="36"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="38"/>
+      <c r="A31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="7">
+        <v>45993</v>
+      </c>
+      <c r="C31" s="22">
+        <v>45999</v>
+      </c>
+      <c r="D31" s="88">
+        <v>135653660</v>
+      </c>
+      <c r="E31" s="15">
+        <v>3450169195</v>
+      </c>
+      <c r="F31" s="82" t="s">
+        <v>365</v>
+      </c>
+      <c r="G31" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="H31" s="85" t="s">
+        <v>366</v>
+      </c>
+      <c r="I31" s="38">
+        <v>45993</v>
+      </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="6"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="37"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="36"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="38"/>
+      <c r="A32" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="7">
+        <v>45993</v>
+      </c>
+      <c r="C32" s="22">
+        <v>45999</v>
+      </c>
+      <c r="D32" s="88">
+        <v>135659491</v>
+      </c>
+      <c r="E32" s="15">
+        <v>3450169789</v>
+      </c>
+      <c r="F32" s="82" t="s">
+        <v>367</v>
+      </c>
+      <c r="G32" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="H32" s="85" t="s">
+        <v>368</v>
+      </c>
+      <c r="I32" s="38">
+        <v>45993</v>
+      </c>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="6"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="37"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="38"/>
+      <c r="A33" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="7">
+        <v>45992</v>
+      </c>
+      <c r="C33" s="22">
+        <v>45999</v>
+      </c>
+      <c r="D33" s="88">
+        <v>135643003</v>
+      </c>
+      <c r="E33" s="15">
+        <v>3450168832</v>
+      </c>
+      <c r="F33" s="82" t="s">
+        <v>369</v>
+      </c>
+      <c r="G33" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="H33" s="85" t="s">
+        <v>370</v>
+      </c>
+      <c r="I33" s="38">
+        <v>45992</v>
+      </c>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34" s="6"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="22"/>
-      <c r="D34" s="37"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="38"/>
+      <c r="A34" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="7">
+        <v>45992</v>
+      </c>
+      <c r="C34" s="22">
+        <v>45999</v>
+      </c>
+      <c r="D34" s="88">
+        <v>135637294</v>
+      </c>
+      <c r="E34" s="15">
+        <v>3450168360</v>
+      </c>
+      <c r="F34" s="82" t="s">
+        <v>371</v>
+      </c>
+      <c r="G34" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="H34" s="85" t="s">
+        <v>216</v>
+      </c>
+      <c r="I34" s="38">
+        <v>45992</v>
+      </c>
     </row>
     <row r="35" spans="1:9">
-      <c r="A35" s="6"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="22"/>
-      <c r="D35" s="37"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="36"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="38"/>
+      <c r="A35" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="7">
+        <v>45992</v>
+      </c>
+      <c r="C35" s="22">
+        <v>45999</v>
+      </c>
+      <c r="D35" s="88">
+        <v>135633111</v>
+      </c>
+      <c r="E35" s="15">
+        <v>3450167952</v>
+      </c>
+      <c r="F35" s="82" t="s">
+        <v>372</v>
+      </c>
+      <c r="G35" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="H35" s="85" t="s">
+        <v>373</v>
+      </c>
+      <c r="I35" s="38">
+        <v>45992</v>
+      </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
       <c r="B36" s="7"/>
       <c r="C36" s="22"/>
-      <c r="D36" s="37"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="36"/>
+      <c r="D36" s="53"/>
+      <c r="E36" s="44"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="87"/>
       <c r="H36" s="11"/>
       <c r="I36" s="38"/>
     </row>
@@ -10761,7 +11515,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="1">
+    <cfRule type="notContainsBlanks" priority="2">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10769,7 +11523,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G43" xr:uid="{6BE23EBC-FF30-4764-B2ED-DADD17818F83}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A19:A42" xr:uid="{739D573C-5EC2-4CE2-AADE-3BE4A15DFB2F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A36:A42" xr:uid="{739D573C-5EC2-4CE2-AADE-3BE4A15DFB2F}">
       <formula1>$J$2</formula1>
     </dataValidation>
   </dataValidations>
@@ -10781,7 +11535,7 @@
           <x14:formula1>
             <xm:f>'06.12'!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>A2:A18</xm:sqref>
+          <xm:sqref>A2:A35</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -10790,6 +11544,65 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="522e863aef51f288a2c445becadad51a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e2cd90bc508d2ca63574b1ae88af87c9" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -11167,65 +11980,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11270,7 +12024,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D4EFA99-97F1-4AD8-8739-0BF52BF73A7C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11278,7 +12032,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D4EFA99-97F1-4AD8-8739-0BF52BF73A7C}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
